--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['41', '81', '83']</t>
   </si>
   <si>
+    <t>['3', '46', '64', '82']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>['82']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1921,7 +1927,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2127,7 +2133,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2333,7 +2339,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2539,7 +2545,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2745,7 +2751,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3032,7 +3038,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ10">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3157,7 +3163,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3363,7 +3369,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3647,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>0.13</v>
@@ -4268,7 +4274,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ16">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR16">
         <v>1.37</v>
@@ -4393,7 +4399,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4599,7 +4605,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4805,7 +4811,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5217,7 +5223,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5629,7 +5635,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5707,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>1.13</v>
@@ -5835,7 +5841,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6041,7 +6047,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6247,7 +6253,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6453,7 +6459,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6659,7 +6665,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6865,7 +6871,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -6946,7 +6952,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR29">
         <v>1.88</v>
@@ -7071,7 +7077,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7483,7 +7489,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7689,7 +7695,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7895,7 +7901,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8101,7 +8107,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8307,7 +8313,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8385,7 +8391,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.78</v>
@@ -8925,7 +8931,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9131,7 +9137,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9337,7 +9343,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9418,7 +9424,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ41">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -9543,7 +9549,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9955,7 +9961,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10161,7 +10167,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10367,7 +10373,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10573,7 +10579,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10654,7 +10660,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ47">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10857,7 +10863,7 @@
         <v>0.75</v>
       </c>
       <c r="AP48">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>0.78</v>
@@ -11191,7 +11197,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11603,7 +11609,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12015,7 +12021,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12427,7 +12433,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12714,7 +12720,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ57">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR57">
         <v>1.87</v>
@@ -13045,7 +13051,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13251,7 +13257,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13457,7 +13463,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13663,7 +13669,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13869,7 +13875,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14075,7 +14081,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14281,7 +14287,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14565,7 +14571,7 @@
         <v>1.8</v>
       </c>
       <c r="AP66">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
@@ -14693,7 +14699,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14899,7 +14905,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15186,7 +15192,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ69">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR69">
         <v>1.17</v>
@@ -15311,7 +15317,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15517,7 +15523,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15723,7 +15729,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16419,7 +16425,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>1.5</v>
@@ -16753,7 +16759,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17371,7 +17377,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17577,7 +17583,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17783,7 +17789,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -17864,7 +17870,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ82">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -17989,7 +17995,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18195,7 +18201,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18401,7 +18407,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19019,7 +19025,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19431,7 +19437,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19637,7 +19643,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19715,7 +19721,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
         <v>0.88</v>
@@ -20336,7 +20342,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR94">
         <v>1.41</v>
@@ -20461,7 +20467,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20667,7 +20673,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21157,7 +21163,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
         <v>0.67</v>
@@ -21285,7 +21291,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21491,7 +21497,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21697,7 +21703,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21903,7 +21909,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22266,6 +22272,212 @@
       </c>
       <c r="BP103">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7452357</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45702.625</v>
+      </c>
+      <c r="F104">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>4</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>5</v>
+      </c>
+      <c r="O104" t="s">
+        <v>164</v>
+      </c>
+      <c r="P104" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q104">
+        <v>2.05</v>
+      </c>
+      <c r="R104">
+        <v>2.4</v>
+      </c>
+      <c r="S104">
+        <v>5.5</v>
+      </c>
+      <c r="T104">
+        <v>1.3</v>
+      </c>
+      <c r="U104">
+        <v>3.4</v>
+      </c>
+      <c r="V104">
+        <v>2.38</v>
+      </c>
+      <c r="W104">
+        <v>1.53</v>
+      </c>
+      <c r="X104">
+        <v>6</v>
+      </c>
+      <c r="Y104">
+        <v>1.13</v>
+      </c>
+      <c r="Z104">
+        <v>1.57</v>
+      </c>
+      <c r="AA104">
+        <v>4.2</v>
+      </c>
+      <c r="AB104">
+        <v>5.2</v>
+      </c>
+      <c r="AC104">
+        <v>1.04</v>
+      </c>
+      <c r="AD104">
+        <v>10</v>
+      </c>
+      <c r="AE104">
+        <v>1.2</v>
+      </c>
+      <c r="AF104">
+        <v>4.33</v>
+      </c>
+      <c r="AG104">
+        <v>1.6</v>
+      </c>
+      <c r="AH104">
+        <v>2.1</v>
+      </c>
+      <c r="AI104">
+        <v>1.7</v>
+      </c>
+      <c r="AJ104">
+        <v>2.05</v>
+      </c>
+      <c r="AK104">
+        <v>1.15</v>
+      </c>
+      <c r="AL104">
+        <v>1.21</v>
+      </c>
+      <c r="AM104">
+        <v>2.35</v>
+      </c>
+      <c r="AN104">
+        <v>1.88</v>
+      </c>
+      <c r="AO104">
+        <v>0.78</v>
+      </c>
+      <c r="AP104">
+        <v>2</v>
+      </c>
+      <c r="AQ104">
+        <v>0.7</v>
+      </c>
+      <c r="AR104">
+        <v>1.62</v>
+      </c>
+      <c r="AS104">
+        <v>1.4</v>
+      </c>
+      <c r="AT104">
+        <v>3.02</v>
+      </c>
+      <c r="AU104">
+        <v>10</v>
+      </c>
+      <c r="AV104">
+        <v>6</v>
+      </c>
+      <c r="AW104">
+        <v>6</v>
+      </c>
+      <c r="AX104">
+        <v>8</v>
+      </c>
+      <c r="AY104">
+        <v>16</v>
+      </c>
+      <c r="AZ104">
+        <v>17</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>7</v>
+      </c>
+      <c r="BC104">
+        <v>11</v>
+      </c>
+      <c r="BD104">
+        <v>1.32</v>
+      </c>
+      <c r="BE104">
+        <v>7.5</v>
+      </c>
+      <c r="BF104">
+        <v>3.65</v>
+      </c>
+      <c r="BG104">
+        <v>1.19</v>
+      </c>
+      <c r="BH104">
+        <v>4.1</v>
+      </c>
+      <c r="BI104">
+        <v>1.34</v>
+      </c>
+      <c r="BJ104">
+        <v>2.9</v>
+      </c>
+      <c r="BK104">
+        <v>1.56</v>
+      </c>
+      <c r="BL104">
+        <v>2.25</v>
+      </c>
+      <c r="BM104">
+        <v>1.88</v>
+      </c>
+      <c r="BN104">
+        <v>1.81</v>
+      </c>
+      <c r="BO104">
+        <v>2.32</v>
+      </c>
+      <c r="BP104">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -22426,7 +22426,7 @@
         <v>8</v>
       </c>
       <c r="AY104">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ104">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,6 +511,9 @@
     <t>['3', '46', '64', '82']</t>
   </si>
   <si>
+    <t>['33']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -692,6 +695,9 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['24', '26', '45+2', '51']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1799,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4">
         <v>0.78</v>
@@ -1927,7 +1933,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2133,7 +2139,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2339,7 +2345,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2545,7 +2551,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2623,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2751,7 +2757,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3163,7 +3169,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3369,7 +3375,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3450,7 +3456,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3656,7 +3662,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4065,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4271,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ16">
         <v>0.7</v>
@@ -4399,7 +4405,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4605,7 +4611,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4811,7 +4817,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5095,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ20">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR20">
         <v>1.75</v>
@@ -5223,7 +5229,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5510,7 +5516,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ22">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR22">
         <v>1.44</v>
@@ -5635,7 +5641,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5716,7 +5722,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>1.53</v>
@@ -5841,7 +5847,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -5919,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6047,7 +6053,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6253,7 +6259,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6459,7 +6465,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6665,7 +6671,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6743,7 +6749,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28">
         <v>0.88</v>
@@ -6871,7 +6877,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7077,7 +7083,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7364,7 +7370,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ31">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR31">
         <v>1.74</v>
@@ -7489,7 +7495,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7570,7 +7576,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
         <v>1.14</v>
@@ -7695,7 +7701,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7773,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ33">
         <v>0.78</v>
@@ -7901,7 +7907,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8107,7 +8113,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8313,7 +8319,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8600,7 +8606,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ37">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR37">
         <v>1.54</v>
@@ -8806,7 +8812,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ38">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR38">
         <v>1.09</v>
@@ -8931,7 +8937,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9137,7 +9143,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9343,7 +9349,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9421,7 +9427,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>0.7</v>
@@ -9549,7 +9555,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9627,7 +9633,7 @@
         <v>1.67</v>
       </c>
       <c r="AP42">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42">
         <v>1.33</v>
@@ -9961,7 +9967,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10042,7 +10048,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR44">
         <v>0.9</v>
@@ -10167,7 +10173,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10245,7 +10251,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ45">
         <v>1.5</v>
@@ -10373,7 +10379,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10579,7 +10585,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11197,7 +11203,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11481,10 +11487,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR51">
         <v>1.45</v>
@@ -11609,7 +11615,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11896,7 +11902,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ53">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.13</v>
@@ -12021,7 +12027,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12099,7 +12105,7 @@
         <v>1.75</v>
       </c>
       <c r="AP54">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12433,7 +12439,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12717,7 +12723,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ57">
         <v>0.7</v>
@@ -13051,7 +13057,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13257,7 +13263,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13463,7 +13469,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13669,7 +13675,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13875,7 +13881,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13953,7 +13959,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>0.88</v>
@@ -14081,7 +14087,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14162,7 +14168,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR64">
         <v>1.45</v>
@@ -14287,7 +14293,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14368,7 +14374,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14699,7 +14705,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14777,7 +14783,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
         <v>1.5</v>
@@ -14905,7 +14911,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -14986,7 +14992,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ68">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR68">
         <v>1.76</v>
@@ -15317,7 +15323,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15523,7 +15529,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15729,7 +15735,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15807,7 +15813,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -16219,7 +16225,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ74">
         <v>0.67</v>
@@ -16634,7 +16640,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ76">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR76">
         <v>1.38</v>
@@ -16759,7 +16765,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17043,10 +17049,10 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ78">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR78">
         <v>1.92</v>
@@ -17377,7 +17383,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17455,7 +17461,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1.78</v>
@@ -17583,7 +17589,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17661,7 +17667,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ81">
         <v>1.33</v>
@@ -17789,7 +17795,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -17995,7 +18001,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18076,7 +18082,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ83">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR83">
         <v>1.59</v>
@@ -18201,7 +18207,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18282,7 +18288,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR84">
         <v>1.31</v>
@@ -18407,7 +18413,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18897,7 +18903,7 @@
         <v>1.86</v>
       </c>
       <c r="AP87">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87">
         <v>1.78</v>
@@ -19025,7 +19031,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19437,7 +19443,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19643,7 +19649,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19930,7 +19936,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR92">
         <v>1.68</v>
@@ -20136,7 +20142,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="AR93">
         <v>1.44</v>
@@ -20467,7 +20473,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20545,7 +20551,7 @@
         <v>1.38</v>
       </c>
       <c r="AP95">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
         <v>1.33</v>
@@ -20673,7 +20679,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20754,7 +20760,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ96">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR96">
         <v>1.89</v>
@@ -20957,7 +20963,7 @@
         <v>1.43</v>
       </c>
       <c r="AP97">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AQ97">
         <v>1.25</v>
@@ -21291,7 +21297,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21497,7 +21503,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21703,7 +21709,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21909,7 +21915,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -21987,10 +21993,10 @@
         <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
         <v>1.25</v>
@@ -22321,7 +22327,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22478,6 +22484,624 @@
       </c>
       <c r="BP104">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7452358</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F105">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>72</v>
+      </c>
+      <c r="H105" t="s">
+        <v>73</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>87</v>
+      </c>
+      <c r="P105" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q105">
+        <v>2.3</v>
+      </c>
+      <c r="R105">
+        <v>2.3</v>
+      </c>
+      <c r="S105">
+        <v>4.75</v>
+      </c>
+      <c r="T105">
+        <v>1.33</v>
+      </c>
+      <c r="U105">
+        <v>3.25</v>
+      </c>
+      <c r="V105">
+        <v>2.63</v>
+      </c>
+      <c r="W105">
+        <v>1.44</v>
+      </c>
+      <c r="X105">
+        <v>6.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.11</v>
+      </c>
+      <c r="Z105">
+        <v>1.67</v>
+      </c>
+      <c r="AA105">
+        <v>3.64</v>
+      </c>
+      <c r="AB105">
+        <v>5.1</v>
+      </c>
+      <c r="AC105">
+        <v>1.02</v>
+      </c>
+      <c r="AD105">
+        <v>10</v>
+      </c>
+      <c r="AE105">
+        <v>1.2</v>
+      </c>
+      <c r="AF105">
+        <v>3.88</v>
+      </c>
+      <c r="AG105">
+        <v>1.67</v>
+      </c>
+      <c r="AH105">
+        <v>2</v>
+      </c>
+      <c r="AI105">
+        <v>1.7</v>
+      </c>
+      <c r="AJ105">
+        <v>2.05</v>
+      </c>
+      <c r="AK105">
+        <v>1.2</v>
+      </c>
+      <c r="AL105">
+        <v>1.25</v>
+      </c>
+      <c r="AM105">
+        <v>2.13</v>
+      </c>
+      <c r="AN105">
+        <v>1.78</v>
+      </c>
+      <c r="AO105">
+        <v>0.13</v>
+      </c>
+      <c r="AP105">
+        <v>1.6</v>
+      </c>
+      <c r="AQ105">
+        <v>0.44</v>
+      </c>
+      <c r="AR105">
+        <v>1.26</v>
+      </c>
+      <c r="AS105">
+        <v>1.2</v>
+      </c>
+      <c r="AT105">
+        <v>2.46</v>
+      </c>
+      <c r="AU105">
+        <v>2</v>
+      </c>
+      <c r="AV105">
+        <v>2</v>
+      </c>
+      <c r="AW105">
+        <v>10</v>
+      </c>
+      <c r="AX105">
+        <v>3</v>
+      </c>
+      <c r="AY105">
+        <v>14</v>
+      </c>
+      <c r="AZ105">
+        <v>6</v>
+      </c>
+      <c r="BA105">
+        <v>9</v>
+      </c>
+      <c r="BB105">
+        <v>0</v>
+      </c>
+      <c r="BC105">
+        <v>9</v>
+      </c>
+      <c r="BD105">
+        <v>1.46</v>
+      </c>
+      <c r="BE105">
+        <v>6.75</v>
+      </c>
+      <c r="BF105">
+        <v>3.05</v>
+      </c>
+      <c r="BG105">
+        <v>1.28</v>
+      </c>
+      <c r="BH105">
+        <v>3.3</v>
+      </c>
+      <c r="BI105">
+        <v>1.49</v>
+      </c>
+      <c r="BJ105">
+        <v>2.4</v>
+      </c>
+      <c r="BK105">
+        <v>1.79</v>
+      </c>
+      <c r="BL105">
+        <v>1.9</v>
+      </c>
+      <c r="BM105">
+        <v>2.23</v>
+      </c>
+      <c r="BN105">
+        <v>1.56</v>
+      </c>
+      <c r="BO105">
+        <v>2.85</v>
+      </c>
+      <c r="BP105">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7452360</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45704.5</v>
+      </c>
+      <c r="F106">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>76</v>
+      </c>
+      <c r="H106" t="s">
+        <v>70</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>3</v>
+      </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>4</v>
+      </c>
+      <c r="N106">
+        <v>5</v>
+      </c>
+      <c r="O106" t="s">
+        <v>160</v>
+      </c>
+      <c r="P106" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q106">
+        <v>5</v>
+      </c>
+      <c r="R106">
+        <v>2.2</v>
+      </c>
+      <c r="S106">
+        <v>2.38</v>
+      </c>
+      <c r="T106">
+        <v>1.4</v>
+      </c>
+      <c r="U106">
+        <v>2.75</v>
+      </c>
+      <c r="V106">
+        <v>2.75</v>
+      </c>
+      <c r="W106">
+        <v>1.4</v>
+      </c>
+      <c r="X106">
+        <v>8</v>
+      </c>
+      <c r="Y106">
+        <v>1.08</v>
+      </c>
+      <c r="Z106">
+        <v>4.75</v>
+      </c>
+      <c r="AA106">
+        <v>3.75</v>
+      </c>
+      <c r="AB106">
+        <v>1.73</v>
+      </c>
+      <c r="AC106">
+        <v>1.01</v>
+      </c>
+      <c r="AD106">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE106">
+        <v>1.27</v>
+      </c>
+      <c r="AF106">
+        <v>3.25</v>
+      </c>
+      <c r="AG106">
+        <v>1.95</v>
+      </c>
+      <c r="AH106">
+        <v>1.85</v>
+      </c>
+      <c r="AI106">
+        <v>1.91</v>
+      </c>
+      <c r="AJ106">
+        <v>1.91</v>
+      </c>
+      <c r="AK106">
+        <v>2.06</v>
+      </c>
+      <c r="AL106">
+        <v>1.28</v>
+      </c>
+      <c r="AM106">
+        <v>1.2</v>
+      </c>
+      <c r="AN106">
+        <v>1.13</v>
+      </c>
+      <c r="AO106">
+        <v>1.13</v>
+      </c>
+      <c r="AP106">
+        <v>1</v>
+      </c>
+      <c r="AQ106">
+        <v>1.33</v>
+      </c>
+      <c r="AR106">
+        <v>1.4</v>
+      </c>
+      <c r="AS106">
+        <v>1.12</v>
+      </c>
+      <c r="AT106">
+        <v>2.52</v>
+      </c>
+      <c r="AU106">
+        <v>4</v>
+      </c>
+      <c r="AV106">
+        <v>8</v>
+      </c>
+      <c r="AW106">
+        <v>8</v>
+      </c>
+      <c r="AX106">
+        <v>7</v>
+      </c>
+      <c r="AY106">
+        <v>14</v>
+      </c>
+      <c r="AZ106">
+        <v>16</v>
+      </c>
+      <c r="BA106">
+        <v>2</v>
+      </c>
+      <c r="BB106">
+        <v>2</v>
+      </c>
+      <c r="BC106">
+        <v>4</v>
+      </c>
+      <c r="BD106">
+        <v>2.75</v>
+      </c>
+      <c r="BE106">
+        <v>6.75</v>
+      </c>
+      <c r="BF106">
+        <v>1.53</v>
+      </c>
+      <c r="BG106">
+        <v>1.26</v>
+      </c>
+      <c r="BH106">
+        <v>3.4</v>
+      </c>
+      <c r="BI106">
+        <v>1.46</v>
+      </c>
+      <c r="BJ106">
+        <v>2.5</v>
+      </c>
+      <c r="BK106">
+        <v>1.74</v>
+      </c>
+      <c r="BL106">
+        <v>1.96</v>
+      </c>
+      <c r="BM106">
+        <v>2.17</v>
+      </c>
+      <c r="BN106">
+        <v>1.6</v>
+      </c>
+      <c r="BO106">
+        <v>2.75</v>
+      </c>
+      <c r="BP106">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7452362</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45704.58333333334</v>
+      </c>
+      <c r="F107">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>165</v>
+      </c>
+      <c r="P107" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q107">
+        <v>1.91</v>
+      </c>
+      <c r="R107">
+        <v>2.5</v>
+      </c>
+      <c r="S107">
+        <v>6.5</v>
+      </c>
+      <c r="T107">
+        <v>1.3</v>
+      </c>
+      <c r="U107">
+        <v>3.4</v>
+      </c>
+      <c r="V107">
+        <v>2.38</v>
+      </c>
+      <c r="W107">
+        <v>1.53</v>
+      </c>
+      <c r="X107">
+        <v>6</v>
+      </c>
+      <c r="Y107">
+        <v>1.13</v>
+      </c>
+      <c r="Z107">
+        <v>1.39</v>
+      </c>
+      <c r="AA107">
+        <v>5</v>
+      </c>
+      <c r="AB107">
+        <v>6.7</v>
+      </c>
+      <c r="AC107">
+        <v>1</v>
+      </c>
+      <c r="AD107">
+        <v>12</v>
+      </c>
+      <c r="AE107">
+        <v>1.16</v>
+      </c>
+      <c r="AF107">
+        <v>4.1</v>
+      </c>
+      <c r="AG107">
+        <v>1.53</v>
+      </c>
+      <c r="AH107">
+        <v>2.25</v>
+      </c>
+      <c r="AI107">
+        <v>1.8</v>
+      </c>
+      <c r="AJ107">
+        <v>1.95</v>
+      </c>
+      <c r="AK107">
+        <v>1.1</v>
+      </c>
+      <c r="AL107">
+        <v>1.18</v>
+      </c>
+      <c r="AM107">
+        <v>2.86</v>
+      </c>
+      <c r="AN107">
+        <v>2.63</v>
+      </c>
+      <c r="AO107">
+        <v>0.38</v>
+      </c>
+      <c r="AP107">
+        <v>2.67</v>
+      </c>
+      <c r="AQ107">
+        <v>0.33</v>
+      </c>
+      <c r="AR107">
+        <v>1.68</v>
+      </c>
+      <c r="AS107">
+        <v>1.17</v>
+      </c>
+      <c r="AT107">
+        <v>2.85</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>0</v>
+      </c>
+      <c r="AW107">
+        <v>8</v>
+      </c>
+      <c r="AX107">
+        <v>15</v>
+      </c>
+      <c r="AY107">
+        <v>15</v>
+      </c>
+      <c r="AZ107">
+        <v>16</v>
+      </c>
+      <c r="BA107">
+        <v>2</v>
+      </c>
+      <c r="BB107">
+        <v>4</v>
+      </c>
+      <c r="BC107">
+        <v>6</v>
+      </c>
+      <c r="BD107">
+        <v>1.29</v>
+      </c>
+      <c r="BE107">
+        <v>8</v>
+      </c>
+      <c r="BF107">
+        <v>3.9</v>
+      </c>
+      <c r="BG107">
+        <v>1.16</v>
+      </c>
+      <c r="BH107">
+        <v>4.3</v>
+      </c>
+      <c r="BI107">
+        <v>1.3</v>
+      </c>
+      <c r="BJ107">
+        <v>3.05</v>
+      </c>
+      <c r="BK107">
+        <v>1.52</v>
+      </c>
+      <c r="BL107">
+        <v>2.33</v>
+      </c>
+      <c r="BM107">
+        <v>1.81</v>
+      </c>
+      <c r="BN107">
+        <v>1.88</v>
+      </c>
+      <c r="BO107">
+        <v>2.23</v>
+      </c>
+      <c r="BP107">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -699,6 +699,9 @@
   <si>
     <t>['24', '26', '45+2', '51']</t>
   </si>
+  <si>
+    <t>['23', '29']</t>
+  </si>
 </sst>
 </file>
 
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2426,7 +2429,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3041,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ10">
         <v>0.7</v>
@@ -5307,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ21">
         <v>1.25</v>
@@ -5928,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
         <v>1.85</v>
@@ -6543,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27">
         <v>0.78</v>
@@ -8194,7 +8197,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR35">
         <v>1.81</v>
@@ -9839,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ43">
         <v>0.67</v>
@@ -10254,7 +10257,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
         <v>1.88</v>
@@ -11693,7 +11696,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -13344,7 +13347,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ60">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
         <v>1.56</v>
@@ -14165,7 +14168,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ64">
         <v>0.33</v>
@@ -14786,7 +14789,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.23</v>
@@ -16434,7 +16437,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR75">
         <v>1.81</v>
@@ -17255,7 +17258,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ79">
         <v>0.88</v>
@@ -19524,7 +19527,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR90">
         <v>1.66</v>
@@ -20139,7 +20142,7 @@
         <v>0.14</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ93">
         <v>0.44</v>
@@ -23102,6 +23105,212 @@
       </c>
       <c r="BP107">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7452361</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45705.625</v>
+      </c>
+      <c r="F108">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" t="s">
+        <v>79</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>2</v>
+      </c>
+      <c r="N108">
+        <v>3</v>
+      </c>
+      <c r="O108" t="s">
+        <v>129</v>
+      </c>
+      <c r="P108" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q108">
+        <v>3.6</v>
+      </c>
+      <c r="R108">
+        <v>2.2</v>
+      </c>
+      <c r="S108">
+        <v>2.88</v>
+      </c>
+      <c r="T108">
+        <v>1.36</v>
+      </c>
+      <c r="U108">
+        <v>3</v>
+      </c>
+      <c r="V108">
+        <v>2.63</v>
+      </c>
+      <c r="W108">
+        <v>1.44</v>
+      </c>
+      <c r="X108">
+        <v>7</v>
+      </c>
+      <c r="Y108">
+        <v>1.1</v>
+      </c>
+      <c r="Z108">
+        <v>3.34</v>
+      </c>
+      <c r="AA108">
+        <v>3.53</v>
+      </c>
+      <c r="AB108">
+        <v>2.05</v>
+      </c>
+      <c r="AC108">
+        <v>1.03</v>
+      </c>
+      <c r="AD108">
+        <v>12.5</v>
+      </c>
+      <c r="AE108">
+        <v>1.25</v>
+      </c>
+      <c r="AF108">
+        <v>3.95</v>
+      </c>
+      <c r="AG108">
+        <v>1.77</v>
+      </c>
+      <c r="AH108">
+        <v>1.98</v>
+      </c>
+      <c r="AI108">
+        <v>1.62</v>
+      </c>
+      <c r="AJ108">
+        <v>2.2</v>
+      </c>
+      <c r="AK108">
+        <v>1.66</v>
+      </c>
+      <c r="AL108">
+        <v>1.25</v>
+      </c>
+      <c r="AM108">
+        <v>1.38</v>
+      </c>
+      <c r="AN108">
+        <v>1.75</v>
+      </c>
+      <c r="AO108">
+        <v>1.5</v>
+      </c>
+      <c r="AP108">
+        <v>1.56</v>
+      </c>
+      <c r="AQ108">
+        <v>1.67</v>
+      </c>
+      <c r="AR108">
+        <v>1.51</v>
+      </c>
+      <c r="AS108">
+        <v>1.65</v>
+      </c>
+      <c r="AT108">
+        <v>3.16</v>
+      </c>
+      <c r="AU108">
+        <v>3</v>
+      </c>
+      <c r="AV108">
+        <v>4</v>
+      </c>
+      <c r="AW108">
+        <v>7</v>
+      </c>
+      <c r="AX108">
+        <v>7</v>
+      </c>
+      <c r="AY108">
+        <v>13</v>
+      </c>
+      <c r="AZ108">
+        <v>16</v>
+      </c>
+      <c r="BA108">
+        <v>2</v>
+      </c>
+      <c r="BB108">
+        <v>2</v>
+      </c>
+      <c r="BC108">
+        <v>4</v>
+      </c>
+      <c r="BD108">
+        <v>2.08</v>
+      </c>
+      <c r="BE108">
+        <v>6.5</v>
+      </c>
+      <c r="BF108">
+        <v>1.9</v>
+      </c>
+      <c r="BG108">
+        <v>1.23</v>
+      </c>
+      <c r="BH108">
+        <v>3.65</v>
+      </c>
+      <c r="BI108">
+        <v>1.41</v>
+      </c>
+      <c r="BJ108">
+        <v>2.65</v>
+      </c>
+      <c r="BK108">
+        <v>1.66</v>
+      </c>
+      <c r="BL108">
+        <v>2.07</v>
+      </c>
+      <c r="BM108">
+        <v>2.02</v>
+      </c>
+      <c r="BN108">
+        <v>1.68</v>
+      </c>
+      <c r="BO108">
+        <v>2.55</v>
+      </c>
+      <c r="BP108">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1062,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2017,7 +2017,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ5">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ7">
         <v>1.67</v>
@@ -4489,7 +4489,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR17">
         <v>1.41</v>
@@ -4692,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18">
         <v>1.33</v>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -8403,7 +8403,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR36">
         <v>1.69</v>
@@ -8812,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ38">
         <v>0.44</v>
@@ -11081,7 +11081,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ49">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR49">
         <v>1.79</v>
@@ -11902,7 +11902,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12523,7 +12523,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ56">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -13138,7 +13138,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -15198,7 +15198,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ69">
         <v>0.7</v>
@@ -15407,7 +15407,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ70">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR70">
         <v>1.17</v>
@@ -17467,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR80">
         <v>1.37</v>
@@ -18909,7 +18909,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ87">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19112,7 +19112,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ88">
         <v>0.67</v>
@@ -21378,7 +21378,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ99">
         <v>0.78</v>
@@ -21587,7 +21587,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ100">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -23311,6 +23311,212 @@
       </c>
       <c r="BP108">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7452365</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45709.625</v>
+      </c>
+      <c r="F109">
+        <v>19</v>
+      </c>
+      <c r="G109" t="s">
+        <v>75</v>
+      </c>
+      <c r="H109" t="s">
+        <v>77</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109" t="s">
+        <v>87</v>
+      </c>
+      <c r="P109" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q109">
+        <v>3.75</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>2.75</v>
+      </c>
+      <c r="T109">
+        <v>1.36</v>
+      </c>
+      <c r="U109">
+        <v>3</v>
+      </c>
+      <c r="V109">
+        <v>2.75</v>
+      </c>
+      <c r="W109">
+        <v>1.4</v>
+      </c>
+      <c r="X109">
+        <v>7</v>
+      </c>
+      <c r="Y109">
+        <v>1.1</v>
+      </c>
+      <c r="Z109">
+        <v>3.56</v>
+      </c>
+      <c r="AA109">
+        <v>3.56</v>
+      </c>
+      <c r="AB109">
+        <v>1.97</v>
+      </c>
+      <c r="AC109">
+        <v>1.05</v>
+      </c>
+      <c r="AD109">
+        <v>9.5</v>
+      </c>
+      <c r="AE109">
+        <v>1.25</v>
+      </c>
+      <c r="AF109">
+        <v>3.7</v>
+      </c>
+      <c r="AG109">
+        <v>1.79</v>
+      </c>
+      <c r="AH109">
+        <v>1.95</v>
+      </c>
+      <c r="AI109">
+        <v>1.7</v>
+      </c>
+      <c r="AJ109">
+        <v>2.05</v>
+      </c>
+      <c r="AK109">
+        <v>1.77</v>
+      </c>
+      <c r="AL109">
+        <v>1.28</v>
+      </c>
+      <c r="AM109">
+        <v>1.28</v>
+      </c>
+      <c r="AN109">
+        <v>0.78</v>
+      </c>
+      <c r="AO109">
+        <v>1.78</v>
+      </c>
+      <c r="AP109">
+        <v>0.8</v>
+      </c>
+      <c r="AQ109">
+        <v>1.7</v>
+      </c>
+      <c r="AR109">
+        <v>1.19</v>
+      </c>
+      <c r="AS109">
+        <v>1.33</v>
+      </c>
+      <c r="AT109">
+        <v>2.52</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>4</v>
+      </c>
+      <c r="AW109">
+        <v>11</v>
+      </c>
+      <c r="AX109">
+        <v>8</v>
+      </c>
+      <c r="AY109">
+        <v>17</v>
+      </c>
+      <c r="AZ109">
+        <v>14</v>
+      </c>
+      <c r="BA109">
+        <v>3</v>
+      </c>
+      <c r="BB109">
+        <v>8</v>
+      </c>
+      <c r="BC109">
+        <v>11</v>
+      </c>
+      <c r="BD109">
+        <v>2.4</v>
+      </c>
+      <c r="BE109">
+        <v>6.75</v>
+      </c>
+      <c r="BF109">
+        <v>1.68</v>
+      </c>
+      <c r="BG109">
+        <v>1.26</v>
+      </c>
+      <c r="BH109">
+        <v>3.4</v>
+      </c>
+      <c r="BI109">
+        <v>1.44</v>
+      </c>
+      <c r="BJ109">
+        <v>2.55</v>
+      </c>
+      <c r="BK109">
+        <v>1.72</v>
+      </c>
+      <c r="BL109">
+        <v>1.97</v>
+      </c>
+      <c r="BM109">
+        <v>2.14</v>
+      </c>
+      <c r="BN109">
+        <v>1.62</v>
+      </c>
+      <c r="BO109">
+        <v>2.65</v>
+      </c>
+      <c r="BP109">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,18 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['25', '27', '58']</t>
+  </si>
+  <si>
+    <t>['20', '48', '51', '71']</t>
+  </si>
+  <si>
+    <t>['50', '77']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -701,6 +713,12 @@
   </si>
   <si>
     <t>['23', '29']</t>
+  </si>
+  <si>
+    <t>['22', '84']</t>
+  </si>
+  <si>
+    <t>['62', '68']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1396,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1602,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1811,7 +1829,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ4">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1936,7 +1954,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2014,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ5">
         <v>1.7</v>
@@ -2142,7 +2160,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2223,7 +2241,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2348,7 +2366,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2554,7 +2572,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2760,7 +2778,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2838,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR9">
         <v>1.96</v>
@@ -3172,7 +3190,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3378,7 +3396,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3456,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3868,10 +3886,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ14">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR14">
         <v>1.77</v>
@@ -4077,7 +4095,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4408,7 +4426,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4486,7 +4504,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ17">
         <v>1.7</v>
@@ -4614,7 +4632,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4695,7 +4713,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
         <v>1.15</v>
@@ -4820,7 +4838,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -4898,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ19">
         <v>0.88</v>
@@ -5232,7 +5250,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5516,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ22">
         <v>0.33</v>
@@ -5644,7 +5662,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5850,7 +5868,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6056,7 +6074,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6137,7 +6155,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR25">
         <v>0.91</v>
@@ -6262,7 +6280,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6343,7 +6361,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
         <v>1.11</v>
@@ -6468,7 +6486,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6549,7 +6567,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR27">
         <v>1.35</v>
@@ -6674,7 +6692,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6880,7 +6898,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -6958,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ29">
         <v>0.7</v>
@@ -7086,7 +7104,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7167,7 +7185,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR30">
         <v>1.16</v>
@@ -7370,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ31">
         <v>0.44</v>
@@ -7498,7 +7516,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7704,7 +7722,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7785,7 +7803,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ33">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR33">
         <v>1.8</v>
@@ -7910,7 +7928,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -7988,7 +8006,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ34">
         <v>1.25</v>
@@ -8116,7 +8134,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8194,7 +8212,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ35">
         <v>1.67</v>
@@ -8322,7 +8340,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8940,7 +8958,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9018,7 +9036,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ39">
         <v>0.88</v>
@@ -9146,7 +9164,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9224,10 +9242,10 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR40">
         <v>1.87</v>
@@ -9352,7 +9370,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9558,7 +9576,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9639,7 +9657,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ42">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR42">
         <v>1.27</v>
@@ -9845,7 +9863,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ43">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -9970,7 +9988,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10176,7 +10194,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10382,7 +10400,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10460,7 +10478,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ46">
         <v>1.25</v>
@@ -10588,7 +10606,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10666,7 +10684,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ47">
         <v>0.7</v>
@@ -10875,7 +10893,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR48">
         <v>1.96</v>
@@ -11078,7 +11096,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ49">
         <v>1.7</v>
@@ -11206,7 +11224,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11618,7 +11636,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11699,7 +11717,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR52">
         <v>1.41</v>
@@ -12030,7 +12048,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12111,7 +12129,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12314,10 +12332,10 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ55">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR55">
         <v>1.59</v>
@@ -12442,7 +12460,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12520,7 +12538,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ56">
         <v>1.7</v>
@@ -12935,7 +12953,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ58">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR58">
         <v>1.05</v>
@@ -13060,7 +13078,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13266,7 +13284,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13344,7 +13362,7 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ60">
         <v>1.67</v>
@@ -13472,7 +13490,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13550,10 +13568,10 @@
         <v>1.6</v>
       </c>
       <c r="AP61">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR61">
         <v>1.74</v>
@@ -13678,7 +13696,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13756,10 +13774,10 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ62">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR62">
         <v>1.34</v>
@@ -13884,7 +13902,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14090,7 +14108,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14296,7 +14314,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14583,7 +14601,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.84</v>
@@ -14708,7 +14726,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14914,7 +14932,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -14992,7 +15010,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ68">
         <v>0.44</v>
@@ -15326,7 +15344,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15532,7 +15550,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15610,7 +15628,7 @@
         <v>1.6</v>
       </c>
       <c r="AP71">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -15738,7 +15756,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15819,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16022,10 +16040,10 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR73">
         <v>1.58</v>
@@ -16231,7 +16249,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ74">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16640,7 +16658,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ76">
         <v>0.33</v>
@@ -16768,7 +16786,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16849,7 +16867,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ77">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR77">
         <v>1.44</v>
@@ -17386,7 +17404,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17592,7 +17610,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17673,7 +17691,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR81">
         <v>1.78</v>
@@ -17798,7 +17816,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -17876,7 +17894,7 @@
         <v>0.86</v>
       </c>
       <c r="AP82">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ82">
         <v>0.7</v>
@@ -18004,7 +18022,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18082,7 +18100,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ83">
         <v>0.33</v>
@@ -18210,7 +18228,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18416,7 +18434,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18494,7 +18512,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ85">
         <v>1.25</v>
@@ -18700,10 +18718,10 @@
         <v>0.43</v>
       </c>
       <c r="AP86">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ86">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19034,7 +19052,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19115,7 +19133,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ88">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR88">
         <v>1.19</v>
@@ -19321,7 +19339,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19446,7 +19464,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19524,7 +19542,7 @@
         <v>1.57</v>
       </c>
       <c r="AP90">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90">
         <v>1.67</v>
@@ -19652,7 +19670,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19936,7 +19954,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ92">
         <v>1.33</v>
@@ -20476,7 +20494,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20557,7 +20575,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -20682,7 +20700,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20760,7 +20778,7 @@
         <v>0.43</v>
       </c>
       <c r="AP96">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ96">
         <v>0.33</v>
@@ -21175,7 +21193,7 @@
         <v>2</v>
       </c>
       <c r="AQ98">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR98">
         <v>1.56</v>
@@ -21300,7 +21318,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21381,7 +21399,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ99">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21506,7 +21524,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21712,7 +21730,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21790,10 +21808,10 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AQ101">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -21918,7 +21936,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22202,7 +22220,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ103">
         <v>0.88</v>
@@ -22330,7 +22348,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22536,7 +22554,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22742,7 +22760,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23154,7 +23172,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23517,6 +23535,830 @@
       </c>
       <c r="BP109">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7452364</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F110">
+        <v>19</v>
+      </c>
+      <c r="G110" t="s">
+        <v>71</v>
+      </c>
+      <c r="H110" t="s">
+        <v>76</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110">
+        <v>3</v>
+      </c>
+      <c r="M110">
+        <v>2</v>
+      </c>
+      <c r="N110">
+        <v>5</v>
+      </c>
+      <c r="O110" t="s">
+        <v>166</v>
+      </c>
+      <c r="P110" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q110">
+        <v>1.83</v>
+      </c>
+      <c r="R110">
+        <v>2.63</v>
+      </c>
+      <c r="S110">
+        <v>6.5</v>
+      </c>
+      <c r="T110">
+        <v>1.25</v>
+      </c>
+      <c r="U110">
+        <v>3.75</v>
+      </c>
+      <c r="V110">
+        <v>2.2</v>
+      </c>
+      <c r="W110">
+        <v>1.62</v>
+      </c>
+      <c r="X110">
+        <v>5</v>
+      </c>
+      <c r="Y110">
+        <v>1.17</v>
+      </c>
+      <c r="Z110">
+        <v>1.43</v>
+      </c>
+      <c r="AA110">
+        <v>4.8</v>
+      </c>
+      <c r="AB110">
+        <v>6.2</v>
+      </c>
+      <c r="AC110">
+        <v>1.01</v>
+      </c>
+      <c r="AD110">
+        <v>17</v>
+      </c>
+      <c r="AE110">
+        <v>1.15</v>
+      </c>
+      <c r="AF110">
+        <v>5.25</v>
+      </c>
+      <c r="AG110">
+        <v>1.47</v>
+      </c>
+      <c r="AH110">
+        <v>2.57</v>
+      </c>
+      <c r="AI110">
+        <v>1.7</v>
+      </c>
+      <c r="AJ110">
+        <v>2.05</v>
+      </c>
+      <c r="AK110">
+        <v>1.09</v>
+      </c>
+      <c r="AL110">
+        <v>1.13</v>
+      </c>
+      <c r="AM110">
+        <v>2.85</v>
+      </c>
+      <c r="AN110">
+        <v>2.11</v>
+      </c>
+      <c r="AO110">
+        <v>0.78</v>
+      </c>
+      <c r="AP110">
+        <v>2.2</v>
+      </c>
+      <c r="AQ110">
+        <v>0.7</v>
+      </c>
+      <c r="AR110">
+        <v>1.63</v>
+      </c>
+      <c r="AS110">
+        <v>1.28</v>
+      </c>
+      <c r="AT110">
+        <v>2.91</v>
+      </c>
+      <c r="AU110">
+        <v>11</v>
+      </c>
+      <c r="AV110">
+        <v>4</v>
+      </c>
+      <c r="AW110">
+        <v>11</v>
+      </c>
+      <c r="AX110">
+        <v>7</v>
+      </c>
+      <c r="AY110">
+        <v>24</v>
+      </c>
+      <c r="AZ110">
+        <v>16</v>
+      </c>
+      <c r="BA110">
+        <v>1</v>
+      </c>
+      <c r="BB110">
+        <v>6</v>
+      </c>
+      <c r="BC110">
+        <v>7</v>
+      </c>
+      <c r="BD110">
+        <v>1.3</v>
+      </c>
+      <c r="BE110">
+        <v>7.5</v>
+      </c>
+      <c r="BF110">
+        <v>3.8</v>
+      </c>
+      <c r="BG110">
+        <v>1.29</v>
+      </c>
+      <c r="BH110">
+        <v>3.2</v>
+      </c>
+      <c r="BI110">
+        <v>1.49</v>
+      </c>
+      <c r="BJ110">
+        <v>2.4</v>
+      </c>
+      <c r="BK110">
+        <v>1.8</v>
+      </c>
+      <c r="BL110">
+        <v>1.88</v>
+      </c>
+      <c r="BM110">
+        <v>2.23</v>
+      </c>
+      <c r="BN110">
+        <v>1.56</v>
+      </c>
+      <c r="BO110">
+        <v>2.9</v>
+      </c>
+      <c r="BP110">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7452368</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="s">
+        <v>70</v>
+      </c>
+      <c r="H111" t="s">
+        <v>78</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>4</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>167</v>
+      </c>
+      <c r="P111" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q111">
+        <v>2</v>
+      </c>
+      <c r="R111">
+        <v>2.4</v>
+      </c>
+      <c r="S111">
+        <v>6</v>
+      </c>
+      <c r="T111">
+        <v>1.3</v>
+      </c>
+      <c r="U111">
+        <v>3.4</v>
+      </c>
+      <c r="V111">
+        <v>2.5</v>
+      </c>
+      <c r="W111">
+        <v>1.5</v>
+      </c>
+      <c r="X111">
+        <v>6</v>
+      </c>
+      <c r="Y111">
+        <v>1.13</v>
+      </c>
+      <c r="Z111">
+        <v>1.51</v>
+      </c>
+      <c r="AA111">
+        <v>4.3</v>
+      </c>
+      <c r="AB111">
+        <v>5.7</v>
+      </c>
+      <c r="AC111">
+        <v>1.04</v>
+      </c>
+      <c r="AD111">
+        <v>10</v>
+      </c>
+      <c r="AE111">
+        <v>1.2</v>
+      </c>
+      <c r="AF111">
+        <v>4.33</v>
+      </c>
+      <c r="AG111">
+        <v>1.61</v>
+      </c>
+      <c r="AH111">
+        <v>2.17</v>
+      </c>
+      <c r="AI111">
+        <v>1.75</v>
+      </c>
+      <c r="AJ111">
+        <v>2</v>
+      </c>
+      <c r="AK111">
+        <v>1.12</v>
+      </c>
+      <c r="AL111">
+        <v>1.17</v>
+      </c>
+      <c r="AM111">
+        <v>2.45</v>
+      </c>
+      <c r="AN111">
+        <v>2.11</v>
+      </c>
+      <c r="AO111">
+        <v>0.67</v>
+      </c>
+      <c r="AP111">
+        <v>2.2</v>
+      </c>
+      <c r="AQ111">
+        <v>0.6</v>
+      </c>
+      <c r="AR111">
+        <v>1.71</v>
+      </c>
+      <c r="AS111">
+        <v>1.23</v>
+      </c>
+      <c r="AT111">
+        <v>2.94</v>
+      </c>
+      <c r="AU111">
+        <v>13</v>
+      </c>
+      <c r="AV111">
+        <v>3</v>
+      </c>
+      <c r="AW111">
+        <v>11</v>
+      </c>
+      <c r="AX111">
+        <v>0</v>
+      </c>
+      <c r="AY111">
+        <v>26</v>
+      </c>
+      <c r="AZ111">
+        <v>3</v>
+      </c>
+      <c r="BA111">
+        <v>7</v>
+      </c>
+      <c r="BB111">
+        <v>2</v>
+      </c>
+      <c r="BC111">
+        <v>9</v>
+      </c>
+      <c r="BD111">
+        <v>1.33</v>
+      </c>
+      <c r="BE111">
+        <v>7.5</v>
+      </c>
+      <c r="BF111">
+        <v>3.55</v>
+      </c>
+      <c r="BG111">
+        <v>1.28</v>
+      </c>
+      <c r="BH111">
+        <v>3.2</v>
+      </c>
+      <c r="BI111">
+        <v>1.48</v>
+      </c>
+      <c r="BJ111">
+        <v>2.45</v>
+      </c>
+      <c r="BK111">
+        <v>1.78</v>
+      </c>
+      <c r="BL111">
+        <v>1.9</v>
+      </c>
+      <c r="BM111">
+        <v>2.23</v>
+      </c>
+      <c r="BN111">
+        <v>1.57</v>
+      </c>
+      <c r="BO111">
+        <v>2.8</v>
+      </c>
+      <c r="BP111">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7452366</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45711.5</v>
+      </c>
+      <c r="F112">
+        <v>19</v>
+      </c>
+      <c r="G112" t="s">
+        <v>73</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>2</v>
+      </c>
+      <c r="M112">
+        <v>2</v>
+      </c>
+      <c r="N112">
+        <v>4</v>
+      </c>
+      <c r="O112" t="s">
+        <v>168</v>
+      </c>
+      <c r="P112" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q112">
+        <v>5.5</v>
+      </c>
+      <c r="R112">
+        <v>2.4</v>
+      </c>
+      <c r="S112">
+        <v>2.05</v>
+      </c>
+      <c r="T112">
+        <v>1.3</v>
+      </c>
+      <c r="U112">
+        <v>3.4</v>
+      </c>
+      <c r="V112">
+        <v>2.5</v>
+      </c>
+      <c r="W112">
+        <v>1.5</v>
+      </c>
+      <c r="X112">
+        <v>6</v>
+      </c>
+      <c r="Y112">
+        <v>1.13</v>
+      </c>
+      <c r="Z112">
+        <v>6.3</v>
+      </c>
+      <c r="AA112">
+        <v>4.1</v>
+      </c>
+      <c r="AB112">
+        <v>1.51</v>
+      </c>
+      <c r="AC112">
+        <v>1.04</v>
+      </c>
+      <c r="AD112">
+        <v>10</v>
+      </c>
+      <c r="AE112">
+        <v>1.2</v>
+      </c>
+      <c r="AF112">
+        <v>4.33</v>
+      </c>
+      <c r="AG112">
+        <v>1.61</v>
+      </c>
+      <c r="AH112">
+        <v>2.05</v>
+      </c>
+      <c r="AI112">
+        <v>1.7</v>
+      </c>
+      <c r="AJ112">
+        <v>2.05</v>
+      </c>
+      <c r="AK112">
+        <v>2.4</v>
+      </c>
+      <c r="AL112">
+        <v>1.18</v>
+      </c>
+      <c r="AM112">
+        <v>1.13</v>
+      </c>
+      <c r="AN112">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO112">
+        <v>1.33</v>
+      </c>
+      <c r="AP112">
+        <v>0.6</v>
+      </c>
+      <c r="AQ112">
+        <v>1.3</v>
+      </c>
+      <c r="AR112">
+        <v>1.42</v>
+      </c>
+      <c r="AS112">
+        <v>1.77</v>
+      </c>
+      <c r="AT112">
+        <v>3.19</v>
+      </c>
+      <c r="AU112">
+        <v>5</v>
+      </c>
+      <c r="AV112">
+        <v>6</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>10</v>
+      </c>
+      <c r="AY112">
+        <v>14</v>
+      </c>
+      <c r="AZ112">
+        <v>16</v>
+      </c>
+      <c r="BA112">
+        <v>5</v>
+      </c>
+      <c r="BB112">
+        <v>6</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>3.3</v>
+      </c>
+      <c r="BE112">
+        <v>7</v>
+      </c>
+      <c r="BF112">
+        <v>1.4</v>
+      </c>
+      <c r="BG112">
+        <v>1.27</v>
+      </c>
+      <c r="BH112">
+        <v>3.3</v>
+      </c>
+      <c r="BI112">
+        <v>1.48</v>
+      </c>
+      <c r="BJ112">
+        <v>2.43</v>
+      </c>
+      <c r="BK112">
+        <v>1.77</v>
+      </c>
+      <c r="BL112">
+        <v>1.92</v>
+      </c>
+      <c r="BM112">
+        <v>2.18</v>
+      </c>
+      <c r="BN112">
+        <v>1.58</v>
+      </c>
+      <c r="BO112">
+        <v>2.8</v>
+      </c>
+      <c r="BP112">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7452363</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45711.58333333334</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="G113" t="s">
+        <v>79</v>
+      </c>
+      <c r="H113" t="s">
+        <v>81</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>169</v>
+      </c>
+      <c r="P113" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q113">
+        <v>2.6</v>
+      </c>
+      <c r="R113">
+        <v>2.25</v>
+      </c>
+      <c r="S113">
+        <v>4</v>
+      </c>
+      <c r="T113">
+        <v>1.33</v>
+      </c>
+      <c r="U113">
+        <v>3.25</v>
+      </c>
+      <c r="V113">
+        <v>2.63</v>
+      </c>
+      <c r="W113">
+        <v>1.44</v>
+      </c>
+      <c r="X113">
+        <v>6.5</v>
+      </c>
+      <c r="Y113">
+        <v>1.11</v>
+      </c>
+      <c r="Z113">
+        <v>1.92</v>
+      </c>
+      <c r="AA113">
+        <v>3.65</v>
+      </c>
+      <c r="AB113">
+        <v>3.65</v>
+      </c>
+      <c r="AC113">
+        <v>1.04</v>
+      </c>
+      <c r="AD113">
+        <v>10</v>
+      </c>
+      <c r="AE113">
+        <v>1.22</v>
+      </c>
+      <c r="AF113">
+        <v>4.2</v>
+      </c>
+      <c r="AG113">
+        <v>1.67</v>
+      </c>
+      <c r="AH113">
+        <v>2.1</v>
+      </c>
+      <c r="AI113">
+        <v>1.62</v>
+      </c>
+      <c r="AJ113">
+        <v>2.2</v>
+      </c>
+      <c r="AK113">
+        <v>1.28</v>
+      </c>
+      <c r="AL113">
+        <v>1.22</v>
+      </c>
+      <c r="AM113">
+        <v>1.77</v>
+      </c>
+      <c r="AN113">
+        <v>2.33</v>
+      </c>
+      <c r="AO113">
+        <v>1.33</v>
+      </c>
+      <c r="AP113">
+        <v>2.4</v>
+      </c>
+      <c r="AQ113">
+        <v>1.2</v>
+      </c>
+      <c r="AR113">
+        <v>1.93</v>
+      </c>
+      <c r="AS113">
+        <v>1.54</v>
+      </c>
+      <c r="AT113">
+        <v>3.47</v>
+      </c>
+      <c r="AU113">
+        <v>8</v>
+      </c>
+      <c r="AV113">
+        <v>4</v>
+      </c>
+      <c r="AW113">
+        <v>8</v>
+      </c>
+      <c r="AX113">
+        <v>8</v>
+      </c>
+      <c r="AY113">
+        <v>20</v>
+      </c>
+      <c r="AZ113">
+        <v>13</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>6</v>
+      </c>
+      <c r="BC113">
+        <v>10</v>
+      </c>
+      <c r="BD113">
+        <v>1.74</v>
+      </c>
+      <c r="BE113">
+        <v>6.4</v>
+      </c>
+      <c r="BF113">
+        <v>2.32</v>
+      </c>
+      <c r="BG113">
+        <v>1.33</v>
+      </c>
+      <c r="BH113">
+        <v>2.95</v>
+      </c>
+      <c r="BI113">
+        <v>1.56</v>
+      </c>
+      <c r="BJ113">
+        <v>2.23</v>
+      </c>
+      <c r="BK113">
+        <v>1.91</v>
+      </c>
+      <c r="BL113">
+        <v>1.77</v>
+      </c>
+      <c r="BM113">
+        <v>2.4</v>
+      </c>
+      <c r="BN113">
+        <v>1.49</v>
+      </c>
+      <c r="BO113">
+        <v>3.15</v>
+      </c>
+      <c r="BP113">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,9 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -719,6 +722,9 @@
   </si>
   <si>
     <t>['62', '68']</t>
+  </si>
+  <si>
+    <t>['30', '37', '83', '86']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1954,7 +1960,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2160,7 +2166,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2238,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6">
         <v>1.3</v>
@@ -2366,7 +2372,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2572,7 +2578,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2778,7 +2784,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3190,7 +3196,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3271,7 +3277,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3396,7 +3402,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4426,7 +4432,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4632,7 +4638,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4838,7 +4844,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5250,7 +5256,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5331,7 +5337,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ21">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5662,7 +5668,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5868,7 +5874,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6074,7 +6080,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6152,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ25">
         <v>0.6</v>
@@ -6280,7 +6286,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6486,7 +6492,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6692,7 +6698,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6898,7 +6904,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7104,7 +7110,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7516,7 +7522,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7722,7 +7728,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7928,7 +7934,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8009,7 +8015,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ34">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8134,7 +8140,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8340,7 +8346,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8624,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ37">
         <v>0.33</v>
@@ -8958,7 +8964,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9164,7 +9170,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9370,7 +9376,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9576,7 +9582,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9988,7 +9994,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10194,7 +10200,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10400,7 +10406,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10481,7 +10487,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10606,7 +10612,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11224,7 +11230,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11302,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ50">
         <v>0.88</v>
@@ -11636,7 +11642,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12048,7 +12054,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12460,7 +12466,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13078,7 +13084,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13159,7 +13165,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR59">
         <v>1.04</v>
@@ -13284,7 +13290,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13490,7 +13496,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13696,7 +13702,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13902,7 +13908,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14108,7 +14114,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14314,7 +14320,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14392,7 +14398,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ65">
         <v>1.33</v>
@@ -14726,7 +14732,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14932,7 +14938,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15344,7 +15350,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15550,7 +15556,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15631,7 +15637,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ71">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -15756,7 +15762,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16786,7 +16792,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16864,7 +16870,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ77">
         <v>0.7</v>
@@ -17404,7 +17410,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17610,7 +17616,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17816,7 +17822,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18022,7 +18028,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18228,7 +18234,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18434,7 +18440,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18515,7 +18521,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -19052,7 +19058,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19336,7 +19342,7 @@
         <v>1.29</v>
       </c>
       <c r="AP89">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ89">
         <v>1.2</v>
@@ -19464,7 +19470,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19670,7 +19676,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -20494,7 +20500,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20700,7 +20706,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20987,7 +20993,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ97">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR97">
         <v>1.78</v>
@@ -21318,7 +21324,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21524,7 +21530,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21602,7 +21608,7 @@
         <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ100">
         <v>1.7</v>
@@ -21730,7 +21736,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21936,7 +21942,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22348,7 +22354,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22554,7 +22560,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22760,7 +22766,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23172,7 +23178,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23584,7 +23590,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -23996,7 +24002,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24359,6 +24365,212 @@
       </c>
       <c r="BP113">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7452367</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45712.625</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>74</v>
+      </c>
+      <c r="H114" t="s">
+        <v>72</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>4</v>
+      </c>
+      <c r="N114">
+        <v>5</v>
+      </c>
+      <c r="O114" t="s">
+        <v>170</v>
+      </c>
+      <c r="P114" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q114">
+        <v>2.88</v>
+      </c>
+      <c r="R114">
+        <v>2.3</v>
+      </c>
+      <c r="S114">
+        <v>3.5</v>
+      </c>
+      <c r="T114">
+        <v>1.33</v>
+      </c>
+      <c r="U114">
+        <v>3.25</v>
+      </c>
+      <c r="V114">
+        <v>2.5</v>
+      </c>
+      <c r="W114">
+        <v>1.5</v>
+      </c>
+      <c r="X114">
+        <v>6.5</v>
+      </c>
+      <c r="Y114">
+        <v>1.11</v>
+      </c>
+      <c r="Z114">
+        <v>2.22</v>
+      </c>
+      <c r="AA114">
+        <v>3.57</v>
+      </c>
+      <c r="AB114">
+        <v>2.96</v>
+      </c>
+      <c r="AC114">
+        <v>1.02</v>
+      </c>
+      <c r="AD114">
+        <v>14.5</v>
+      </c>
+      <c r="AE114">
+        <v>1.22</v>
+      </c>
+      <c r="AF114">
+        <v>4.3</v>
+      </c>
+      <c r="AG114">
+        <v>1.65</v>
+      </c>
+      <c r="AH114">
+        <v>2.13</v>
+      </c>
+      <c r="AI114">
+        <v>1.57</v>
+      </c>
+      <c r="AJ114">
+        <v>2.25</v>
+      </c>
+      <c r="AK114">
+        <v>1.41</v>
+      </c>
+      <c r="AL114">
+        <v>1.26</v>
+      </c>
+      <c r="AM114">
+        <v>1.61</v>
+      </c>
+      <c r="AN114">
+        <v>1.75</v>
+      </c>
+      <c r="AO114">
+        <v>1.25</v>
+      </c>
+      <c r="AP114">
+        <v>1.56</v>
+      </c>
+      <c r="AQ114">
+        <v>1.44</v>
+      </c>
+      <c r="AR114">
+        <v>1.41</v>
+      </c>
+      <c r="AS114">
+        <v>1.18</v>
+      </c>
+      <c r="AT114">
+        <v>2.59</v>
+      </c>
+      <c r="AU114">
+        <v>3</v>
+      </c>
+      <c r="AV114">
+        <v>9</v>
+      </c>
+      <c r="AW114">
+        <v>2</v>
+      </c>
+      <c r="AX114">
+        <v>11</v>
+      </c>
+      <c r="AY114">
+        <v>5</v>
+      </c>
+      <c r="AZ114">
+        <v>23</v>
+      </c>
+      <c r="BA114">
+        <v>5</v>
+      </c>
+      <c r="BB114">
+        <v>8</v>
+      </c>
+      <c r="BC114">
+        <v>13</v>
+      </c>
+      <c r="BD114">
+        <v>1.86</v>
+      </c>
+      <c r="BE114">
+        <v>6.5</v>
+      </c>
+      <c r="BF114">
+        <v>2.15</v>
+      </c>
+      <c r="BG114">
+        <v>1.26</v>
+      </c>
+      <c r="BH114">
+        <v>3.4</v>
+      </c>
+      <c r="BI114">
+        <v>1.47</v>
+      </c>
+      <c r="BJ114">
+        <v>2.48</v>
+      </c>
+      <c r="BK114">
+        <v>1.74</v>
+      </c>
+      <c r="BL114">
+        <v>1.95</v>
+      </c>
+      <c r="BM114">
+        <v>2.17</v>
+      </c>
+      <c r="BN114">
+        <v>1.6</v>
+      </c>
+      <c r="BO114">
+        <v>2.8</v>
+      </c>
+      <c r="BP114">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,9 @@
     <t>['5']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -725,6 +728,9 @@
   </si>
   <si>
     <t>['30', '37', '83', '86']</t>
+  </si>
+  <si>
+    <t>['50', '79']</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1966,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2166,7 +2172,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2372,7 +2378,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2578,7 +2584,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2784,7 +2790,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3196,7 +3202,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3274,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11">
         <v>1.44</v>
@@ -3402,7 +3408,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4432,7 +4438,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4638,7 +4644,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4844,7 +4850,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -4925,7 +4931,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ19">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR19">
         <v>1.07</v>
@@ -5256,7 +5262,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5668,7 +5674,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5874,7 +5880,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6080,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6286,7 +6292,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6492,7 +6498,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6698,7 +6704,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6779,7 +6785,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ28">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR28">
         <v>1.19</v>
@@ -6904,7 +6910,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7110,7 +7116,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7188,7 +7194,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30">
         <v>1.3</v>
@@ -7522,7 +7528,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7600,7 +7606,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ32">
         <v>1.33</v>
@@ -7728,7 +7734,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7934,7 +7940,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8140,7 +8146,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8346,7 +8352,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8964,7 +8970,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9045,7 +9051,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ39">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR39">
         <v>1.84</v>
@@ -9170,7 +9176,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9376,7 +9382,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9582,7 +9588,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9994,7 +10000,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10072,7 +10078,7 @@
         <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ44">
         <v>0.33</v>
@@ -10200,7 +10206,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10406,7 +10412,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10612,7 +10618,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11230,7 +11236,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11311,7 +11317,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ50">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR50">
         <v>1.51</v>
@@ -11642,7 +11648,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12054,7 +12060,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12466,7 +12472,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12956,7 +12962,7 @@
         <v>0.6</v>
       </c>
       <c r="AP58">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ58">
         <v>0.7</v>
@@ -13084,7 +13090,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13290,7 +13296,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13496,7 +13502,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13702,7 +13708,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13908,7 +13914,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13989,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR63">
         <v>1.52</v>
@@ -14114,7 +14120,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14320,7 +14326,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14732,7 +14738,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14938,7 +14944,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15350,7 +15356,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15428,7 +15434,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ70">
         <v>1.7</v>
@@ -15556,7 +15562,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15762,7 +15768,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16792,7 +16798,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17285,7 +17291,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ79">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17410,7 +17416,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17616,7 +17622,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17822,7 +17828,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18028,7 +18034,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18234,7 +18240,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18312,7 +18318,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ84">
         <v>0.44</v>
@@ -18440,7 +18446,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19058,7 +19064,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19470,7 +19476,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19676,7 +19682,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19757,7 +19763,7 @@
         <v>2</v>
       </c>
       <c r="AQ91">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR91">
         <v>1.65</v>
@@ -20372,7 +20378,7 @@
         <v>0.75</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ94">
         <v>0.7</v>
@@ -20500,7 +20506,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20706,7 +20712,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21324,7 +21330,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21530,7 +21536,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21736,7 +21742,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21942,7 +21948,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22229,7 +22235,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ103">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR103">
         <v>2.05</v>
@@ -22354,7 +22360,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22560,7 +22566,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22766,7 +22772,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23178,7 +23184,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23590,7 +23596,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -24002,7 +24008,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24414,7 +24420,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24571,6 +24577,212 @@
       </c>
       <c r="BP114">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7452359</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45714.64583333334</v>
+      </c>
+      <c r="F115">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>78</v>
+      </c>
+      <c r="H115" t="s">
+        <v>71</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>2</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>171</v>
+      </c>
+      <c r="P115" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q115">
+        <v>4.33</v>
+      </c>
+      <c r="R115">
+        <v>2.4</v>
+      </c>
+      <c r="S115">
+        <v>2.3</v>
+      </c>
+      <c r="T115">
+        <v>1.29</v>
+      </c>
+      <c r="U115">
+        <v>3.5</v>
+      </c>
+      <c r="V115">
+        <v>2.25</v>
+      </c>
+      <c r="W115">
+        <v>1.57</v>
+      </c>
+      <c r="X115">
+        <v>5.5</v>
+      </c>
+      <c r="Y115">
+        <v>1.14</v>
+      </c>
+      <c r="Z115">
+        <v>2.92</v>
+      </c>
+      <c r="AA115">
+        <v>3.78</v>
+      </c>
+      <c r="AB115">
+        <v>2.16</v>
+      </c>
+      <c r="AC115">
+        <v>1</v>
+      </c>
+      <c r="AD115">
+        <v>12</v>
+      </c>
+      <c r="AE115">
+        <v>1.12</v>
+      </c>
+      <c r="AF115">
+        <v>4.8</v>
+      </c>
+      <c r="AG115">
+        <v>1.53</v>
+      </c>
+      <c r="AH115">
+        <v>2.25</v>
+      </c>
+      <c r="AI115">
+        <v>1.53</v>
+      </c>
+      <c r="AJ115">
+        <v>2.38</v>
+      </c>
+      <c r="AK115">
+        <v>2.07</v>
+      </c>
+      <c r="AL115">
+        <v>1.23</v>
+      </c>
+      <c r="AM115">
+        <v>1.23</v>
+      </c>
+      <c r="AN115">
+        <v>1.38</v>
+      </c>
+      <c r="AO115">
+        <v>0.88</v>
+      </c>
+      <c r="AP115">
+        <v>1.22</v>
+      </c>
+      <c r="AQ115">
+        <v>1.11</v>
+      </c>
+      <c r="AR115">
+        <v>1.35</v>
+      </c>
+      <c r="AS115">
+        <v>1.61</v>
+      </c>
+      <c r="AT115">
+        <v>2.96</v>
+      </c>
+      <c r="AU115">
+        <v>3</v>
+      </c>
+      <c r="AV115">
+        <v>7</v>
+      </c>
+      <c r="AW115">
+        <v>10</v>
+      </c>
+      <c r="AX115">
+        <v>8</v>
+      </c>
+      <c r="AY115">
+        <v>17</v>
+      </c>
+      <c r="AZ115">
+        <v>18</v>
+      </c>
+      <c r="BA115">
+        <v>5</v>
+      </c>
+      <c r="BB115">
+        <v>2</v>
+      </c>
+      <c r="BC115">
+        <v>7</v>
+      </c>
+      <c r="BD115">
+        <v>3.05</v>
+      </c>
+      <c r="BE115">
+        <v>7</v>
+      </c>
+      <c r="BF115">
+        <v>1.46</v>
+      </c>
+      <c r="BG115">
+        <v>1.21</v>
+      </c>
+      <c r="BH115">
+        <v>3.8</v>
+      </c>
+      <c r="BI115">
+        <v>1.37</v>
+      </c>
+      <c r="BJ115">
+        <v>2.8</v>
+      </c>
+      <c r="BK115">
+        <v>1.61</v>
+      </c>
+      <c r="BL115">
+        <v>2.15</v>
+      </c>
+      <c r="BM115">
+        <v>1.95</v>
+      </c>
+      <c r="BN115">
+        <v>1.74</v>
+      </c>
+      <c r="BO115">
+        <v>2.43</v>
+      </c>
+      <c r="BP115">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -732,6 +732,9 @@
   <si>
     <t>['50', '79']</t>
   </si>
+  <si>
+    <t>['18']</t>
+  </si>
 </sst>
 </file>
 
@@ -1092,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3074,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.7</v>
@@ -3489,7 +3492,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -5340,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
         <v>1.44</v>
@@ -5755,7 +5758,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR23">
         <v>1.53</v>
@@ -6576,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>0.7</v>
@@ -7609,7 +7612,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR32">
         <v>1.14</v>
@@ -9872,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
         <v>0.6</v>
@@ -11726,7 +11729,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>1.2</v>
@@ -11935,7 +11938,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR53">
         <v>1.13</v>
@@ -14198,7 +14201,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>0.33</v>
@@ -14407,7 +14410,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -17085,7 +17088,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR78">
         <v>1.92</v>
@@ -17288,7 +17291,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
         <v>1.11</v>
@@ -19969,7 +19972,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR92">
         <v>1.68</v>
@@ -20172,7 +20175,7 @@
         <v>0.14</v>
       </c>
       <c r="AP93">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>0.44</v>
@@ -22029,7 +22032,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR102">
         <v>1.25</v>
@@ -22853,7 +22856,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR106">
         <v>1.4</v>
@@ -23262,7 +23265,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ108">
         <v>1.67</v>
@@ -24783,6 +24786,212 @@
       </c>
       <c r="BP115">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7452372</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45716.625</v>
+      </c>
+      <c r="F116">
+        <v>20</v>
+      </c>
+      <c r="G116" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116" t="s">
+        <v>70</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>2</v>
+      </c>
+      <c r="O116" t="s">
+        <v>165</v>
+      </c>
+      <c r="P116" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q116">
+        <v>3.75</v>
+      </c>
+      <c r="R116">
+        <v>2.05</v>
+      </c>
+      <c r="S116">
+        <v>3.1</v>
+      </c>
+      <c r="T116">
+        <v>1.44</v>
+      </c>
+      <c r="U116">
+        <v>2.63</v>
+      </c>
+      <c r="V116">
+        <v>3.25</v>
+      </c>
+      <c r="W116">
+        <v>1.33</v>
+      </c>
+      <c r="X116">
+        <v>9</v>
+      </c>
+      <c r="Y116">
+        <v>1.07</v>
+      </c>
+      <c r="Z116">
+        <v>2.76</v>
+      </c>
+      <c r="AA116">
+        <v>3.41</v>
+      </c>
+      <c r="AB116">
+        <v>2.41</v>
+      </c>
+      <c r="AC116">
+        <v>1.06</v>
+      </c>
+      <c r="AD116">
+        <v>8.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.33</v>
+      </c>
+      <c r="AF116">
+        <v>3.25</v>
+      </c>
+      <c r="AG116">
+        <v>1.92</v>
+      </c>
+      <c r="AH116">
+        <v>1.82</v>
+      </c>
+      <c r="AI116">
+        <v>1.91</v>
+      </c>
+      <c r="AJ116">
+        <v>1.91</v>
+      </c>
+      <c r="AK116">
+        <v>1.58</v>
+      </c>
+      <c r="AL116">
+        <v>1.3</v>
+      </c>
+      <c r="AM116">
+        <v>1.38</v>
+      </c>
+      <c r="AN116">
+        <v>1.56</v>
+      </c>
+      <c r="AO116">
+        <v>1.33</v>
+      </c>
+      <c r="AP116">
+        <v>1.5</v>
+      </c>
+      <c r="AQ116">
+        <v>1.3</v>
+      </c>
+      <c r="AR116">
+        <v>1.48</v>
+      </c>
+      <c r="AS116">
+        <v>1.21</v>
+      </c>
+      <c r="AT116">
+        <v>2.69</v>
+      </c>
+      <c r="AU116">
+        <v>3</v>
+      </c>
+      <c r="AV116">
+        <v>3</v>
+      </c>
+      <c r="AW116">
+        <v>7</v>
+      </c>
+      <c r="AX116">
+        <v>6</v>
+      </c>
+      <c r="AY116">
+        <v>12</v>
+      </c>
+      <c r="AZ116">
+        <v>12</v>
+      </c>
+      <c r="BA116">
+        <v>3</v>
+      </c>
+      <c r="BB116">
+        <v>8</v>
+      </c>
+      <c r="BC116">
+        <v>11</v>
+      </c>
+      <c r="BD116">
+        <v>2.32</v>
+      </c>
+      <c r="BE116">
+        <v>6.75</v>
+      </c>
+      <c r="BF116">
+        <v>1.73</v>
+      </c>
+      <c r="BG116">
+        <v>1.27</v>
+      </c>
+      <c r="BH116">
+        <v>3.3</v>
+      </c>
+      <c r="BI116">
+        <v>1.47</v>
+      </c>
+      <c r="BJ116">
+        <v>2.48</v>
+      </c>
+      <c r="BK116">
+        <v>1.75</v>
+      </c>
+      <c r="BL116">
+        <v>1.95</v>
+      </c>
+      <c r="BM116">
+        <v>2.18</v>
+      </c>
+      <c r="BN116">
+        <v>1.58</v>
+      </c>
+      <c r="BO116">
+        <v>2.8</v>
+      </c>
+      <c r="BP116">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,15 @@
     <t>['90+4']</t>
   </si>
   <si>
+    <t>['14', '32', '44']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['54', '90+2']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -734,6 +743,15 @@
   </si>
   <si>
     <t>['18']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['16', '67', '90+7']</t>
+  </si>
+  <si>
+    <t>['76']</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1969,7 +1987,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2175,7 +2193,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2253,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6">
         <v>1.3</v>
@@ -2381,7 +2399,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2462,7 +2480,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ7">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2587,7 +2605,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2665,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ8">
         <v>0.33</v>
@@ -2793,7 +2811,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3205,7 +3223,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3283,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ11">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3411,7 +3429,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3698,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4107,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15">
         <v>0.6</v>
@@ -4441,7 +4459,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4647,7 +4665,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4853,7 +4871,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -4934,7 +4952,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ19">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.07</v>
@@ -5137,10 +5155,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ20">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR20">
         <v>1.75</v>
@@ -5265,7 +5283,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5346,7 +5364,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5677,7 +5695,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5883,7 +5901,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -5961,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR24">
         <v>1.85</v>
@@ -6089,7 +6107,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6167,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ25">
         <v>0.6</v>
@@ -6295,7 +6313,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6501,7 +6519,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6707,7 +6725,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6788,7 +6806,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ28">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.19</v>
@@ -6913,7 +6931,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7119,7 +7137,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7197,7 +7215,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
         <v>1.3</v>
@@ -7406,7 +7424,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ31">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR31">
         <v>1.74</v>
@@ -7531,7 +7549,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7609,7 +7627,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32">
         <v>1.3</v>
@@ -7737,7 +7755,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7815,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ33">
         <v>0.7</v>
@@ -7943,7 +7961,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8024,7 +8042,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ34">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8149,7 +8167,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8230,7 +8248,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR35">
         <v>1.81</v>
@@ -8355,7 +8373,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8639,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ37">
         <v>0.33</v>
@@ -8848,7 +8866,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ38">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR38">
         <v>1.09</v>
@@ -8973,7 +8991,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9054,7 +9072,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ39">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.84</v>
@@ -9179,7 +9197,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9385,7 +9403,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9463,7 +9481,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ41">
         <v>0.7</v>
@@ -9591,7 +9609,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10003,7 +10021,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10081,7 +10099,7 @@
         <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ44">
         <v>0.33</v>
@@ -10209,7 +10227,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10287,10 +10305,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ45">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR45">
         <v>1.88</v>
@@ -10415,7 +10433,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10496,7 +10514,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10621,7 +10639,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11239,7 +11257,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11317,10 +11335,10 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ50">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.51</v>
@@ -11523,10 +11541,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ51">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR51">
         <v>1.45</v>
@@ -11651,7 +11669,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12063,7 +12081,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12475,7 +12493,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12759,7 +12777,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ57">
         <v>0.7</v>
@@ -12965,7 +12983,7 @@
         <v>0.6</v>
       </c>
       <c r="AP58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ58">
         <v>0.7</v>
@@ -13093,7 +13111,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13174,7 +13192,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ59">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR59">
         <v>1.04</v>
@@ -13299,7 +13317,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13380,7 +13398,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.56</v>
@@ -13505,7 +13523,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13711,7 +13729,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13917,7 +13935,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13995,10 +14013,10 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.52</v>
@@ -14123,7 +14141,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14329,7 +14347,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14407,7 +14425,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -14741,7 +14759,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14822,7 +14840,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR67">
         <v>1.23</v>
@@ -14947,7 +14965,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15028,7 +15046,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ68">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR68">
         <v>1.76</v>
@@ -15359,7 +15377,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15437,7 +15455,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
         <v>1.7</v>
@@ -15565,7 +15583,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15646,7 +15664,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ71">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -15771,7 +15789,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15849,7 +15867,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ72">
         <v>1.2</v>
@@ -16470,7 +16488,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR75">
         <v>1.81</v>
@@ -16801,7 +16819,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16879,7 +16897,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ77">
         <v>0.7</v>
@@ -17085,7 +17103,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ78">
         <v>1.3</v>
@@ -17294,7 +17312,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17419,7 +17437,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17497,7 +17515,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ80">
         <v>1.7</v>
@@ -17625,7 +17643,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17703,7 +17721,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ81">
         <v>1.3</v>
@@ -17831,7 +17849,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18037,7 +18055,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18243,7 +18261,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18321,10 +18339,10 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR84">
         <v>1.31</v>
@@ -18449,7 +18467,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18530,7 +18548,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -19067,7 +19085,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19351,7 +19369,7 @@
         <v>1.29</v>
       </c>
       <c r="AP89">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ89">
         <v>1.2</v>
@@ -19479,7 +19497,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19560,7 +19578,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR90">
         <v>1.66</v>
@@ -19685,7 +19703,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19766,7 +19784,7 @@
         <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.65</v>
@@ -20178,7 +20196,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR93">
         <v>1.44</v>
@@ -20381,7 +20399,7 @@
         <v>0.75</v>
       </c>
       <c r="AP94">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ94">
         <v>0.7</v>
@@ -20509,7 +20527,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20587,7 +20605,7 @@
         <v>1.38</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ95">
         <v>1.3</v>
@@ -20715,7 +20733,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20999,10 +21017,10 @@
         <v>1.43</v>
       </c>
       <c r="AP97">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ97">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR97">
         <v>1.78</v>
@@ -21333,7 +21351,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21539,7 +21557,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21617,7 +21635,7 @@
         <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ100">
         <v>1.7</v>
@@ -21745,7 +21763,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21951,7 +21969,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22238,7 +22256,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ103">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>2.05</v>
@@ -22363,7 +22381,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22569,7 +22587,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22650,7 +22668,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ105">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR105">
         <v>1.26</v>
@@ -22775,7 +22793,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -22853,7 +22871,7 @@
         <v>1.13</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ106">
         <v>1.3</v>
@@ -23059,7 +23077,7 @@
         <v>0.38</v>
       </c>
       <c r="AP107">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ107">
         <v>0.33</v>
@@ -23187,7 +23205,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23268,7 +23286,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ108">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR108">
         <v>1.51</v>
@@ -23599,7 +23617,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -24011,7 +24029,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24423,7 +24441,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24501,10 +24519,10 @@
         <v>1.25</v>
       </c>
       <c r="AP114">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ114">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR114">
         <v>1.41</v>
@@ -24629,7 +24647,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24707,10 +24725,10 @@
         <v>0.88</v>
       </c>
       <c r="AP115">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ115">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.35</v>
@@ -24835,7 +24853,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -24992,6 +25010,830 @@
       </c>
       <c r="BP116">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7452374</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>74</v>
+      </c>
+      <c r="H117" t="s">
+        <v>73</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>3</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>4</v>
+      </c>
+      <c r="O117" t="s">
+        <v>172</v>
+      </c>
+      <c r="P117" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q117">
+        <v>2.38</v>
+      </c>
+      <c r="R117">
+        <v>2.38</v>
+      </c>
+      <c r="S117">
+        <v>4.33</v>
+      </c>
+      <c r="T117">
+        <v>1.3</v>
+      </c>
+      <c r="U117">
+        <v>3.4</v>
+      </c>
+      <c r="V117">
+        <v>2.5</v>
+      </c>
+      <c r="W117">
+        <v>1.5</v>
+      </c>
+      <c r="X117">
+        <v>6</v>
+      </c>
+      <c r="Y117">
+        <v>1.13</v>
+      </c>
+      <c r="Z117">
+        <v>1.73</v>
+      </c>
+      <c r="AA117">
+        <v>3.71</v>
+      </c>
+      <c r="AB117">
+        <v>4.5</v>
+      </c>
+      <c r="AC117">
+        <v>1.01</v>
+      </c>
+      <c r="AD117">
+        <v>16.5</v>
+      </c>
+      <c r="AE117">
+        <v>1.2</v>
+      </c>
+      <c r="AF117">
+        <v>4.5</v>
+      </c>
+      <c r="AG117">
+        <v>1.67</v>
+      </c>
+      <c r="AH117">
+        <v>2</v>
+      </c>
+      <c r="AI117">
+        <v>1.57</v>
+      </c>
+      <c r="AJ117">
+        <v>2.25</v>
+      </c>
+      <c r="AK117">
+        <v>1.23</v>
+      </c>
+      <c r="AL117">
+        <v>1.25</v>
+      </c>
+      <c r="AM117">
+        <v>1.98</v>
+      </c>
+      <c r="AN117">
+        <v>1.56</v>
+      </c>
+      <c r="AO117">
+        <v>0.44</v>
+      </c>
+      <c r="AP117">
+        <v>1.7</v>
+      </c>
+      <c r="AQ117">
+        <v>0.4</v>
+      </c>
+      <c r="AR117">
+        <v>1.35</v>
+      </c>
+      <c r="AS117">
+        <v>1.14</v>
+      </c>
+      <c r="AT117">
+        <v>2.49</v>
+      </c>
+      <c r="AU117">
+        <v>5</v>
+      </c>
+      <c r="AV117">
+        <v>3</v>
+      </c>
+      <c r="AW117">
+        <v>10</v>
+      </c>
+      <c r="AX117">
+        <v>10</v>
+      </c>
+      <c r="AY117">
+        <v>15</v>
+      </c>
+      <c r="AZ117">
+        <v>15</v>
+      </c>
+      <c r="BA117">
+        <v>4</v>
+      </c>
+      <c r="BB117">
+        <v>4</v>
+      </c>
+      <c r="BC117">
+        <v>8</v>
+      </c>
+      <c r="BD117">
+        <v>1.57</v>
+      </c>
+      <c r="BE117">
+        <v>7</v>
+      </c>
+      <c r="BF117">
+        <v>2.65</v>
+      </c>
+      <c r="BG117">
+        <v>1.19</v>
+      </c>
+      <c r="BH117">
+        <v>4.1</v>
+      </c>
+      <c r="BI117">
+        <v>1.33</v>
+      </c>
+      <c r="BJ117">
+        <v>2.95</v>
+      </c>
+      <c r="BK117">
+        <v>1.55</v>
+      </c>
+      <c r="BL117">
+        <v>2.28</v>
+      </c>
+      <c r="BM117">
+        <v>1.85</v>
+      </c>
+      <c r="BN117">
+        <v>1.83</v>
+      </c>
+      <c r="BO117">
+        <v>2.3</v>
+      </c>
+      <c r="BP117">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7452373</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F118">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s">
+        <v>72</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118">
+        <v>2</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>3</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>173</v>
+      </c>
+      <c r="P118" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q118">
+        <v>3.6</v>
+      </c>
+      <c r="R118">
+        <v>2.3</v>
+      </c>
+      <c r="S118">
+        <v>2.75</v>
+      </c>
+      <c r="T118">
+        <v>1.33</v>
+      </c>
+      <c r="U118">
+        <v>3.25</v>
+      </c>
+      <c r="V118">
+        <v>2.63</v>
+      </c>
+      <c r="W118">
+        <v>1.44</v>
+      </c>
+      <c r="X118">
+        <v>6.5</v>
+      </c>
+      <c r="Y118">
+        <v>1.11</v>
+      </c>
+      <c r="Z118">
+        <v>2.95</v>
+      </c>
+      <c r="AA118">
+        <v>3.67</v>
+      </c>
+      <c r="AB118">
+        <v>2.18</v>
+      </c>
+      <c r="AC118">
+        <v>1.03</v>
+      </c>
+      <c r="AD118">
+        <v>12.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.22</v>
+      </c>
+      <c r="AF118">
+        <v>4.3</v>
+      </c>
+      <c r="AG118">
+        <v>1.67</v>
+      </c>
+      <c r="AH118">
+        <v>2.1</v>
+      </c>
+      <c r="AI118">
+        <v>1.62</v>
+      </c>
+      <c r="AJ118">
+        <v>2.2</v>
+      </c>
+      <c r="AK118">
+        <v>1.65</v>
+      </c>
+      <c r="AL118">
+        <v>1.28</v>
+      </c>
+      <c r="AM118">
+        <v>1.35</v>
+      </c>
+      <c r="AN118">
+        <v>1</v>
+      </c>
+      <c r="AO118">
+        <v>1.44</v>
+      </c>
+      <c r="AP118">
+        <v>0.9</v>
+      </c>
+      <c r="AQ118">
+        <v>1.6</v>
+      </c>
+      <c r="AR118">
+        <v>1.38</v>
+      </c>
+      <c r="AS118">
+        <v>1.3</v>
+      </c>
+      <c r="AT118">
+        <v>2.68</v>
+      </c>
+      <c r="AU118">
+        <v>9</v>
+      </c>
+      <c r="AV118">
+        <v>10</v>
+      </c>
+      <c r="AW118">
+        <v>8</v>
+      </c>
+      <c r="AX118">
+        <v>10</v>
+      </c>
+      <c r="AY118">
+        <v>20</v>
+      </c>
+      <c r="AZ118">
+        <v>26</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>7</v>
+      </c>
+      <c r="BC118">
+        <v>10</v>
+      </c>
+      <c r="BD118">
+        <v>2.17</v>
+      </c>
+      <c r="BE118">
+        <v>6.4</v>
+      </c>
+      <c r="BF118">
+        <v>1.84</v>
+      </c>
+      <c r="BG118">
+        <v>1.36</v>
+      </c>
+      <c r="BH118">
+        <v>2.85</v>
+      </c>
+      <c r="BI118">
+        <v>1.61</v>
+      </c>
+      <c r="BJ118">
+        <v>2.15</v>
+      </c>
+      <c r="BK118">
+        <v>1.98</v>
+      </c>
+      <c r="BL118">
+        <v>1.72</v>
+      </c>
+      <c r="BM118">
+        <v>2.5</v>
+      </c>
+      <c r="BN118">
+        <v>1.46</v>
+      </c>
+      <c r="BO118">
+        <v>3.3</v>
+      </c>
+      <c r="BP118">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7452370</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F119">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>81</v>
+      </c>
+      <c r="H119" t="s">
+        <v>71</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>2</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+      <c r="O119" t="s">
+        <v>174</v>
+      </c>
+      <c r="P119" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q119">
+        <v>2.5</v>
+      </c>
+      <c r="R119">
+        <v>2.38</v>
+      </c>
+      <c r="S119">
+        <v>3.75</v>
+      </c>
+      <c r="T119">
+        <v>1.29</v>
+      </c>
+      <c r="U119">
+        <v>3.5</v>
+      </c>
+      <c r="V119">
+        <v>2.38</v>
+      </c>
+      <c r="W119">
+        <v>1.53</v>
+      </c>
+      <c r="X119">
+        <v>5.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.14</v>
+      </c>
+      <c r="Z119">
+        <v>1.94</v>
+      </c>
+      <c r="AA119">
+        <v>3.53</v>
+      </c>
+      <c r="AB119">
+        <v>3.67</v>
+      </c>
+      <c r="AC119">
+        <v>1.01</v>
+      </c>
+      <c r="AD119">
+        <v>16.5</v>
+      </c>
+      <c r="AE119">
+        <v>1.19</v>
+      </c>
+      <c r="AF119">
+        <v>4.7</v>
+      </c>
+      <c r="AG119">
+        <v>1.55</v>
+      </c>
+      <c r="AH119">
+        <v>2.2</v>
+      </c>
+      <c r="AI119">
+        <v>1.53</v>
+      </c>
+      <c r="AJ119">
+        <v>2.38</v>
+      </c>
+      <c r="AK119">
+        <v>1.3</v>
+      </c>
+      <c r="AL119">
+        <v>1.26</v>
+      </c>
+      <c r="AM119">
+        <v>1.78</v>
+      </c>
+      <c r="AN119">
+        <v>2.67</v>
+      </c>
+      <c r="AO119">
+        <v>1.11</v>
+      </c>
+      <c r="AP119">
+        <v>2.7</v>
+      </c>
+      <c r="AQ119">
+        <v>1</v>
+      </c>
+      <c r="AR119">
+        <v>1.65</v>
+      </c>
+      <c r="AS119">
+        <v>1.61</v>
+      </c>
+      <c r="AT119">
+        <v>3.26</v>
+      </c>
+      <c r="AU119">
+        <v>8</v>
+      </c>
+      <c r="AV119">
+        <v>9</v>
+      </c>
+      <c r="AW119">
+        <v>12</v>
+      </c>
+      <c r="AX119">
+        <v>5</v>
+      </c>
+      <c r="AY119">
+        <v>22</v>
+      </c>
+      <c r="AZ119">
+        <v>16</v>
+      </c>
+      <c r="BA119">
+        <v>8</v>
+      </c>
+      <c r="BB119">
+        <v>4</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>1.6</v>
+      </c>
+      <c r="BE119">
+        <v>6.75</v>
+      </c>
+      <c r="BF119">
+        <v>2.55</v>
+      </c>
+      <c r="BG119">
+        <v>1.23</v>
+      </c>
+      <c r="BH119">
+        <v>3.65</v>
+      </c>
+      <c r="BI119">
+        <v>1.41</v>
+      </c>
+      <c r="BJ119">
+        <v>2.65</v>
+      </c>
+      <c r="BK119">
+        <v>1.67</v>
+      </c>
+      <c r="BL119">
+        <v>2.05</v>
+      </c>
+      <c r="BM119">
+        <v>2.06</v>
+      </c>
+      <c r="BN119">
+        <v>1.66</v>
+      </c>
+      <c r="BO119">
+        <v>2.6</v>
+      </c>
+      <c r="BP119">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7452371</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45718.58333333334</v>
+      </c>
+      <c r="F120">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>78</v>
+      </c>
+      <c r="H120" t="s">
+        <v>79</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" t="s">
+        <v>87</v>
+      </c>
+      <c r="P120" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q120">
+        <v>5.5</v>
+      </c>
+      <c r="R120">
+        <v>2.5</v>
+      </c>
+      <c r="S120">
+        <v>2.05</v>
+      </c>
+      <c r="T120">
+        <v>1.29</v>
+      </c>
+      <c r="U120">
+        <v>3.5</v>
+      </c>
+      <c r="V120">
+        <v>2.38</v>
+      </c>
+      <c r="W120">
+        <v>1.53</v>
+      </c>
+      <c r="X120">
+        <v>5.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.14</v>
+      </c>
+      <c r="Z120">
+        <v>5.2</v>
+      </c>
+      <c r="AA120">
+        <v>4.3</v>
+      </c>
+      <c r="AB120">
+        <v>1.55</v>
+      </c>
+      <c r="AC120">
+        <v>1.01</v>
+      </c>
+      <c r="AD120">
+        <v>16.5</v>
+      </c>
+      <c r="AE120">
+        <v>1.2</v>
+      </c>
+      <c r="AF120">
+        <v>4.5</v>
+      </c>
+      <c r="AG120">
+        <v>1.57</v>
+      </c>
+      <c r="AH120">
+        <v>2.15</v>
+      </c>
+      <c r="AI120">
+        <v>1.7</v>
+      </c>
+      <c r="AJ120">
+        <v>2.05</v>
+      </c>
+      <c r="AK120">
+        <v>2.45</v>
+      </c>
+      <c r="AL120">
+        <v>1.2</v>
+      </c>
+      <c r="AM120">
+        <v>1.14</v>
+      </c>
+      <c r="AN120">
+        <v>1.22</v>
+      </c>
+      <c r="AO120">
+        <v>1.67</v>
+      </c>
+      <c r="AP120">
+        <v>1.2</v>
+      </c>
+      <c r="AQ120">
+        <v>1.6</v>
+      </c>
+      <c r="AR120">
+        <v>1.35</v>
+      </c>
+      <c r="AS120">
+        <v>1.62</v>
+      </c>
+      <c r="AT120">
+        <v>2.97</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>2</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>13</v>
+      </c>
+      <c r="AY120">
+        <v>8</v>
+      </c>
+      <c r="AZ120">
+        <v>20</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>8</v>
+      </c>
+      <c r="BC120">
+        <v>10</v>
+      </c>
+      <c r="BD120">
+        <v>3.15</v>
+      </c>
+      <c r="BE120">
+        <v>7</v>
+      </c>
+      <c r="BF120">
+        <v>1.43</v>
+      </c>
+      <c r="BG120">
+        <v>1.21</v>
+      </c>
+      <c r="BH120">
+        <v>3.8</v>
+      </c>
+      <c r="BI120">
+        <v>1.38</v>
+      </c>
+      <c r="BJ120">
+        <v>2.7</v>
+      </c>
+      <c r="BK120">
+        <v>1.64</v>
+      </c>
+      <c r="BL120">
+        <v>2.1</v>
+      </c>
+      <c r="BM120">
+        <v>1.98</v>
+      </c>
+      <c r="BN120">
+        <v>1.72</v>
+      </c>
+      <c r="BO120">
+        <v>2.48</v>
+      </c>
+      <c r="BP120">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -539,6 +539,9 @@
   </si>
   <si>
     <t>['54', '90+2']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
   </si>
   <si>
     <t>['53', '59', '90+2']</t>
@@ -1113,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1987,7 +1990,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2193,7 +2196,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2399,7 +2402,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2605,7 +2608,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2686,7 +2689,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ8">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2811,7 +2814,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3223,7 +3226,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3429,7 +3432,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3713,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ13">
         <v>0.4</v>
@@ -4459,7 +4462,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4665,7 +4668,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4871,7 +4874,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5283,7 +5286,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5570,7 +5573,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ22">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR22">
         <v>1.44</v>
@@ -5695,7 +5698,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5773,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ23">
         <v>1.3</v>
@@ -5901,7 +5904,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6107,7 +6110,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6313,7 +6316,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6519,7 +6522,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6725,7 +6728,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6931,7 +6934,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7137,7 +7140,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7549,7 +7552,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7755,7 +7758,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7961,7 +7964,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8167,7 +8170,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8373,7 +8376,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8451,7 +8454,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ36">
         <v>1.7</v>
@@ -8660,7 +8663,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ37">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR37">
         <v>1.54</v>
@@ -8991,7 +8994,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9197,7 +9200,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9403,7 +9406,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9609,7 +9612,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10021,7 +10024,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10102,7 +10105,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ44">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR44">
         <v>0.9</v>
@@ -10227,7 +10230,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10433,7 +10436,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10639,7 +10642,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10923,7 +10926,7 @@
         <v>0.75</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ48">
         <v>0.7</v>
@@ -11257,7 +11260,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11669,7 +11672,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12081,7 +12084,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12493,7 +12496,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13111,7 +13114,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13317,7 +13320,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13523,7 +13526,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13729,7 +13732,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13935,7 +13938,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14141,7 +14144,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14222,7 +14225,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR64">
         <v>1.45</v>
@@ -14347,7 +14350,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14631,7 +14634,7 @@
         <v>1.8</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -14759,7 +14762,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14965,7 +14968,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15377,7 +15380,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15583,7 +15586,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15789,7 +15792,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16485,7 +16488,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ75">
         <v>1.6</v>
@@ -16694,7 +16697,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ76">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR76">
         <v>1.38</v>
@@ -16819,7 +16822,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17437,7 +17440,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17643,7 +17646,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17849,7 +17852,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18055,7 +18058,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18136,7 +18139,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ83">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR83">
         <v>1.59</v>
@@ -18261,7 +18264,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18467,7 +18470,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19085,7 +19088,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19497,7 +19500,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19703,7 +19706,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19781,7 +19784,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20527,7 +20530,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20733,7 +20736,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20814,7 +20817,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ96">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR96">
         <v>1.89</v>
@@ -21223,7 +21226,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ98">
         <v>0.6</v>
@@ -21351,7 +21354,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21557,7 +21560,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21763,7 +21766,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21969,7 +21972,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22381,7 +22384,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22459,7 +22462,7 @@
         <v>0.78</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ104">
         <v>0.7</v>
@@ -22587,7 +22590,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22793,7 +22796,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23080,7 +23083,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ107">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR107">
         <v>1.68</v>
@@ -23205,7 +23208,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23617,7 +23620,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -24029,7 +24032,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24441,7 +24444,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24647,7 +24650,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24853,7 +24856,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25059,7 +25062,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q117">
         <v>2.38</v>
@@ -25265,7 +25268,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25471,7 +25474,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -25834,6 +25837,212 @@
       </c>
       <c r="BP120">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7452369</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45719.625</v>
+      </c>
+      <c r="F121">
+        <v>20</v>
+      </c>
+      <c r="G121" t="s">
+        <v>80</v>
+      </c>
+      <c r="H121" t="s">
+        <v>75</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>175</v>
+      </c>
+      <c r="P121" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q121">
+        <v>1.83</v>
+      </c>
+      <c r="R121">
+        <v>2.5</v>
+      </c>
+      <c r="S121">
+        <v>7</v>
+      </c>
+      <c r="T121">
+        <v>1.3</v>
+      </c>
+      <c r="U121">
+        <v>3.4</v>
+      </c>
+      <c r="V121">
+        <v>2.5</v>
+      </c>
+      <c r="W121">
+        <v>1.5</v>
+      </c>
+      <c r="X121">
+        <v>6</v>
+      </c>
+      <c r="Y121">
+        <v>1.13</v>
+      </c>
+      <c r="Z121">
+        <v>1.37</v>
+      </c>
+      <c r="AA121">
+        <v>4.8</v>
+      </c>
+      <c r="AB121">
+        <v>7.4</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>16.5</v>
+      </c>
+      <c r="AE121">
+        <v>1.2</v>
+      </c>
+      <c r="AF121">
+        <v>4.5</v>
+      </c>
+      <c r="AG121">
+        <v>1.57</v>
+      </c>
+      <c r="AH121">
+        <v>2.15</v>
+      </c>
+      <c r="AI121">
+        <v>1.91</v>
+      </c>
+      <c r="AJ121">
+        <v>1.91</v>
+      </c>
+      <c r="AK121">
+        <v>1.09</v>
+      </c>
+      <c r="AL121">
+        <v>1.17</v>
+      </c>
+      <c r="AM121">
+        <v>2.95</v>
+      </c>
+      <c r="AN121">
+        <v>2</v>
+      </c>
+      <c r="AO121">
+        <v>0.33</v>
+      </c>
+      <c r="AP121">
+        <v>1.9</v>
+      </c>
+      <c r="AQ121">
+        <v>0.4</v>
+      </c>
+      <c r="AR121">
+        <v>1.67</v>
+      </c>
+      <c r="AS121">
+        <v>1.19</v>
+      </c>
+      <c r="AT121">
+        <v>2.86</v>
+      </c>
+      <c r="AU121">
+        <v>7</v>
+      </c>
+      <c r="AV121">
+        <v>2</v>
+      </c>
+      <c r="AW121">
+        <v>13</v>
+      </c>
+      <c r="AX121">
+        <v>6</v>
+      </c>
+      <c r="AY121">
+        <v>23</v>
+      </c>
+      <c r="AZ121">
+        <v>8</v>
+      </c>
+      <c r="BA121">
+        <v>8</v>
+      </c>
+      <c r="BB121">
+        <v>3</v>
+      </c>
+      <c r="BC121">
+        <v>11</v>
+      </c>
+      <c r="BD121">
+        <v>1.26</v>
+      </c>
+      <c r="BE121">
+        <v>8</v>
+      </c>
+      <c r="BF121">
+        <v>4.1</v>
+      </c>
+      <c r="BG121">
+        <v>1.2</v>
+      </c>
+      <c r="BH121">
+        <v>3.9</v>
+      </c>
+      <c r="BI121">
+        <v>1.36</v>
+      </c>
+      <c r="BJ121">
+        <v>2.8</v>
+      </c>
+      <c r="BK121">
+        <v>1.6</v>
+      </c>
+      <c r="BL121">
+        <v>2.17</v>
+      </c>
+      <c r="BM121">
+        <v>1.95</v>
+      </c>
+      <c r="BN121">
+        <v>1.75</v>
+      </c>
+      <c r="BO121">
+        <v>2.4</v>
+      </c>
+      <c r="BP121">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['3', '55', '82']</t>
   </si>
   <si>
     <t>['53', '59', '90+2']</t>
@@ -1116,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1656,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ3">
         <v>0.6</v>
@@ -1990,7 +1993,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2196,7 +2199,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2402,7 +2405,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2608,7 +2611,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2814,7 +2817,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2892,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9">
         <v>1.2</v>
@@ -3226,7 +3229,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3432,7 +3435,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3719,7 +3722,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ13">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4462,7 +4465,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4668,7 +4671,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4874,7 +4877,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5161,7 +5164,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ20">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
         <v>1.75</v>
@@ -5286,7 +5289,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5570,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ22">
         <v>0.4</v>
@@ -5698,7 +5701,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5904,7 +5907,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6110,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6316,7 +6319,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6522,7 +6525,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6728,7 +6731,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6934,7 +6937,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7140,7 +7143,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7427,7 +7430,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ31">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR31">
         <v>1.74</v>
@@ -7552,7 +7555,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7758,7 +7761,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7964,7 +7967,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8170,7 +8173,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8248,7 +8251,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ35">
         <v>1.6</v>
@@ -8376,7 +8379,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8869,7 +8872,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ38">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR38">
         <v>1.09</v>
@@ -8994,7 +8997,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9200,7 +9203,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9406,7 +9409,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9612,7 +9615,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10024,7 +10027,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10230,7 +10233,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10436,7 +10439,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10642,7 +10645,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11132,7 +11135,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>1.7</v>
@@ -11260,7 +11263,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11547,7 +11550,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ51">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR51">
         <v>1.45</v>
@@ -11672,7 +11675,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12084,7 +12087,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12496,7 +12499,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13114,7 +13117,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13320,7 +13323,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13526,7 +13529,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13604,7 +13607,7 @@
         <v>1.6</v>
       </c>
       <c r="AP61">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ61">
         <v>1.3</v>
@@ -13732,7 +13735,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13938,7 +13941,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14144,7 +14147,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14350,7 +14353,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14762,7 +14765,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14968,7 +14971,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15049,7 +15052,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ68">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR68">
         <v>1.76</v>
@@ -15380,7 +15383,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15586,7 +15589,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15664,7 +15667,7 @@
         <v>1.6</v>
       </c>
       <c r="AP71">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ71">
         <v>1.6</v>
@@ -15792,7 +15795,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16822,7 +16825,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17440,7 +17443,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17646,7 +17649,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17852,7 +17855,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -17930,7 +17933,7 @@
         <v>0.86</v>
       </c>
       <c r="AP82">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ82">
         <v>0.7</v>
@@ -18058,7 +18061,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18264,7 +18267,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18345,7 +18348,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR84">
         <v>1.31</v>
@@ -18470,7 +18473,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19088,7 +19091,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19500,7 +19503,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19706,7 +19709,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19990,7 +19993,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ92">
         <v>1.3</v>
@@ -20199,7 +20202,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR93">
         <v>1.44</v>
@@ -20530,7 +20533,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20736,7 +20739,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21354,7 +21357,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21560,7 +21563,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21766,7 +21769,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21972,7 +21975,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22384,7 +22387,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22590,7 +22593,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22671,7 +22674,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ105">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR105">
         <v>1.26</v>
@@ -22796,7 +22799,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23208,7 +23211,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23620,7 +23623,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -23698,7 +23701,7 @@
         <v>0.78</v>
       </c>
       <c r="AP110">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ110">
         <v>0.7</v>
@@ -24032,7 +24035,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24444,7 +24447,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24650,7 +24653,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24856,7 +24859,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25062,7 +25065,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q117">
         <v>2.38</v>
@@ -25143,7 +25146,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR117">
         <v>1.35</v>
@@ -25268,7 +25271,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25474,7 +25477,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -26043,6 +26046,212 @@
       </c>
       <c r="BP121">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7452377</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45723.625</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>71</v>
+      </c>
+      <c r="H122" t="s">
+        <v>73</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>3</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>4</v>
+      </c>
+      <c r="O122" t="s">
+        <v>176</v>
+      </c>
+      <c r="P122" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q122">
+        <v>1.83</v>
+      </c>
+      <c r="R122">
+        <v>2.62</v>
+      </c>
+      <c r="S122">
+        <v>5.8</v>
+      </c>
+      <c r="T122">
+        <v>1.25</v>
+      </c>
+      <c r="U122">
+        <v>3.8</v>
+      </c>
+      <c r="V122">
+        <v>2.1</v>
+      </c>
+      <c r="W122">
+        <v>1.67</v>
+      </c>
+      <c r="X122">
+        <v>4.8</v>
+      </c>
+      <c r="Y122">
+        <v>1.17</v>
+      </c>
+      <c r="Z122">
+        <v>1.37</v>
+      </c>
+      <c r="AA122">
+        <v>4.7</v>
+      </c>
+      <c r="AB122">
+        <v>7.8</v>
+      </c>
+      <c r="AC122">
+        <v>1.03</v>
+      </c>
+      <c r="AD122">
+        <v>19</v>
+      </c>
+      <c r="AE122">
+        <v>1.12</v>
+      </c>
+      <c r="AF122">
+        <v>5.25</v>
+      </c>
+      <c r="AG122">
+        <v>1.52</v>
+      </c>
+      <c r="AH122">
+        <v>2.43</v>
+      </c>
+      <c r="AI122">
+        <v>1.62</v>
+      </c>
+      <c r="AJ122">
+        <v>2.15</v>
+      </c>
+      <c r="AK122">
+        <v>1.18</v>
+      </c>
+      <c r="AL122">
+        <v>1.16</v>
+      </c>
+      <c r="AM122">
+        <v>2.88</v>
+      </c>
+      <c r="AN122">
+        <v>2.2</v>
+      </c>
+      <c r="AO122">
+        <v>0.4</v>
+      </c>
+      <c r="AP122">
+        <v>2.27</v>
+      </c>
+      <c r="AQ122">
+        <v>0.36</v>
+      </c>
+      <c r="AR122">
+        <v>1.71</v>
+      </c>
+      <c r="AS122">
+        <v>1.16</v>
+      </c>
+      <c r="AT122">
+        <v>2.87</v>
+      </c>
+      <c r="AU122">
+        <v>7</v>
+      </c>
+      <c r="AV122">
+        <v>5</v>
+      </c>
+      <c r="AW122">
+        <v>6</v>
+      </c>
+      <c r="AX122">
+        <v>4</v>
+      </c>
+      <c r="AY122">
+        <v>15</v>
+      </c>
+      <c r="AZ122">
+        <v>11</v>
+      </c>
+      <c r="BA122">
+        <v>4</v>
+      </c>
+      <c r="BB122">
+        <v>1</v>
+      </c>
+      <c r="BC122">
+        <v>5</v>
+      </c>
+      <c r="BD122">
+        <v>1.26</v>
+      </c>
+      <c r="BE122">
+        <v>8</v>
+      </c>
+      <c r="BF122">
+        <v>4.1</v>
+      </c>
+      <c r="BG122">
+        <v>1.23</v>
+      </c>
+      <c r="BH122">
+        <v>3.65</v>
+      </c>
+      <c r="BI122">
+        <v>0</v>
+      </c>
+      <c r="BJ122">
+        <v>0</v>
+      </c>
+      <c r="BK122">
+        <v>1.65</v>
+      </c>
+      <c r="BL122">
+        <v>2.08</v>
+      </c>
+      <c r="BM122">
+        <v>2.02</v>
+      </c>
+      <c r="BN122">
+        <v>1.7</v>
+      </c>
+      <c r="BO122">
+        <v>2.55</v>
+      </c>
+      <c r="BP122">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,12 @@
     <t>['3', '55', '82']</t>
   </si>
   <si>
+    <t>['45+8']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -673,9 +679,6 @@
     <t>['71', '85']</t>
   </si>
   <si>
-    <t>['77']</t>
-  </si>
-  <si>
     <t>['3']</t>
   </si>
   <si>
@@ -758,6 +761,15 @@
   </si>
   <si>
     <t>['76']</t>
+  </si>
+  <si>
+    <t>['11', '23', '78', '89']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['43']</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1453,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1865,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1993,7 +2005,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2199,7 +2211,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2405,7 +2417,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2611,7 +2623,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2692,7 +2704,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ8">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2817,7 +2829,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2898,7 +2910,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ9">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR9">
         <v>1.96</v>
@@ -3104,7 +3116,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3229,7 +3241,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3307,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ11">
         <v>1.6</v>
@@ -3435,7 +3447,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3513,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ12">
         <v>1.3</v>
@@ -3925,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR14">
         <v>1.77</v>
@@ -4337,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR16">
         <v>1.37</v>
@@ -4465,7 +4477,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4543,7 +4555,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17">
         <v>1.7</v>
@@ -4671,7 +4683,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4877,7 +4889,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5289,7 +5301,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5576,7 +5588,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ22">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR22">
         <v>1.44</v>
@@ -5701,7 +5713,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5907,7 +5919,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6113,7 +6125,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6319,7 +6331,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6400,7 +6412,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
         <v>1.11</v>
@@ -6525,7 +6537,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6606,7 +6618,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR27">
         <v>1.35</v>
@@ -6731,7 +6743,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6809,7 +6821,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -6937,7 +6949,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7015,10 +7027,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ29">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR29">
         <v>1.88</v>
@@ -7143,7 +7155,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7221,7 +7233,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ30">
         <v>1.3</v>
@@ -7427,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ31">
         <v>0.36</v>
@@ -7555,7 +7567,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7633,7 +7645,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ32">
         <v>1.3</v>
@@ -7761,7 +7773,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7842,7 +7854,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ33">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR33">
         <v>1.8</v>
@@ -7967,7 +7979,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8173,7 +8185,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8379,7 +8391,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8666,7 +8678,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ37">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR37">
         <v>1.54</v>
@@ -8997,7 +9009,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9075,7 +9087,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9203,7 +9215,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9281,7 +9293,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ40">
         <v>1.3</v>
@@ -9409,7 +9421,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9490,7 +9502,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ41">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -9615,7 +9627,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9693,10 +9705,10 @@
         <v>1.67</v>
       </c>
       <c r="AP42">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ42">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>1.27</v>
@@ -10027,7 +10039,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10105,10 +10117,10 @@
         <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ44">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR44">
         <v>0.9</v>
@@ -10233,7 +10245,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10439,7 +10451,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10517,7 +10529,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
         <v>1.6</v>
@@ -10645,7 +10657,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10726,7 +10738,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ47">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10932,7 +10944,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ48">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR48">
         <v>1.96</v>
@@ -11263,7 +11275,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11675,7 +11687,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11756,7 +11768,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ52">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR52">
         <v>1.41</v>
@@ -12087,7 +12099,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12165,7 +12177,7 @@
         <v>1.75</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ54">
         <v>1.3</v>
@@ -12371,7 +12383,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ55">
         <v>0.6</v>
@@ -12499,7 +12511,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12577,7 +12589,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
         <v>1.7</v>
@@ -12786,7 +12798,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ57">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR57">
         <v>1.87</v>
@@ -12989,10 +13001,10 @@
         <v>0.6</v>
       </c>
       <c r="AP58">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR58">
         <v>1.05</v>
@@ -13117,7 +13129,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13323,7 +13335,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13529,7 +13541,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13735,7 +13747,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13941,7 +13953,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14147,7 +14159,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14228,7 +14240,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR64">
         <v>1.45</v>
@@ -14353,7 +14365,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14640,7 +14652,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR66">
         <v>1.84</v>
@@ -14765,7 +14777,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14843,7 +14855,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ67">
         <v>1.6</v>
@@ -14971,7 +14983,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -15049,7 +15061,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ68">
         <v>0.36</v>
@@ -15258,7 +15270,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ69">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
         <v>1.17</v>
@@ -15383,7 +15395,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15461,7 +15473,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ70">
         <v>1.7</v>
@@ -15589,7 +15601,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15795,7 +15807,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15876,7 +15888,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ72">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16079,7 +16091,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ73">
         <v>1.3</v>
@@ -16285,7 +16297,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
         <v>0.6</v>
@@ -16700,7 +16712,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ76">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR76">
         <v>1.38</v>
@@ -16825,7 +16837,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16906,7 +16918,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ77">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR77">
         <v>1.44</v>
@@ -17443,7 +17455,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17649,7 +17661,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17855,7 +17867,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -17936,7 +17948,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ82">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18061,7 +18073,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18139,10 +18151,10 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ83">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR83">
         <v>1.59</v>
@@ -18267,7 +18279,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18345,7 +18357,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ84">
         <v>0.36</v>
@@ -18473,7 +18485,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18551,7 +18563,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ85">
         <v>1.6</v>
@@ -18760,7 +18772,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ86">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -18963,7 +18975,7 @@
         <v>1.86</v>
       </c>
       <c r="AP87">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ87">
         <v>1.7</v>
@@ -19091,7 +19103,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19378,7 +19390,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19503,7 +19515,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19581,7 +19593,7 @@
         <v>1.57</v>
       </c>
       <c r="AP90">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ90">
         <v>1.6</v>
@@ -19709,7 +19721,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -20405,10 +20417,10 @@
         <v>0.75</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ94">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR94">
         <v>1.41</v>
@@ -20533,7 +20545,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20739,7 +20751,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20817,10 +20829,10 @@
         <v>0.43</v>
       </c>
       <c r="AP96">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ96">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR96">
         <v>1.89</v>
@@ -21357,7 +21369,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21438,7 +21450,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ99">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21563,7 +21575,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21769,7 +21781,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21850,7 +21862,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ101">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -21975,7 +21987,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22053,7 +22065,7 @@
         <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ102">
         <v>1.3</v>
@@ -22259,7 +22271,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -22387,7 +22399,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22468,7 +22480,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ104">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.62</v>
@@ -22593,7 +22605,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22671,7 +22683,7 @@
         <v>0.13</v>
       </c>
       <c r="AP105">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ105">
         <v>0.36</v>
@@ -22799,7 +22811,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23086,7 +23098,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ107">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR107">
         <v>1.68</v>
@@ -23211,7 +23223,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23623,7 +23635,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -23704,7 +23716,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ110">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR110">
         <v>1.63</v>
@@ -23907,7 +23919,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ111">
         <v>0.6</v>
@@ -24035,7 +24047,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24319,10 +24331,10 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ113">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR113">
         <v>1.93</v>
@@ -24447,7 +24459,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24653,7 +24665,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24731,7 +24743,7 @@
         <v>0.88</v>
       </c>
       <c r="AP115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -24859,7 +24871,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25065,7 +25077,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q117">
         <v>2.38</v>
@@ -25271,7 +25283,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25477,7 +25489,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -25761,7 +25773,7 @@
         <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ120">
         <v>1.6</v>
@@ -25970,7 +25982,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ121">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26252,6 +26264,830 @@
       </c>
       <c r="BP122">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7452378</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F123">
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>78</v>
+      </c>
+      <c r="H123" t="s">
+        <v>81</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>3</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>4</v>
+      </c>
+      <c r="N123">
+        <v>5</v>
+      </c>
+      <c r="O123" t="s">
+        <v>177</v>
+      </c>
+      <c r="P123" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q123">
+        <v>4.75</v>
+      </c>
+      <c r="R123">
+        <v>2.38</v>
+      </c>
+      <c r="S123">
+        <v>2.25</v>
+      </c>
+      <c r="T123">
+        <v>1.3</v>
+      </c>
+      <c r="U123">
+        <v>3.4</v>
+      </c>
+      <c r="V123">
+        <v>2.5</v>
+      </c>
+      <c r="W123">
+        <v>1.5</v>
+      </c>
+      <c r="X123">
+        <v>6</v>
+      </c>
+      <c r="Y123">
+        <v>1.13</v>
+      </c>
+      <c r="Z123">
+        <v>3.95</v>
+      </c>
+      <c r="AA123">
+        <v>3.9</v>
+      </c>
+      <c r="AB123">
+        <v>1.78</v>
+      </c>
+      <c r="AC123">
+        <v>1.03</v>
+      </c>
+      <c r="AD123">
+        <v>11</v>
+      </c>
+      <c r="AE123">
+        <v>1.18</v>
+      </c>
+      <c r="AF123">
+        <v>4.75</v>
+      </c>
+      <c r="AG123">
+        <v>1.55</v>
+      </c>
+      <c r="AH123">
+        <v>2.2</v>
+      </c>
+      <c r="AI123">
+        <v>1.67</v>
+      </c>
+      <c r="AJ123">
+        <v>2.1</v>
+      </c>
+      <c r="AK123">
+        <v>2.05</v>
+      </c>
+      <c r="AL123">
+        <v>1.18</v>
+      </c>
+      <c r="AM123">
+        <v>1.22</v>
+      </c>
+      <c r="AN123">
+        <v>1.2</v>
+      </c>
+      <c r="AO123">
+        <v>1.2</v>
+      </c>
+      <c r="AP123">
+        <v>1.09</v>
+      </c>
+      <c r="AQ123">
+        <v>1.36</v>
+      </c>
+      <c r="AR123">
+        <v>1.31</v>
+      </c>
+      <c r="AS123">
+        <v>1.53</v>
+      </c>
+      <c r="AT123">
+        <v>2.84</v>
+      </c>
+      <c r="AU123">
+        <v>4</v>
+      </c>
+      <c r="AV123">
+        <v>10</v>
+      </c>
+      <c r="AW123">
+        <v>9</v>
+      </c>
+      <c r="AX123">
+        <v>18</v>
+      </c>
+      <c r="AY123">
+        <v>17</v>
+      </c>
+      <c r="AZ123">
+        <v>35</v>
+      </c>
+      <c r="BA123">
+        <v>8</v>
+      </c>
+      <c r="BB123">
+        <v>7</v>
+      </c>
+      <c r="BC123">
+        <v>15</v>
+      </c>
+      <c r="BD123">
+        <v>2.9</v>
+      </c>
+      <c r="BE123">
+        <v>6.75</v>
+      </c>
+      <c r="BF123">
+        <v>1.48</v>
+      </c>
+      <c r="BG123">
+        <v>1.26</v>
+      </c>
+      <c r="BH123">
+        <v>3.4</v>
+      </c>
+      <c r="BI123">
+        <v>1.46</v>
+      </c>
+      <c r="BJ123">
+        <v>2.5</v>
+      </c>
+      <c r="BK123">
+        <v>1.73</v>
+      </c>
+      <c r="BL123">
+        <v>1.96</v>
+      </c>
+      <c r="BM123">
+        <v>2.15</v>
+      </c>
+      <c r="BN123">
+        <v>1.61</v>
+      </c>
+      <c r="BO123">
+        <v>2.7</v>
+      </c>
+      <c r="BP123">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7452380</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F124">
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>72</v>
+      </c>
+      <c r="H124" t="s">
+        <v>75</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>87</v>
+      </c>
+      <c r="P124" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q124">
+        <v>2.38</v>
+      </c>
+      <c r="R124">
+        <v>2.2</v>
+      </c>
+      <c r="S124">
+        <v>5</v>
+      </c>
+      <c r="T124">
+        <v>1.4</v>
+      </c>
+      <c r="U124">
+        <v>2.75</v>
+      </c>
+      <c r="V124">
+        <v>3</v>
+      </c>
+      <c r="W124">
+        <v>1.36</v>
+      </c>
+      <c r="X124">
+        <v>8</v>
+      </c>
+      <c r="Y124">
+        <v>1.08</v>
+      </c>
+      <c r="Z124">
+        <v>1.61</v>
+      </c>
+      <c r="AA124">
+        <v>4</v>
+      </c>
+      <c r="AB124">
+        <v>5</v>
+      </c>
+      <c r="AC124">
+        <v>1.02</v>
+      </c>
+      <c r="AD124">
+        <v>10</v>
+      </c>
+      <c r="AE124">
+        <v>1.29</v>
+      </c>
+      <c r="AF124">
+        <v>3.3</v>
+      </c>
+      <c r="AG124">
+        <v>1.89</v>
+      </c>
+      <c r="AH124">
+        <v>1.85</v>
+      </c>
+      <c r="AI124">
+        <v>1.91</v>
+      </c>
+      <c r="AJ124">
+        <v>1.91</v>
+      </c>
+      <c r="AK124">
+        <v>1.2</v>
+      </c>
+      <c r="AL124">
+        <v>1.26</v>
+      </c>
+      <c r="AM124">
+        <v>2.05</v>
+      </c>
+      <c r="AN124">
+        <v>1.6</v>
+      </c>
+      <c r="AO124">
+        <v>0.4</v>
+      </c>
+      <c r="AP124">
+        <v>1.45</v>
+      </c>
+      <c r="AQ124">
+        <v>0.64</v>
+      </c>
+      <c r="AR124">
+        <v>1.29</v>
+      </c>
+      <c r="AS124">
+        <v>1.16</v>
+      </c>
+      <c r="AT124">
+        <v>2.45</v>
+      </c>
+      <c r="AU124">
+        <v>7</v>
+      </c>
+      <c r="AV124">
+        <v>4</v>
+      </c>
+      <c r="AW124">
+        <v>17</v>
+      </c>
+      <c r="AX124">
+        <v>5</v>
+      </c>
+      <c r="AY124">
+        <v>30</v>
+      </c>
+      <c r="AZ124">
+        <v>10</v>
+      </c>
+      <c r="BA124">
+        <v>6</v>
+      </c>
+      <c r="BB124">
+        <v>4</v>
+      </c>
+      <c r="BC124">
+        <v>10</v>
+      </c>
+      <c r="BD124">
+        <v>1.52</v>
+      </c>
+      <c r="BE124">
+        <v>6.75</v>
+      </c>
+      <c r="BF124">
+        <v>2.8</v>
+      </c>
+      <c r="BG124">
+        <v>1.3</v>
+      </c>
+      <c r="BH124">
+        <v>3.05</v>
+      </c>
+      <c r="BI124">
+        <v>1.54</v>
+      </c>
+      <c r="BJ124">
+        <v>2.3</v>
+      </c>
+      <c r="BK124">
+        <v>1.88</v>
+      </c>
+      <c r="BL124">
+        <v>1.81</v>
+      </c>
+      <c r="BM124">
+        <v>2.33</v>
+      </c>
+      <c r="BN124">
+        <v>1.5</v>
+      </c>
+      <c r="BO124">
+        <v>3.05</v>
+      </c>
+      <c r="BP124">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7452375</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45725.5</v>
+      </c>
+      <c r="F125">
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>70</v>
+      </c>
+      <c r="H125" t="s">
+        <v>74</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>178</v>
+      </c>
+      <c r="P125" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q125">
+        <v>2.25</v>
+      </c>
+      <c r="R125">
+        <v>2.25</v>
+      </c>
+      <c r="S125">
+        <v>5</v>
+      </c>
+      <c r="T125">
+        <v>1.36</v>
+      </c>
+      <c r="U125">
+        <v>3</v>
+      </c>
+      <c r="V125">
+        <v>2.75</v>
+      </c>
+      <c r="W125">
+        <v>1.4</v>
+      </c>
+      <c r="X125">
+        <v>8</v>
+      </c>
+      <c r="Y125">
+        <v>1.08</v>
+      </c>
+      <c r="Z125">
+        <v>1.6</v>
+      </c>
+      <c r="AA125">
+        <v>3.95</v>
+      </c>
+      <c r="AB125">
+        <v>5.3</v>
+      </c>
+      <c r="AC125">
+        <v>1.05</v>
+      </c>
+      <c r="AD125">
+        <v>9.5</v>
+      </c>
+      <c r="AE125">
+        <v>1.25</v>
+      </c>
+      <c r="AF125">
+        <v>3.7</v>
+      </c>
+      <c r="AG125">
+        <v>1.77</v>
+      </c>
+      <c r="AH125">
+        <v>1.98</v>
+      </c>
+      <c r="AI125">
+        <v>1.91</v>
+      </c>
+      <c r="AJ125">
+        <v>1.91</v>
+      </c>
+      <c r="AK125">
+        <v>1.15</v>
+      </c>
+      <c r="AL125">
+        <v>1.2</v>
+      </c>
+      <c r="AM125">
+        <v>2.25</v>
+      </c>
+      <c r="AN125">
+        <v>2.2</v>
+      </c>
+      <c r="AO125">
+        <v>0.7</v>
+      </c>
+      <c r="AP125">
+        <v>2.09</v>
+      </c>
+      <c r="AQ125">
+        <v>0.73</v>
+      </c>
+      <c r="AR125">
+        <v>1.82</v>
+      </c>
+      <c r="AS125">
+        <v>1.44</v>
+      </c>
+      <c r="AT125">
+        <v>3.26</v>
+      </c>
+      <c r="AU125">
+        <v>10</v>
+      </c>
+      <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
+        <v>13</v>
+      </c>
+      <c r="AX125">
+        <v>5</v>
+      </c>
+      <c r="AY125">
+        <v>28</v>
+      </c>
+      <c r="AZ125">
+        <v>10</v>
+      </c>
+      <c r="BA125">
+        <v>8</v>
+      </c>
+      <c r="BB125">
+        <v>1</v>
+      </c>
+      <c r="BC125">
+        <v>9</v>
+      </c>
+      <c r="BD125">
+        <v>1.34</v>
+      </c>
+      <c r="BE125">
+        <v>7.5</v>
+      </c>
+      <c r="BF125">
+        <v>3.45</v>
+      </c>
+      <c r="BG125">
+        <v>1.19</v>
+      </c>
+      <c r="BH125">
+        <v>4</v>
+      </c>
+      <c r="BI125">
+        <v>1.34</v>
+      </c>
+      <c r="BJ125">
+        <v>2.9</v>
+      </c>
+      <c r="BK125">
+        <v>1.56</v>
+      </c>
+      <c r="BL125">
+        <v>2.23</v>
+      </c>
+      <c r="BM125">
+        <v>1.88</v>
+      </c>
+      <c r="BN125">
+        <v>1.8</v>
+      </c>
+      <c r="BO125">
+        <v>2.33</v>
+      </c>
+      <c r="BP125">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7452376</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>76</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>2</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>82</v>
+      </c>
+      <c r="P126" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q126">
+        <v>1.73</v>
+      </c>
+      <c r="R126">
+        <v>2.75</v>
+      </c>
+      <c r="S126">
+        <v>7.5</v>
+      </c>
+      <c r="T126">
+        <v>1.25</v>
+      </c>
+      <c r="U126">
+        <v>3.75</v>
+      </c>
+      <c r="V126">
+        <v>2.2</v>
+      </c>
+      <c r="W126">
+        <v>1.62</v>
+      </c>
+      <c r="X126">
+        <v>5</v>
+      </c>
+      <c r="Y126">
+        <v>1.17</v>
+      </c>
+      <c r="Z126">
+        <v>1.3</v>
+      </c>
+      <c r="AA126">
+        <v>5.4</v>
+      </c>
+      <c r="AB126">
+        <v>8.6</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>17</v>
+      </c>
+      <c r="AE126">
+        <v>1.15</v>
+      </c>
+      <c r="AF126">
+        <v>5.25</v>
+      </c>
+      <c r="AG126">
+        <v>1.46</v>
+      </c>
+      <c r="AH126">
+        <v>2.6</v>
+      </c>
+      <c r="AI126">
+        <v>1.91</v>
+      </c>
+      <c r="AJ126">
+        <v>1.91</v>
+      </c>
+      <c r="AK126">
+        <v>1.06</v>
+      </c>
+      <c r="AL126">
+        <v>1.1</v>
+      </c>
+      <c r="AM126">
+        <v>3.4</v>
+      </c>
+      <c r="AN126">
+        <v>2.4</v>
+      </c>
+      <c r="AO126">
+        <v>0.7</v>
+      </c>
+      <c r="AP126">
+        <v>2.27</v>
+      </c>
+      <c r="AQ126">
+        <v>0.73</v>
+      </c>
+      <c r="AR126">
+        <v>1.92</v>
+      </c>
+      <c r="AS126">
+        <v>1.28</v>
+      </c>
+      <c r="AT126">
+        <v>3.2</v>
+      </c>
+      <c r="AU126">
+        <v>9</v>
+      </c>
+      <c r="AV126">
+        <v>3</v>
+      </c>
+      <c r="AW126">
+        <v>6</v>
+      </c>
+      <c r="AX126">
+        <v>4</v>
+      </c>
+      <c r="AY126">
+        <v>15</v>
+      </c>
+      <c r="AZ126">
+        <v>7</v>
+      </c>
+      <c r="BA126">
+        <v>3</v>
+      </c>
+      <c r="BB126">
+        <v>3</v>
+      </c>
+      <c r="BC126">
+        <v>6</v>
+      </c>
+      <c r="BD126">
+        <v>1.25</v>
+      </c>
+      <c r="BE126">
+        <v>7.5</v>
+      </c>
+      <c r="BF126">
+        <v>4.3</v>
+      </c>
+      <c r="BG126">
+        <v>1.24</v>
+      </c>
+      <c r="BH126">
+        <v>3.55</v>
+      </c>
+      <c r="BI126">
+        <v>1.43</v>
+      </c>
+      <c r="BJ126">
+        <v>2.55</v>
+      </c>
+      <c r="BK126">
+        <v>1.68</v>
+      </c>
+      <c r="BL126">
+        <v>2.02</v>
+      </c>
+      <c r="BM126">
+        <v>2.06</v>
+      </c>
+      <c r="BN126">
+        <v>1.66</v>
+      </c>
+      <c r="BO126">
+        <v>2.65</v>
+      </c>
+      <c r="BP126">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="254">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,9 @@
     <t>['77']</t>
   </si>
   <si>
+    <t>['48', '59', '69', '90+2']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -770,6 +773,9 @@
   </si>
   <si>
     <t>['43']</t>
+  </si>
+  <si>
+    <t>['54', '74']</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2005,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2211,7 +2217,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2292,7 +2298,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2417,7 +2423,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2623,7 +2629,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2829,7 +2835,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3113,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10">
         <v>0.73</v>
@@ -3241,7 +3247,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3447,7 +3453,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4477,7 +4483,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4683,7 +4689,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4764,7 +4770,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR18">
         <v>1.15</v>
@@ -4889,7 +4895,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5301,7 +5307,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5379,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -5713,7 +5719,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5919,7 +5925,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6125,7 +6131,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6331,7 +6337,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6537,7 +6543,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6615,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ27">
         <v>0.73</v>
@@ -6743,7 +6749,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6949,7 +6955,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7155,7 +7161,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7236,7 +7242,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ30">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR30">
         <v>1.16</v>
@@ -7567,7 +7573,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7773,7 +7779,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7979,7 +7985,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8185,7 +8191,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8391,7 +8397,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9009,7 +9015,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9215,7 +9221,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9296,7 +9302,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ40">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR40">
         <v>1.87</v>
@@ -9421,7 +9427,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9627,7 +9633,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9911,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
         <v>0.6</v>
@@ -10039,7 +10045,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10245,7 +10251,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10451,7 +10457,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10657,7 +10663,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11275,7 +11281,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11687,7 +11693,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11765,7 +11771,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ52">
         <v>1.36</v>
@@ -12099,7 +12105,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12180,7 +12186,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ54">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12511,7 +12517,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13129,7 +13135,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13335,7 +13341,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13541,7 +13547,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13622,7 +13628,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
         <v>1.74</v>
@@ -13747,7 +13753,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13953,7 +13959,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14159,7 +14165,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14237,7 +14243,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ64">
         <v>0.64</v>
@@ -14365,7 +14371,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14777,7 +14783,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -15395,7 +15401,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15601,7 +15607,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15807,7 +15813,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16094,7 +16100,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ73">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR73">
         <v>1.58</v>
@@ -16837,7 +16843,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17327,7 +17333,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17455,7 +17461,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17661,7 +17667,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17742,7 +17748,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ81">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR81">
         <v>1.78</v>
@@ -17867,7 +17873,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18073,7 +18079,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18279,7 +18285,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18485,7 +18491,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19103,7 +19109,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19515,7 +19521,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19721,7 +19727,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -20211,7 +20217,7 @@
         <v>0.14</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ93">
         <v>0.36</v>
@@ -20545,7 +20551,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20626,7 +20632,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ95">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -20751,7 +20757,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21369,7 +21375,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21575,7 +21581,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21781,7 +21787,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21987,7 +21993,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22399,7 +22405,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22605,7 +22611,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22811,7 +22817,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23223,7 +23229,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23301,7 +23307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
         <v>1.6</v>
@@ -23635,7 +23641,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -24047,7 +24053,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24128,7 +24134,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ112">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR112">
         <v>1.42</v>
@@ -24459,7 +24465,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24665,7 +24671,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24871,7 +24877,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -24949,7 +24955,7 @@
         <v>1.33</v>
       </c>
       <c r="AP116">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ116">
         <v>1.3</v>
@@ -25077,7 +25083,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q117">
         <v>2.38</v>
@@ -25283,7 +25289,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25489,7 +25495,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -26313,7 +26319,7 @@
         <v>177</v>
       </c>
       <c r="P123" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26519,7 +26525,7 @@
         <v>87</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26725,7 +26731,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -26931,7 +26937,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27088,6 +27094,212 @@
       </c>
       <c r="BP126">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7452379</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45726.625</v>
+      </c>
+      <c r="F127">
+        <v>21</v>
+      </c>
+      <c r="G127" t="s">
+        <v>77</v>
+      </c>
+      <c r="H127" t="s">
+        <v>80</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>4</v>
+      </c>
+      <c r="M127">
+        <v>2</v>
+      </c>
+      <c r="N127">
+        <v>6</v>
+      </c>
+      <c r="O127" t="s">
+        <v>179</v>
+      </c>
+      <c r="P127" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q127">
+        <v>3.5</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>2.88</v>
+      </c>
+      <c r="T127">
+        <v>1.36</v>
+      </c>
+      <c r="U127">
+        <v>3</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.1</v>
+      </c>
+      <c r="Z127">
+        <v>2.96</v>
+      </c>
+      <c r="AA127">
+        <v>3.41</v>
+      </c>
+      <c r="AB127">
+        <v>2.27</v>
+      </c>
+      <c r="AC127">
+        <v>1.02</v>
+      </c>
+      <c r="AD127">
+        <v>10</v>
+      </c>
+      <c r="AE127">
+        <v>1.25</v>
+      </c>
+      <c r="AF127">
+        <v>3.6</v>
+      </c>
+      <c r="AG127">
+        <v>1.77</v>
+      </c>
+      <c r="AH127">
+        <v>1.98</v>
+      </c>
+      <c r="AI127">
+        <v>1.67</v>
+      </c>
+      <c r="AJ127">
+        <v>2.1</v>
+      </c>
+      <c r="AK127">
+        <v>1.62</v>
+      </c>
+      <c r="AL127">
+        <v>1.3</v>
+      </c>
+      <c r="AM127">
+        <v>1.4</v>
+      </c>
+      <c r="AN127">
+        <v>1.5</v>
+      </c>
+      <c r="AO127">
+        <v>1.3</v>
+      </c>
+      <c r="AP127">
+        <v>1.64</v>
+      </c>
+      <c r="AQ127">
+        <v>1.18</v>
+      </c>
+      <c r="AR127">
+        <v>1.45</v>
+      </c>
+      <c r="AS127">
+        <v>1.78</v>
+      </c>
+      <c r="AT127">
+        <v>3.23</v>
+      </c>
+      <c r="AU127">
+        <v>7</v>
+      </c>
+      <c r="AV127">
+        <v>6</v>
+      </c>
+      <c r="AW127">
+        <v>2</v>
+      </c>
+      <c r="AX127">
+        <v>10</v>
+      </c>
+      <c r="AY127">
+        <v>9</v>
+      </c>
+      <c r="AZ127">
+        <v>16</v>
+      </c>
+      <c r="BA127">
+        <v>4</v>
+      </c>
+      <c r="BB127">
+        <v>2</v>
+      </c>
+      <c r="BC127">
+        <v>6</v>
+      </c>
+      <c r="BD127">
+        <v>2.2</v>
+      </c>
+      <c r="BE127">
+        <v>6.75</v>
+      </c>
+      <c r="BF127">
+        <v>1.79</v>
+      </c>
+      <c r="BG127">
+        <v>1.23</v>
+      </c>
+      <c r="BH127">
+        <v>3.65</v>
+      </c>
+      <c r="BI127">
+        <v>1.41</v>
+      </c>
+      <c r="BJ127">
+        <v>2.65</v>
+      </c>
+      <c r="BK127">
+        <v>1.66</v>
+      </c>
+      <c r="BL127">
+        <v>2.06</v>
+      </c>
+      <c r="BM127">
+        <v>2.04</v>
+      </c>
+      <c r="BN127">
+        <v>1.67</v>
+      </c>
+      <c r="BO127">
+        <v>2.55</v>
+      </c>
+      <c r="BP127">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -27248,10 +27248,10 @@
         <v>10</v>
       </c>
       <c r="AY127">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ127">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA127">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -556,6 +556,21 @@
     <t>['48', '59', '69', '90+2']</t>
   </si>
   <si>
+    <t>['26', '77']</t>
+  </si>
+  <si>
+    <t>['5', '14', '18', '74']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['42', '44', '81']</t>
+  </si>
+  <si>
+    <t>['48', '60', '66']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -776,6 +791,21 @@
   </si>
   <si>
     <t>['54', '74']</t>
+  </si>
+  <si>
+    <t>['11', '36']</t>
+  </si>
+  <si>
+    <t>['50', '59']</t>
+  </si>
+  <si>
+    <t>['31', '89']</t>
+  </si>
+  <si>
+    <t>['26', '41']</t>
+  </si>
+  <si>
+    <t>['12', '47', '60']</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1680,7 +1710,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ3">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2011,7 +2041,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2089,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ5">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2217,7 +2247,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2295,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>1.18</v>
@@ -2423,7 +2453,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2501,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2629,7 +2659,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2707,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -2835,7 +2865,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3247,7 +3277,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3328,7 +3358,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ11">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3453,7 +3483,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3534,7 +3564,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ12">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3737,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
         <v>0.36</v>
@@ -4149,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ15">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4483,7 +4513,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4564,7 +4594,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ17">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR17">
         <v>1.41</v>
@@ -4689,7 +4719,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4767,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>1.18</v>
@@ -4895,7 +4925,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -4973,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR19">
         <v>1.07</v>
@@ -5179,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ20">
         <v>0.36</v>
@@ -5307,7 +5337,7 @@
         <v>87</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -5388,7 +5418,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5719,7 +5749,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5797,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR23">
         <v>1.53</v>
@@ -5925,7 +5955,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6003,10 +6033,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR24">
         <v>1.85</v>
@@ -6131,7 +6161,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6209,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR25">
         <v>0.91</v>
@@ -6337,7 +6367,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6415,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>1.36</v>
@@ -6543,7 +6573,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6749,7 +6779,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6830,7 +6860,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR28">
         <v>1.19</v>
@@ -6955,7 +6985,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7161,7 +7191,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7573,7 +7603,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7654,7 +7684,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ32">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR32">
         <v>1.14</v>
@@ -7779,7 +7809,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7857,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ33">
         <v>0.73</v>
@@ -7985,7 +8015,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8063,10 +8093,10 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ34">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8191,7 +8221,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8272,7 +8302,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ35">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR35">
         <v>1.81</v>
@@ -8397,7 +8427,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8475,10 +8505,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ36">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR36">
         <v>1.69</v>
@@ -8681,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ37">
         <v>0.64</v>
@@ -8887,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>0.36</v>
@@ -9015,7 +9045,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9096,7 +9126,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>1.84</v>
@@ -9221,7 +9251,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
@@ -9427,7 +9457,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9505,7 +9535,7 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ41">
         <v>0.73</v>
@@ -9633,7 +9663,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9920,7 +9950,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -10045,7 +10075,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10251,7 +10281,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10329,10 +10359,10 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ45">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR45">
         <v>1.88</v>
@@ -10457,7 +10487,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10538,7 +10568,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ46">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10663,7 +10693,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10741,7 +10771,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ47">
         <v>0.73</v>
@@ -10947,7 +10977,7 @@
         <v>0.75</v>
       </c>
       <c r="AP48">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ48">
         <v>0.73</v>
@@ -11156,7 +11186,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR49">
         <v>1.79</v>
@@ -11281,7 +11311,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11359,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR50">
         <v>1.51</v>
@@ -11565,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ51">
         <v>0.36</v>
@@ -11693,7 +11723,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11977,10 +12007,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR53">
         <v>1.13</v>
@@ -12105,7 +12135,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12392,7 +12422,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ55">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR55">
         <v>1.59</v>
@@ -12517,7 +12547,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12598,7 +12628,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ56">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12801,7 +12831,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ57">
         <v>0.73</v>
@@ -13135,7 +13165,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13213,10 +13243,10 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR59">
         <v>1.04</v>
@@ -13341,7 +13371,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13419,10 +13449,10 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR60">
         <v>1.56</v>
@@ -13547,7 +13577,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13753,7 +13783,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13831,10 +13861,10 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ62">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR62">
         <v>1.34</v>
@@ -13959,7 +13989,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14037,10 +14067,10 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR63">
         <v>1.52</v>
@@ -14165,7 +14195,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14371,7 +14401,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14449,10 +14479,10 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ65">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14655,7 +14685,7 @@
         <v>1.8</v>
       </c>
       <c r="AP66">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ66">
         <v>1.36</v>
@@ -14783,7 +14813,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14864,7 +14894,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ67">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR67">
         <v>1.23</v>
@@ -15273,7 +15303,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
         <v>0.73</v>
@@ -15401,7 +15431,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15482,7 +15512,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ70">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR70">
         <v>1.17</v>
@@ -15607,7 +15637,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15688,7 +15718,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ71">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -15813,7 +15843,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15891,7 +15921,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -16306,7 +16336,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ74">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16509,10 +16539,10 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR75">
         <v>1.81</v>
@@ -16715,7 +16745,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ76">
         <v>0.64</v>
@@ -16843,7 +16873,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16921,7 +16951,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ77">
         <v>0.73</v>
@@ -17127,10 +17157,10 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ78">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR78">
         <v>1.92</v>
@@ -17336,7 +17366,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17461,7 +17491,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17539,10 +17569,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ80">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR80">
         <v>1.37</v>
@@ -17667,7 +17697,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17745,7 +17775,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ81">
         <v>1.18</v>
@@ -17873,7 +17903,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q82">
         <v>2</v>
@@ -18079,7 +18109,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18285,7 +18315,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18491,7 +18521,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18572,7 +18602,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ85">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -18775,7 +18805,7 @@
         <v>0.43</v>
       </c>
       <c r="AP86">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ86">
         <v>0.73</v>
@@ -18984,7 +19014,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ87">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19109,7 +19139,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19187,10 +19217,10 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR88">
         <v>1.19</v>
@@ -19393,7 +19423,7 @@
         <v>1.29</v>
       </c>
       <c r="AP89">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ89">
         <v>1.36</v>
@@ -19521,7 +19551,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19602,7 +19632,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ90">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR90">
         <v>1.66</v>
@@ -19727,7 +19757,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19805,10 +19835,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR91">
         <v>1.65</v>
@@ -20014,7 +20044,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ92">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR92">
         <v>1.68</v>
@@ -20551,7 +20581,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20629,7 +20659,7 @@
         <v>1.38</v>
       </c>
       <c r="AP95">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ95">
         <v>1.18</v>
@@ -20757,7 +20787,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21041,10 +21071,10 @@
         <v>1.43</v>
       </c>
       <c r="AP97">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ97">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR97">
         <v>1.78</v>
@@ -21247,10 +21277,10 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ98">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR98">
         <v>1.56</v>
@@ -21375,7 +21405,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21453,7 +21483,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>0.73</v>
@@ -21581,7 +21611,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21659,10 +21689,10 @@
         <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -21787,7 +21817,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21865,7 +21895,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ101">
         <v>1.36</v>
@@ -21993,7 +22023,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22074,7 +22104,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ102">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR102">
         <v>1.25</v>
@@ -22280,7 +22310,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR103">
         <v>2.05</v>
@@ -22405,7 +22435,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22483,7 +22513,7 @@
         <v>0.78</v>
       </c>
       <c r="AP104">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ104">
         <v>0.73</v>
@@ -22611,7 +22641,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22817,7 +22847,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -22895,10 +22925,10 @@
         <v>1.13</v>
       </c>
       <c r="AP106">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ106">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR106">
         <v>1.4</v>
@@ -23101,7 +23131,7 @@
         <v>0.38</v>
       </c>
       <c r="AP107">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ107">
         <v>0.64</v>
@@ -23229,7 +23259,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23310,7 +23340,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR108">
         <v>1.51</v>
@@ -23513,10 +23543,10 @@
         <v>1.78</v>
       </c>
       <c r="AP109">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ109">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR109">
         <v>1.19</v>
@@ -23641,7 +23671,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q110">
         <v>1.83</v>
@@ -23928,7 +23958,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ111">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -24053,7 +24083,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24131,7 +24161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ112">
         <v>1.18</v>
@@ -24465,7 +24495,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24543,10 +24573,10 @@
         <v>1.25</v>
       </c>
       <c r="AP114">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ114">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR114">
         <v>1.41</v>
@@ -24671,7 +24701,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24752,7 +24782,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR115">
         <v>1.35</v>
@@ -24877,7 +24907,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -24958,7 +24988,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR116">
         <v>1.48</v>
@@ -25083,7 +25113,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q117">
         <v>2.38</v>
@@ -25161,7 +25191,7 @@
         <v>0.44</v>
       </c>
       <c r="AP117">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ117">
         <v>0.36</v>
@@ -25289,7 +25319,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q118">
         <v>3.6</v>
@@ -25367,10 +25397,10 @@
         <v>1.44</v>
       </c>
       <c r="AP118">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ118">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR118">
         <v>1.38</v>
@@ -25495,7 +25525,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -25573,10 +25603,10 @@
         <v>1.11</v>
       </c>
       <c r="AP119">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
         <v>1.65</v>
@@ -25782,7 +25812,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ120">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR120">
         <v>1.35</v>
@@ -25985,7 +26015,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>0.64</v>
@@ -26319,7 +26349,7 @@
         <v>177</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26525,7 +26555,7 @@
         <v>87</v>
       </c>
       <c r="P124" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26731,7 +26761,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -26937,7 +26967,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27143,7 +27173,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>3.5</v>
@@ -27300,6 +27330,1242 @@
       </c>
       <c r="BP127">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7452381</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>80</v>
+      </c>
+      <c r="H128" t="s">
+        <v>72</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>3</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>4</v>
+      </c>
+      <c r="O128" t="s">
+        <v>180</v>
+      </c>
+      <c r="P128" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q128">
+        <v>2.25</v>
+      </c>
+      <c r="R128">
+        <v>2.38</v>
+      </c>
+      <c r="S128">
+        <v>4.5</v>
+      </c>
+      <c r="T128">
+        <v>1.3</v>
+      </c>
+      <c r="U128">
+        <v>3.4</v>
+      </c>
+      <c r="V128">
+        <v>2.5</v>
+      </c>
+      <c r="W128">
+        <v>1.5</v>
+      </c>
+      <c r="X128">
+        <v>6</v>
+      </c>
+      <c r="Y128">
+        <v>1.13</v>
+      </c>
+      <c r="Z128">
+        <v>1.58</v>
+      </c>
+      <c r="AA128">
+        <v>4.2</v>
+      </c>
+      <c r="AB128">
+        <v>5.1</v>
+      </c>
+      <c r="AC128">
+        <v>1.03</v>
+      </c>
+      <c r="AD128">
+        <v>11</v>
+      </c>
+      <c r="AE128">
+        <v>1.2</v>
+      </c>
+      <c r="AF128">
+        <v>4.5</v>
+      </c>
+      <c r="AG128">
+        <v>1.61</v>
+      </c>
+      <c r="AH128">
+        <v>2.1</v>
+      </c>
+      <c r="AI128">
+        <v>1.62</v>
+      </c>
+      <c r="AJ128">
+        <v>2.2</v>
+      </c>
+      <c r="AK128">
+        <v>1.2</v>
+      </c>
+      <c r="AL128">
+        <v>1.23</v>
+      </c>
+      <c r="AM128">
+        <v>2.1</v>
+      </c>
+      <c r="AN128">
+        <v>1.9</v>
+      </c>
+      <c r="AO128">
+        <v>1.6</v>
+      </c>
+      <c r="AP128">
+        <v>1.82</v>
+      </c>
+      <c r="AQ128">
+        <v>1.55</v>
+      </c>
+      <c r="AR128">
+        <v>1.76</v>
+      </c>
+      <c r="AS128">
+        <v>1.41</v>
+      </c>
+      <c r="AT128">
+        <v>3.17</v>
+      </c>
+      <c r="AU128">
+        <v>8</v>
+      </c>
+      <c r="AV128">
+        <v>4</v>
+      </c>
+      <c r="AW128">
+        <v>14</v>
+      </c>
+      <c r="AX128">
+        <v>4</v>
+      </c>
+      <c r="AY128">
+        <v>22</v>
+      </c>
+      <c r="AZ128">
+        <v>8</v>
+      </c>
+      <c r="BA128">
+        <v>7</v>
+      </c>
+      <c r="BB128">
+        <v>1</v>
+      </c>
+      <c r="BC128">
+        <v>8</v>
+      </c>
+      <c r="BD128">
+        <v>1.57</v>
+      </c>
+      <c r="BE128">
+        <v>9</v>
+      </c>
+      <c r="BF128">
+        <v>2.62</v>
+      </c>
+      <c r="BG128">
+        <v>1.21</v>
+      </c>
+      <c r="BH128">
+        <v>3.8</v>
+      </c>
+      <c r="BI128">
+        <v>1.41</v>
+      </c>
+      <c r="BJ128">
+        <v>2.6</v>
+      </c>
+      <c r="BK128">
+        <v>1.73</v>
+      </c>
+      <c r="BL128">
+        <v>1.93</v>
+      </c>
+      <c r="BM128">
+        <v>2.25</v>
+      </c>
+      <c r="BN128">
+        <v>1.53</v>
+      </c>
+      <c r="BO128">
+        <v>3</v>
+      </c>
+      <c r="BP128">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7452382</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>81</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>3</v>
+      </c>
+      <c r="L129">
+        <v>4</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>6</v>
+      </c>
+      <c r="O129" t="s">
+        <v>181</v>
+      </c>
+      <c r="P129" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q129">
+        <v>2.25</v>
+      </c>
+      <c r="R129">
+        <v>2.3</v>
+      </c>
+      <c r="S129">
+        <v>5</v>
+      </c>
+      <c r="T129">
+        <v>1.33</v>
+      </c>
+      <c r="U129">
+        <v>3.25</v>
+      </c>
+      <c r="V129">
+        <v>2.63</v>
+      </c>
+      <c r="W129">
+        <v>1.44</v>
+      </c>
+      <c r="X129">
+        <v>6.5</v>
+      </c>
+      <c r="Y129">
+        <v>1.11</v>
+      </c>
+      <c r="Z129">
+        <v>1.85</v>
+      </c>
+      <c r="AA129">
+        <v>3.66</v>
+      </c>
+      <c r="AB129">
+        <v>3.92</v>
+      </c>
+      <c r="AC129">
+        <v>1.04</v>
+      </c>
+      <c r="AD129">
+        <v>10</v>
+      </c>
+      <c r="AE129">
+        <v>1.22</v>
+      </c>
+      <c r="AF129">
+        <v>4</v>
+      </c>
+      <c r="AG129">
+        <v>1.8</v>
+      </c>
+      <c r="AH129">
+        <v>1.94</v>
+      </c>
+      <c r="AI129">
+        <v>1.75</v>
+      </c>
+      <c r="AJ129">
+        <v>2</v>
+      </c>
+      <c r="AK129">
+        <v>1.19</v>
+      </c>
+      <c r="AL129">
+        <v>1.24</v>
+      </c>
+      <c r="AM129">
+        <v>2.1</v>
+      </c>
+      <c r="AN129">
+        <v>2.7</v>
+      </c>
+      <c r="AO129">
+        <v>1.7</v>
+      </c>
+      <c r="AP129">
+        <v>2.73</v>
+      </c>
+      <c r="AQ129">
+        <v>1.55</v>
+      </c>
+      <c r="AR129">
+        <v>1.73</v>
+      </c>
+      <c r="AS129">
+        <v>1.33</v>
+      </c>
+      <c r="AT129">
+        <v>3.06</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>5</v>
+      </c>
+      <c r="AW129">
+        <v>5</v>
+      </c>
+      <c r="AX129">
+        <v>6</v>
+      </c>
+      <c r="AY129">
+        <v>17</v>
+      </c>
+      <c r="AZ129">
+        <v>15</v>
+      </c>
+      <c r="BA129">
+        <v>5</v>
+      </c>
+      <c r="BB129">
+        <v>2</v>
+      </c>
+      <c r="BC129">
+        <v>7</v>
+      </c>
+      <c r="BD129">
+        <v>1.53</v>
+      </c>
+      <c r="BE129">
+        <v>9</v>
+      </c>
+      <c r="BF129">
+        <v>2.75</v>
+      </c>
+      <c r="BG129">
+        <v>1.12</v>
+      </c>
+      <c r="BH129">
+        <v>4.75</v>
+      </c>
+      <c r="BI129">
+        <v>1.28</v>
+      </c>
+      <c r="BJ129">
+        <v>3.2</v>
+      </c>
+      <c r="BK129">
+        <v>1.52</v>
+      </c>
+      <c r="BL129">
+        <v>2.25</v>
+      </c>
+      <c r="BM129">
+        <v>1.9</v>
+      </c>
+      <c r="BN129">
+        <v>1.75</v>
+      </c>
+      <c r="BO129">
+        <v>2.5</v>
+      </c>
+      <c r="BP129">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7452383</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>75</v>
+      </c>
+      <c r="H130" t="s">
+        <v>71</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
+        <v>182</v>
+      </c>
+      <c r="P130" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q130">
+        <v>4.75</v>
+      </c>
+      <c r="R130">
+        <v>2.3</v>
+      </c>
+      <c r="S130">
+        <v>2.3</v>
+      </c>
+      <c r="T130">
+        <v>1.33</v>
+      </c>
+      <c r="U130">
+        <v>3.25</v>
+      </c>
+      <c r="V130">
+        <v>2.63</v>
+      </c>
+      <c r="W130">
+        <v>1.44</v>
+      </c>
+      <c r="X130">
+        <v>6.5</v>
+      </c>
+      <c r="Y130">
+        <v>1.11</v>
+      </c>
+      <c r="Z130">
+        <v>4.2</v>
+      </c>
+      <c r="AA130">
+        <v>4.1</v>
+      </c>
+      <c r="AB130">
+        <v>1.7</v>
+      </c>
+      <c r="AC130">
+        <v>1.04</v>
+      </c>
+      <c r="AD130">
+        <v>10</v>
+      </c>
+      <c r="AE130">
+        <v>1.25</v>
+      </c>
+      <c r="AF130">
+        <v>3.95</v>
+      </c>
+      <c r="AG130">
+        <v>1.7</v>
+      </c>
+      <c r="AH130">
+        <v>1.95</v>
+      </c>
+      <c r="AI130">
+        <v>1.7</v>
+      </c>
+      <c r="AJ130">
+        <v>2.05</v>
+      </c>
+      <c r="AK130">
+        <v>2</v>
+      </c>
+      <c r="AL130">
+        <v>1.25</v>
+      </c>
+      <c r="AM130">
+        <v>1.22</v>
+      </c>
+      <c r="AN130">
+        <v>0.8</v>
+      </c>
+      <c r="AO130">
+        <v>1</v>
+      </c>
+      <c r="AP130">
+        <v>1</v>
+      </c>
+      <c r="AQ130">
+        <v>0.91</v>
+      </c>
+      <c r="AR130">
+        <v>1.23</v>
+      </c>
+      <c r="AS130">
+        <v>1.63</v>
+      </c>
+      <c r="AT130">
+        <v>2.86</v>
+      </c>
+      <c r="AU130">
+        <v>3</v>
+      </c>
+      <c r="AV130">
+        <v>3</v>
+      </c>
+      <c r="AW130">
+        <v>3</v>
+      </c>
+      <c r="AX130">
+        <v>18</v>
+      </c>
+      <c r="AY130">
+        <v>6</v>
+      </c>
+      <c r="AZ130">
+        <v>30</v>
+      </c>
+      <c r="BA130">
+        <v>0</v>
+      </c>
+      <c r="BB130">
+        <v>5</v>
+      </c>
+      <c r="BC130">
+        <v>5</v>
+      </c>
+      <c r="BD130">
+        <v>2.45</v>
+      </c>
+      <c r="BE130">
+        <v>8.5</v>
+      </c>
+      <c r="BF130">
+        <v>1.67</v>
+      </c>
+      <c r="BG130">
+        <v>1.2</v>
+      </c>
+      <c r="BH130">
+        <v>3.9</v>
+      </c>
+      <c r="BI130">
+        <v>1.38</v>
+      </c>
+      <c r="BJ130">
+        <v>2.7</v>
+      </c>
+      <c r="BK130">
+        <v>1.7</v>
+      </c>
+      <c r="BL130">
+        <v>1.98</v>
+      </c>
+      <c r="BM130">
+        <v>2.15</v>
+      </c>
+      <c r="BN130">
+        <v>1.57</v>
+      </c>
+      <c r="BO130">
+        <v>2.95</v>
+      </c>
+      <c r="BP130">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7452384</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>73</v>
+      </c>
+      <c r="H131" t="s">
+        <v>70</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>3</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>5</v>
+      </c>
+      <c r="O131" t="s">
+        <v>183</v>
+      </c>
+      <c r="P131" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q131">
+        <v>5</v>
+      </c>
+      <c r="R131">
+        <v>2.25</v>
+      </c>
+      <c r="S131">
+        <v>2.3</v>
+      </c>
+      <c r="T131">
+        <v>1.36</v>
+      </c>
+      <c r="U131">
+        <v>3</v>
+      </c>
+      <c r="V131">
+        <v>2.75</v>
+      </c>
+      <c r="W131">
+        <v>1.4</v>
+      </c>
+      <c r="X131">
+        <v>7</v>
+      </c>
+      <c r="Y131">
+        <v>1.1</v>
+      </c>
+      <c r="Z131">
+        <v>4.75</v>
+      </c>
+      <c r="AA131">
+        <v>3.73</v>
+      </c>
+      <c r="AB131">
+        <v>1.69</v>
+      </c>
+      <c r="AC131">
+        <v>1.05</v>
+      </c>
+      <c r="AD131">
+        <v>9.5</v>
+      </c>
+      <c r="AE131">
+        <v>1.28</v>
+      </c>
+      <c r="AF131">
+        <v>3.6</v>
+      </c>
+      <c r="AG131">
+        <v>1.87</v>
+      </c>
+      <c r="AH131">
+        <v>1.87</v>
+      </c>
+      <c r="AI131">
+        <v>1.8</v>
+      </c>
+      <c r="AJ131">
+        <v>1.95</v>
+      </c>
+      <c r="AK131">
+        <v>2.1</v>
+      </c>
+      <c r="AL131">
+        <v>1.26</v>
+      </c>
+      <c r="AM131">
+        <v>1.19</v>
+      </c>
+      <c r="AN131">
+        <v>0.6</v>
+      </c>
+      <c r="AO131">
+        <v>1.3</v>
+      </c>
+      <c r="AP131">
+        <v>0.82</v>
+      </c>
+      <c r="AQ131">
+        <v>1.18</v>
+      </c>
+      <c r="AR131">
+        <v>1.4</v>
+      </c>
+      <c r="AS131">
+        <v>1.18</v>
+      </c>
+      <c r="AT131">
+        <v>2.58</v>
+      </c>
+      <c r="AU131">
+        <v>8</v>
+      </c>
+      <c r="AV131">
+        <v>11</v>
+      </c>
+      <c r="AW131">
+        <v>4</v>
+      </c>
+      <c r="AX131">
+        <v>8</v>
+      </c>
+      <c r="AY131">
+        <v>14</v>
+      </c>
+      <c r="AZ131">
+        <v>25</v>
+      </c>
+      <c r="BA131">
+        <v>6</v>
+      </c>
+      <c r="BB131">
+        <v>10</v>
+      </c>
+      <c r="BC131">
+        <v>16</v>
+      </c>
+      <c r="BD131">
+        <v>2.88</v>
+      </c>
+      <c r="BE131">
+        <v>9</v>
+      </c>
+      <c r="BF131">
+        <v>1.5</v>
+      </c>
+      <c r="BG131">
+        <v>1.19</v>
+      </c>
+      <c r="BH131">
+        <v>4.1</v>
+      </c>
+      <c r="BI131">
+        <v>1.36</v>
+      </c>
+      <c r="BJ131">
+        <v>2.8</v>
+      </c>
+      <c r="BK131">
+        <v>1.65</v>
+      </c>
+      <c r="BL131">
+        <v>2.05</v>
+      </c>
+      <c r="BM131">
+        <v>2.1</v>
+      </c>
+      <c r="BN131">
+        <v>1.6</v>
+      </c>
+      <c r="BO131">
+        <v>2.85</v>
+      </c>
+      <c r="BP131">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7452385</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" t="s">
+        <v>79</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>2</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>3</v>
+      </c>
+      <c r="M132">
+        <v>2</v>
+      </c>
+      <c r="N132">
+        <v>5</v>
+      </c>
+      <c r="O132" t="s">
+        <v>184</v>
+      </c>
+      <c r="P132" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q132">
+        <v>4.75</v>
+      </c>
+      <c r="R132">
+        <v>2.3</v>
+      </c>
+      <c r="S132">
+        <v>2.3</v>
+      </c>
+      <c r="T132">
+        <v>1.33</v>
+      </c>
+      <c r="U132">
+        <v>3.25</v>
+      </c>
+      <c r="V132">
+        <v>2.5</v>
+      </c>
+      <c r="W132">
+        <v>1.5</v>
+      </c>
+      <c r="X132">
+        <v>6.5</v>
+      </c>
+      <c r="Y132">
+        <v>1.11</v>
+      </c>
+      <c r="Z132">
+        <v>4.6</v>
+      </c>
+      <c r="AA132">
+        <v>3.94</v>
+      </c>
+      <c r="AB132">
+        <v>1.67</v>
+      </c>
+      <c r="AC132">
+        <v>1.04</v>
+      </c>
+      <c r="AD132">
+        <v>10</v>
+      </c>
+      <c r="AE132">
+        <v>1.22</v>
+      </c>
+      <c r="AF132">
+        <v>4.2</v>
+      </c>
+      <c r="AG132">
+        <v>1.8</v>
+      </c>
+      <c r="AH132">
+        <v>1.94</v>
+      </c>
+      <c r="AI132">
+        <v>1.67</v>
+      </c>
+      <c r="AJ132">
+        <v>2.1</v>
+      </c>
+      <c r="AK132">
+        <v>1.95</v>
+      </c>
+      <c r="AL132">
+        <v>1.26</v>
+      </c>
+      <c r="AM132">
+        <v>1.23</v>
+      </c>
+      <c r="AN132">
+        <v>1.7</v>
+      </c>
+      <c r="AO132">
+        <v>1.6</v>
+      </c>
+      <c r="AP132">
+        <v>1.82</v>
+      </c>
+      <c r="AQ132">
+        <v>1.45</v>
+      </c>
+      <c r="AR132">
+        <v>1.38</v>
+      </c>
+      <c r="AS132">
+        <v>1.62</v>
+      </c>
+      <c r="AT132">
+        <v>3</v>
+      </c>
+      <c r="AU132">
+        <v>6</v>
+      </c>
+      <c r="AV132">
+        <v>6</v>
+      </c>
+      <c r="AW132">
+        <v>6</v>
+      </c>
+      <c r="AX132">
+        <v>4</v>
+      </c>
+      <c r="AY132">
+        <v>12</v>
+      </c>
+      <c r="AZ132">
+        <v>10</v>
+      </c>
+      <c r="BA132">
+        <v>5</v>
+      </c>
+      <c r="BB132">
+        <v>5</v>
+      </c>
+      <c r="BC132">
+        <v>10</v>
+      </c>
+      <c r="BD132">
+        <v>3.1</v>
+      </c>
+      <c r="BE132">
+        <v>9.5</v>
+      </c>
+      <c r="BF132">
+        <v>1.44</v>
+      </c>
+      <c r="BG132">
+        <v>1.14</v>
+      </c>
+      <c r="BH132">
+        <v>4.4</v>
+      </c>
+      <c r="BI132">
+        <v>1.25</v>
+      </c>
+      <c r="BJ132">
+        <v>3.4</v>
+      </c>
+      <c r="BK132">
+        <v>1.47</v>
+      </c>
+      <c r="BL132">
+        <v>2.4</v>
+      </c>
+      <c r="BM132">
+        <v>1.8</v>
+      </c>
+      <c r="BN132">
+        <v>1.83</v>
+      </c>
+      <c r="BO132">
+        <v>2.35</v>
+      </c>
+      <c r="BP132">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7452386</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s">
+        <v>78</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>3</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133" t="s">
+        <v>87</v>
+      </c>
+      <c r="P133" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q133">
+        <v>2.88</v>
+      </c>
+      <c r="R133">
+        <v>2.25</v>
+      </c>
+      <c r="S133">
+        <v>3.5</v>
+      </c>
+      <c r="T133">
+        <v>1.36</v>
+      </c>
+      <c r="U133">
+        <v>3</v>
+      </c>
+      <c r="V133">
+        <v>2.63</v>
+      </c>
+      <c r="W133">
+        <v>1.44</v>
+      </c>
+      <c r="X133">
+        <v>7</v>
+      </c>
+      <c r="Y133">
+        <v>1.1</v>
+      </c>
+      <c r="Z133">
+        <v>2.06</v>
+      </c>
+      <c r="AA133">
+        <v>3.53</v>
+      </c>
+      <c r="AB133">
+        <v>3.32</v>
+      </c>
+      <c r="AC133">
+        <v>1.05</v>
+      </c>
+      <c r="AD133">
+        <v>9.5</v>
+      </c>
+      <c r="AE133">
+        <v>1.25</v>
+      </c>
+      <c r="AF133">
+        <v>3.75</v>
+      </c>
+      <c r="AG133">
+        <v>1.92</v>
+      </c>
+      <c r="AH133">
+        <v>1.82</v>
+      </c>
+      <c r="AI133">
+        <v>1.62</v>
+      </c>
+      <c r="AJ133">
+        <v>2.2</v>
+      </c>
+      <c r="AK133">
+        <v>1.36</v>
+      </c>
+      <c r="AL133">
+        <v>1.3</v>
+      </c>
+      <c r="AM133">
+        <v>1.61</v>
+      </c>
+      <c r="AN133">
+        <v>0.9</v>
+      </c>
+      <c r="AO133">
+        <v>0.6</v>
+      </c>
+      <c r="AP133">
+        <v>0.82</v>
+      </c>
+      <c r="AQ133">
+        <v>0.82</v>
+      </c>
+      <c r="AR133">
+        <v>1.44</v>
+      </c>
+      <c r="AS133">
+        <v>1.17</v>
+      </c>
+      <c r="AT133">
+        <v>2.61</v>
+      </c>
+      <c r="AU133">
+        <v>0</v>
+      </c>
+      <c r="AV133">
+        <v>8</v>
+      </c>
+      <c r="AW133">
+        <v>2</v>
+      </c>
+      <c r="AX133">
+        <v>6</v>
+      </c>
+      <c r="AY133">
+        <v>3</v>
+      </c>
+      <c r="AZ133">
+        <v>16</v>
+      </c>
+      <c r="BA133">
+        <v>2</v>
+      </c>
+      <c r="BB133">
+        <v>7</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>1.8</v>
+      </c>
+      <c r="BE133">
+        <v>8.5</v>
+      </c>
+      <c r="BF133">
+        <v>2.2</v>
+      </c>
+      <c r="BG133">
+        <v>1.2</v>
+      </c>
+      <c r="BH133">
+        <v>3.9</v>
+      </c>
+      <c r="BI133">
+        <v>1.38</v>
+      </c>
+      <c r="BJ133">
+        <v>2.7</v>
+      </c>
+      <c r="BK133">
+        <v>1.68</v>
+      </c>
+      <c r="BL133">
+        <v>1.98</v>
+      </c>
+      <c r="BM133">
+        <v>2.15</v>
+      </c>
+      <c r="BN133">
+        <v>1.57</v>
+      </c>
+      <c r="BO133">
+        <v>2.9</v>
+      </c>
+      <c r="BP133">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -322,10 +322,10 @@
     <t>['74']</t>
   </si>
   <si>
-    <t>['24']</t>
+    <t>['33', '35', '71', '74']</t>
   </si>
   <si>
-    <t>['33', '35', '71', '74']</t>
+    <t>['24']</t>
   </si>
   <si>
     <t>['6', '22', '32', '59', '65']</t>
@@ -352,10 +352,10 @@
     <t>['10', '49', '53', '89']</t>
   </si>
   <si>
-    <t>['4', '17', '75']</t>
+    <t>['34', '36']</t>
   </si>
   <si>
-    <t>['34', '36']</t>
+    <t>['4', '17', '75']</t>
   </si>
   <si>
     <t>['29']</t>
@@ -379,10 +379,10 @@
     <t>['28', '39', '45+1']</t>
   </si>
   <si>
-    <t>['27', '90+7']</t>
+    <t>['16', '45+3']</t>
   </si>
   <si>
-    <t>['16', '45+3']</t>
+    <t>['27', '90+7']</t>
   </si>
   <si>
     <t>['13', '57', '73']</t>
@@ -475,10 +475,10 @@
     <t>['6']</t>
   </si>
   <si>
-    <t>['72']</t>
+    <t>['8', '89']</t>
   </si>
   <si>
-    <t>['8', '89']</t>
+    <t>['72']</t>
   </si>
   <si>
     <t>['47']</t>
@@ -514,10 +514,10 @@
     <t>['33']</t>
   </si>
   <si>
-    <t>['25', '27', '58']</t>
+    <t>['20', '48', '51', '71']</t>
   </si>
   <si>
-    <t>['20', '48', '51', '71']</t>
+    <t>['25', '27', '58']</t>
   </si>
   <si>
     <t>['50', '77']</t>
@@ -532,10 +532,10 @@
     <t>['90+4']</t>
   </si>
   <si>
-    <t>['14', '32', '44']</t>
+    <t>['35']</t>
   </si>
   <si>
-    <t>['35']</t>
+    <t>['14', '32', '44']</t>
   </si>
   <si>
     <t>['54', '90+2']</t>
@@ -616,10 +616,10 @@
     <t>['65', '90+6']</t>
   </si>
   <si>
-    <t>['28', '48']</t>
+    <t>['31']</t>
   </si>
   <si>
-    <t>['31']</t>
+    <t>['28', '48']</t>
   </si>
   <si>
     <t>['58']</t>
@@ -646,10 +646,10 @@
     <t>['11', '16']</t>
   </si>
   <si>
-    <t>['61']</t>
+    <t>['52', '72']</t>
   </si>
   <si>
-    <t>['52', '72']</t>
+    <t>['61']</t>
   </si>
   <si>
     <t>['4', '44', '77']</t>
@@ -772,10 +772,10 @@
     <t>['18']</t>
   </si>
   <si>
-    <t>['52']</t>
+    <t>['16', '67', '90+7']</t>
   </si>
   <si>
-    <t>['16', '67', '90+7']</t>
+    <t>['52']</t>
   </si>
   <si>
     <t>['76']</t>
@@ -6531,7 +6531,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7452280</v>
+        <v>7452281</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -6546,28 +6546,28 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O27" t="s">
         <v>102</v>
@@ -6576,160 +6576,160 @@
         <v>200</v>
       </c>
       <c r="Q27">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="T27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V27">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W27">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB27">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD27">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE27">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH27">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI27">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AJ27">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK27">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AL27">
         <v>1.22</v>
       </c>
       <c r="AM27">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AN27">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AQ27">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="AR27">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT27">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AU27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB27">
         <v>3</v>
       </c>
       <c r="BC27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD27">
-        <v>1.5</v>
+        <v>2.81</v>
       </c>
       <c r="BE27">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF27">
-        <v>3.34</v>
+        <v>1.65</v>
       </c>
       <c r="BG27">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH27">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BI27">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="BJ27">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="BK27">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BL27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BM27">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BN27">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="BO27">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="BP27">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="28" spans="1:68">
@@ -6737,7 +6737,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>7452281</v>
+        <v>7452280</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -6752,28 +6752,28 @@
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28">
         <v>3</v>
-      </c>
-      <c r="L28">
-        <v>4</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>5</v>
       </c>
       <c r="O28" t="s">
         <v>103</v>
@@ -6782,160 +6782,160 @@
         <v>201</v>
       </c>
       <c r="Q28">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="T28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA28">
+        <v>3.8</v>
+      </c>
+      <c r="AB28">
+        <v>4.75</v>
+      </c>
+      <c r="AC28">
+        <v>1.03</v>
+      </c>
+      <c r="AD28">
+        <v>12.5</v>
+      </c>
+      <c r="AE28">
+        <v>1.27</v>
+      </c>
+      <c r="AF28">
         <v>3.7</v>
       </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>1.02</v>
-      </c>
-      <c r="AD28">
-        <v>14.5</v>
-      </c>
-      <c r="AE28">
-        <v>1.22</v>
-      </c>
-      <c r="AF28">
-        <v>4.3</v>
-      </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH28">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AI28">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ28">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK28">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AL28">
         <v>1.22</v>
       </c>
       <c r="AM28">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AN28">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AR28">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AS28">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="AU28">
+        <v>8</v>
+      </c>
+      <c r="AV28">
+        <v>6</v>
+      </c>
+      <c r="AW28">
+        <v>5</v>
+      </c>
+      <c r="AX28">
+        <v>6</v>
+      </c>
+      <c r="AY28">
+        <v>16</v>
+      </c>
+      <c r="AZ28">
+        <v>14</v>
+      </c>
+      <c r="BA28">
         <v>7</v>
-      </c>
-      <c r="AV28">
-        <v>4</v>
-      </c>
-      <c r="AW28">
-        <v>4</v>
-      </c>
-      <c r="AX28">
-        <v>7</v>
-      </c>
-      <c r="AY28">
-        <v>12</v>
-      </c>
-      <c r="AZ28">
-        <v>13</v>
-      </c>
-      <c r="BA28">
-        <v>3</v>
       </c>
       <c r="BB28">
         <v>3</v>
       </c>
       <c r="BC28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD28">
-        <v>2.81</v>
+        <v>1.5</v>
       </c>
       <c r="BE28">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF28">
-        <v>1.65</v>
+        <v>3.34</v>
       </c>
       <c r="BG28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH28">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BI28">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="BJ28">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="BK28">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BL28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BM28">
+        <v>1.8</v>
+      </c>
+      <c r="BN28">
+        <v>1.92</v>
+      </c>
+      <c r="BO28">
         <v>2.25</v>
       </c>
-      <c r="BN28">
+      <c r="BP28">
         <v>1.59</v>
-      </c>
-      <c r="BO28">
-        <v>2.88</v>
-      </c>
-      <c r="BP28">
-        <v>1.35</v>
       </c>
     </row>
     <row r="29" spans="1:68">
@@ -9209,7 +9209,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7452294</v>
+        <v>7452293</v>
       </c>
       <c r="C40" t="s">
         <v>68</v>
@@ -9224,10 +9224,10 @@
         <v>7</v>
       </c>
       <c r="G40" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H40" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I40">
         <v>2</v>
@@ -9239,10 +9239,10 @@
         <v>2</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40">
         <v>4</v>
@@ -9254,13 +9254,13 @@
         <v>210</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R40">
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T40">
         <v>1.33</v>
@@ -9281,133 +9281,133 @@
         <v>1.11</v>
       </c>
       <c r="Z40">
+        <v>2.4</v>
+      </c>
+      <c r="AA40">
+        <v>3.5</v>
+      </c>
+      <c r="AB40">
+        <v>2.75</v>
+      </c>
+      <c r="AC40">
+        <v>1.02</v>
+      </c>
+      <c r="AD40">
+        <v>10</v>
+      </c>
+      <c r="AE40">
+        <v>1.25</v>
+      </c>
+      <c r="AF40">
+        <v>3.6</v>
+      </c>
+      <c r="AG40">
+        <v>1.67</v>
+      </c>
+      <c r="AH40">
+        <v>2.15</v>
+      </c>
+      <c r="AI40">
+        <v>1.57</v>
+      </c>
+      <c r="AJ40">
+        <v>2.25</v>
+      </c>
+      <c r="AK40">
+        <v>1.4</v>
+      </c>
+      <c r="AL40">
+        <v>1.27</v>
+      </c>
+      <c r="AM40">
+        <v>1.5</v>
+      </c>
+      <c r="AN40">
+        <v>0.5</v>
+      </c>
+      <c r="AO40">
+        <v>0.33</v>
+      </c>
+      <c r="AP40">
+        <v>0.82</v>
+      </c>
+      <c r="AQ40">
+        <v>0.73</v>
+      </c>
+      <c r="AR40">
+        <v>1.35</v>
+      </c>
+      <c r="AS40">
+        <v>1.16</v>
+      </c>
+      <c r="AT40">
+        <v>2.51</v>
+      </c>
+      <c r="AU40">
+        <v>7</v>
+      </c>
+      <c r="AV40">
+        <v>7</v>
+      </c>
+      <c r="AW40">
+        <v>5</v>
+      </c>
+      <c r="AX40">
+        <v>8</v>
+      </c>
+      <c r="AY40">
+        <v>12</v>
+      </c>
+      <c r="AZ40">
+        <v>22</v>
+      </c>
+      <c r="BA40">
+        <v>7</v>
+      </c>
+      <c r="BB40">
+        <v>9</v>
+      </c>
+      <c r="BC40">
+        <v>16</v>
+      </c>
+      <c r="BD40">
+        <v>1.97</v>
+      </c>
+      <c r="BE40">
+        <v>7.3</v>
+      </c>
+      <c r="BF40">
         <v>2.2</v>
       </c>
-      <c r="AA40">
-        <v>3.7</v>
-      </c>
-      <c r="AB40">
-        <v>3</v>
-      </c>
-      <c r="AC40">
-        <v>1.01</v>
-      </c>
-      <c r="AD40">
-        <v>11</v>
-      </c>
-      <c r="AE40">
-        <v>1.17</v>
-      </c>
-      <c r="AF40">
-        <v>4.5</v>
-      </c>
-      <c r="AG40">
-        <v>1.65</v>
-      </c>
-      <c r="AH40">
-        <v>2.2</v>
-      </c>
-      <c r="AI40">
-        <v>1.53</v>
-      </c>
-      <c r="AJ40">
-        <v>2.38</v>
-      </c>
-      <c r="AK40">
-        <v>1.36</v>
-      </c>
-      <c r="AL40">
-        <v>1.29</v>
-      </c>
-      <c r="AM40">
-        <v>1.7</v>
-      </c>
-      <c r="AN40">
-        <v>1.67</v>
-      </c>
-      <c r="AO40">
-        <v>2.33</v>
-      </c>
-      <c r="AP40">
-        <v>2.27</v>
-      </c>
-      <c r="AQ40">
+      <c r="BG40">
         <v>1.18</v>
       </c>
-      <c r="AR40">
-        <v>1.87</v>
-      </c>
-      <c r="AS40">
-        <v>2.27</v>
-      </c>
-      <c r="AT40">
-        <v>4.14</v>
-      </c>
-      <c r="AU40">
-        <v>5</v>
-      </c>
-      <c r="AV40">
-        <v>9</v>
-      </c>
-      <c r="AW40">
-        <v>1</v>
-      </c>
-      <c r="AX40">
-        <v>6</v>
-      </c>
-      <c r="AY40">
-        <v>6</v>
-      </c>
-      <c r="AZ40">
-        <v>19</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>10</v>
-      </c>
-      <c r="BC40">
-        <v>10</v>
-      </c>
-      <c r="BD40">
-        <v>1.87</v>
-      </c>
-      <c r="BE40">
-        <v>7.2</v>
-      </c>
-      <c r="BF40">
-        <v>2.4</v>
-      </c>
-      <c r="BG40">
-        <v>1.22</v>
-      </c>
       <c r="BH40">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="BI40">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BJ40">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="BK40">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BL40">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BM40">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="BN40">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="BO40">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BP40">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="41" spans="1:68">
@@ -9415,7 +9415,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7452293</v>
+        <v>7452294</v>
       </c>
       <c r="C41" t="s">
         <v>68</v>
@@ -9430,10 +9430,10 @@
         <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I41">
         <v>2</v>
@@ -9445,10 +9445,10 @@
         <v>2</v>
       </c>
       <c r="L41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -9460,13 +9460,13 @@
         <v>211</v>
       </c>
       <c r="Q41">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T41">
         <v>1.33</v>
@@ -9487,133 +9487,133 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
+        <v>2.2</v>
+      </c>
+      <c r="AA41">
+        <v>3.7</v>
+      </c>
+      <c r="AB41">
+        <v>3</v>
+      </c>
+      <c r="AC41">
+        <v>1.01</v>
+      </c>
+      <c r="AD41">
+        <v>11</v>
+      </c>
+      <c r="AE41">
+        <v>1.17</v>
+      </c>
+      <c r="AF41">
+        <v>4.5</v>
+      </c>
+      <c r="AG41">
+        <v>1.65</v>
+      </c>
+      <c r="AH41">
+        <v>2.2</v>
+      </c>
+      <c r="AI41">
+        <v>1.53</v>
+      </c>
+      <c r="AJ41">
+        <v>2.38</v>
+      </c>
+      <c r="AK41">
+        <v>1.36</v>
+      </c>
+      <c r="AL41">
+        <v>1.29</v>
+      </c>
+      <c r="AM41">
+        <v>1.7</v>
+      </c>
+      <c r="AN41">
+        <v>1.67</v>
+      </c>
+      <c r="AO41">
+        <v>2.33</v>
+      </c>
+      <c r="AP41">
+        <v>2.27</v>
+      </c>
+      <c r="AQ41">
+        <v>1.18</v>
+      </c>
+      <c r="AR41">
+        <v>1.87</v>
+      </c>
+      <c r="AS41">
+        <v>2.27</v>
+      </c>
+      <c r="AT41">
+        <v>4.14</v>
+      </c>
+      <c r="AU41">
+        <v>5</v>
+      </c>
+      <c r="AV41">
+        <v>9</v>
+      </c>
+      <c r="AW41">
+        <v>1</v>
+      </c>
+      <c r="AX41">
+        <v>6</v>
+      </c>
+      <c r="AY41">
+        <v>6</v>
+      </c>
+      <c r="AZ41">
+        <v>19</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>10</v>
+      </c>
+      <c r="BC41">
+        <v>10</v>
+      </c>
+      <c r="BD41">
+        <v>1.87</v>
+      </c>
+      <c r="BE41">
+        <v>7.2</v>
+      </c>
+      <c r="BF41">
         <v>2.4</v>
       </c>
-      <c r="AA41">
-        <v>3.5</v>
-      </c>
-      <c r="AB41">
-        <v>2.75</v>
-      </c>
-      <c r="AC41">
-        <v>1.02</v>
-      </c>
-      <c r="AD41">
-        <v>10</v>
-      </c>
-      <c r="AE41">
-        <v>1.25</v>
-      </c>
-      <c r="AF41">
-        <v>3.6</v>
-      </c>
-      <c r="AG41">
-        <v>1.67</v>
-      </c>
-      <c r="AH41">
-        <v>2.15</v>
-      </c>
-      <c r="AI41">
-        <v>1.57</v>
-      </c>
-      <c r="AJ41">
-        <v>2.25</v>
-      </c>
-      <c r="AK41">
-        <v>1.4</v>
-      </c>
-      <c r="AL41">
-        <v>1.27</v>
-      </c>
-      <c r="AM41">
-        <v>1.5</v>
-      </c>
-      <c r="AN41">
-        <v>0.5</v>
-      </c>
-      <c r="AO41">
-        <v>0.33</v>
-      </c>
-      <c r="AP41">
-        <v>0.82</v>
-      </c>
-      <c r="AQ41">
-        <v>0.73</v>
-      </c>
-      <c r="AR41">
+      <c r="BG41">
+        <v>1.22</v>
+      </c>
+      <c r="BH41">
+        <v>3.75</v>
+      </c>
+      <c r="BI41">
+        <v>1.41</v>
+      </c>
+      <c r="BJ41">
+        <v>2.63</v>
+      </c>
+      <c r="BK41">
+        <v>2.1</v>
+      </c>
+      <c r="BL41">
+        <v>1.98</v>
+      </c>
+      <c r="BM41">
+        <v>2.18</v>
+      </c>
+      <c r="BN41">
+        <v>1.6</v>
+      </c>
+      <c r="BO41">
+        <v>2.88</v>
+      </c>
+      <c r="BP41">
         <v>1.35</v>
-      </c>
-      <c r="AS41">
-        <v>1.16</v>
-      </c>
-      <c r="AT41">
-        <v>2.51</v>
-      </c>
-      <c r="AU41">
-        <v>7</v>
-      </c>
-      <c r="AV41">
-        <v>7</v>
-      </c>
-      <c r="AW41">
-        <v>5</v>
-      </c>
-      <c r="AX41">
-        <v>8</v>
-      </c>
-      <c r="AY41">
-        <v>12</v>
-      </c>
-      <c r="AZ41">
-        <v>22</v>
-      </c>
-      <c r="BA41">
-        <v>7</v>
-      </c>
-      <c r="BB41">
-        <v>9</v>
-      </c>
-      <c r="BC41">
-        <v>16</v>
-      </c>
-      <c r="BD41">
-        <v>1.97</v>
-      </c>
-      <c r="BE41">
-        <v>7.3</v>
-      </c>
-      <c r="BF41">
-        <v>2.2</v>
-      </c>
-      <c r="BG41">
-        <v>1.18</v>
-      </c>
-      <c r="BH41">
-        <v>4.25</v>
-      </c>
-      <c r="BI41">
-        <v>1.34</v>
-      </c>
-      <c r="BJ41">
-        <v>2.95</v>
-      </c>
-      <c r="BK41">
-        <v>2</v>
-      </c>
-      <c r="BL41">
-        <v>2</v>
-      </c>
-      <c r="BM41">
-        <v>1.95</v>
-      </c>
-      <c r="BN41">
-        <v>1.77</v>
-      </c>
-      <c r="BO41">
-        <v>2.6</v>
-      </c>
-      <c r="BP41">
-        <v>1.43</v>
       </c>
     </row>
     <row r="42" spans="1:68">
@@ -10281,7 +10281,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11475,7 +11475,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7452303</v>
+        <v>7452306</v>
       </c>
       <c r="C51" t="s">
         <v>68</v>
@@ -11490,49 +11490,49 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51">
         <v>2</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O51" t="s">
         <v>121</v>
       </c>
       <c r="P51" t="s">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U51">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V51">
         <v>2.5</v>
@@ -11541,139 +11541,139 @@
         <v>1.5</v>
       </c>
       <c r="X51">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB51">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
         <v>1.01</v>
       </c>
       <c r="AD51">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE51">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF51">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG51">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH51">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AI51">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK51">
+        <v>1.7</v>
+      </c>
+      <c r="AL51">
         <v>1.29</v>
       </c>
-      <c r="AL51">
-        <v>1.28</v>
-      </c>
       <c r="AM51">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AN51">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="AQ51">
-        <v>0.36</v>
+        <v>1.36</v>
       </c>
       <c r="AR51">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AS51">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AT51">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="AU51">
+        <v>5</v>
+      </c>
+      <c r="AV51">
         <v>7</v>
       </c>
-      <c r="AV51">
+      <c r="AW51">
+        <v>8</v>
+      </c>
+      <c r="AX51">
+        <v>3</v>
+      </c>
+      <c r="AY51">
+        <v>18</v>
+      </c>
+      <c r="AZ51">
+        <v>14</v>
+      </c>
+      <c r="BA51">
+        <v>6</v>
+      </c>
+      <c r="BB51">
         <v>4</v>
       </c>
-      <c r="AW51">
-        <v>5</v>
-      </c>
-      <c r="AX51">
-        <v>4</v>
-      </c>
-      <c r="AY51">
-        <v>16</v>
-      </c>
-      <c r="AZ51">
+      <c r="BC51">
         <v>10</v>
       </c>
-      <c r="BA51">
-        <v>4</v>
-      </c>
-      <c r="BB51">
-        <v>2</v>
-      </c>
-      <c r="BC51">
-        <v>6</v>
-      </c>
       <c r="BD51">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="BE51">
-        <v>8.5</v>
+        <v>6.85</v>
       </c>
       <c r="BF51">
-        <v>2.91</v>
+        <v>1.81</v>
       </c>
       <c r="BG51">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BH51">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="BI51">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="BJ51">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="BK51">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BL51">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="BM51">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="BN51">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="BO51">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="BP51">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="52" spans="1:68">
@@ -11681,7 +11681,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7452306</v>
+        <v>7452303</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -11696,49 +11696,49 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
         <v>3</v>
-      </c>
-      <c r="L52">
-        <v>2</v>
-      </c>
-      <c r="M52">
-        <v>2</v>
-      </c>
-      <c r="N52">
-        <v>4</v>
       </c>
       <c r="O52" t="s">
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>101</v>
       </c>
       <c r="Q52">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="T52">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U52">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V52">
         <v>2.5</v>
@@ -11747,139 +11747,139 @@
         <v>1.5</v>
       </c>
       <c r="X52">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA52">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AC52">
         <v>1.01</v>
       </c>
       <c r="AD52">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG52">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH52">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AI52">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AJ52">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK52">
+        <v>1.29</v>
+      </c>
+      <c r="AL52">
+        <v>1.28</v>
+      </c>
+      <c r="AM52">
+        <v>1.84</v>
+      </c>
+      <c r="AN52">
+        <v>0.67</v>
+      </c>
+      <c r="AO52">
+        <v>0</v>
+      </c>
+      <c r="AP52">
+        <v>0.82</v>
+      </c>
+      <c r="AQ52">
+        <v>0.36</v>
+      </c>
+      <c r="AR52">
+        <v>1.45</v>
+      </c>
+      <c r="AS52">
+        <v>1.24</v>
+      </c>
+      <c r="AT52">
+        <v>2.69</v>
+      </c>
+      <c r="AU52">
+        <v>7</v>
+      </c>
+      <c r="AV52">
+        <v>4</v>
+      </c>
+      <c r="AW52">
+        <v>5</v>
+      </c>
+      <c r="AX52">
+        <v>4</v>
+      </c>
+      <c r="AY52">
+        <v>16</v>
+      </c>
+      <c r="AZ52">
+        <v>10</v>
+      </c>
+      <c r="BA52">
+        <v>4</v>
+      </c>
+      <c r="BB52">
+        <v>2</v>
+      </c>
+      <c r="BC52">
+        <v>6</v>
+      </c>
+      <c r="BD52">
+        <v>1.55</v>
+      </c>
+      <c r="BE52">
+        <v>8.5</v>
+      </c>
+      <c r="BF52">
+        <v>2.91</v>
+      </c>
+      <c r="BG52">
+        <v>1.21</v>
+      </c>
+      <c r="BH52">
+        <v>4.1</v>
+      </c>
+      <c r="BI52">
+        <v>1.4</v>
+      </c>
+      <c r="BJ52">
+        <v>2.8</v>
+      </c>
+      <c r="BK52">
+        <v>2</v>
+      </c>
+      <c r="BL52">
+        <v>2.13</v>
+      </c>
+      <c r="BM52">
+        <v>2.08</v>
+      </c>
+      <c r="BN52">
         <v>1.7</v>
       </c>
-      <c r="AL52">
-        <v>1.29</v>
-      </c>
-      <c r="AM52">
-        <v>1.36</v>
-      </c>
-      <c r="AN52">
-        <v>1.5</v>
-      </c>
-      <c r="AO52">
-        <v>2</v>
-      </c>
-      <c r="AP52">
-        <v>1.64</v>
-      </c>
-      <c r="AQ52">
-        <v>1.36</v>
-      </c>
-      <c r="AR52">
-        <v>1.41</v>
-      </c>
-      <c r="AS52">
-        <v>1.48</v>
-      </c>
-      <c r="AT52">
-        <v>2.89</v>
-      </c>
-      <c r="AU52">
-        <v>5</v>
-      </c>
-      <c r="AV52">
-        <v>7</v>
-      </c>
-      <c r="AW52">
-        <v>8</v>
-      </c>
-      <c r="AX52">
-        <v>3</v>
-      </c>
-      <c r="AY52">
-        <v>18</v>
-      </c>
-      <c r="AZ52">
-        <v>14</v>
-      </c>
-      <c r="BA52">
-        <v>6</v>
-      </c>
-      <c r="BB52">
-        <v>4</v>
-      </c>
-      <c r="BC52">
-        <v>10</v>
-      </c>
-      <c r="BD52">
-        <v>2.58</v>
-      </c>
-      <c r="BE52">
-        <v>6.85</v>
-      </c>
-      <c r="BF52">
-        <v>1.81</v>
-      </c>
-      <c r="BG52">
-        <v>1.11</v>
-      </c>
-      <c r="BH52">
-        <v>4.55</v>
-      </c>
-      <c r="BI52">
-        <v>1.26</v>
-      </c>
-      <c r="BJ52">
-        <v>3.08</v>
-      </c>
-      <c r="BK52">
-        <v>2.1</v>
-      </c>
-      <c r="BL52">
-        <v>2.32</v>
-      </c>
-      <c r="BM52">
-        <v>1.89</v>
-      </c>
-      <c r="BN52">
-        <v>1.85</v>
-      </c>
       <c r="BO52">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BP52">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="53" spans="1:68">
@@ -12753,7 +12753,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q57">
         <v>2.25</v>
@@ -15183,7 +15183,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>7452324</v>
+        <v>7452325</v>
       </c>
       <c r="C69" t="s">
         <v>68</v>
@@ -15198,10 +15198,10 @@
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -15216,70 +15216,70 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="s">
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>3.6</v>
       </c>
       <c r="R69">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
         <v>2.75</v>
       </c>
       <c r="T69">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U69">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V69">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W69">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X69">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y69">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z69">
         <v>3.1</v>
       </c>
       <c r="AA69">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB69">
         <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AD69">
-        <v>1.07</v>
+        <v>13</v>
       </c>
       <c r="AE69">
-        <v>1.24</v>
+        <v>3.92</v>
       </c>
       <c r="AF69">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="AG69">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH69">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI69">
         <v>1.62</v>
@@ -15288,100 +15288,100 @@
         <v>2.2</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL69">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AM69">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AN69">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO69">
-        <v>0.83</v>
+        <v>1.4</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>1.55</v>
       </c>
       <c r="AR69">
         <v>1.17</v>
       </c>
       <c r="AS69">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AT69">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="AU69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV69">
         <v>6</v>
       </c>
       <c r="AW69">
+        <v>11</v>
+      </c>
+      <c r="AX69">
         <v>6</v>
       </c>
-      <c r="AX69">
-        <v>5</v>
-      </c>
       <c r="AY69">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AZ69">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA69">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC69">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD69">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="BE69">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BF69">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="BG69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BH69">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BI69">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BJ69">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="BK69">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL69">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BM69">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BN69">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BO69">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BP69">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="70" spans="1:68">
@@ -15389,7 +15389,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>7452325</v>
+        <v>7452324</v>
       </c>
       <c r="C70" t="s">
         <v>68</v>
@@ -15404,10 +15404,10 @@
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H70" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -15422,70 +15422,70 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
       </c>
       <c r="R70">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>2.75</v>
       </c>
       <c r="T70">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U70">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V70">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W70">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X70">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y70">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
         <v>3.1</v>
       </c>
       <c r="AA70">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB70">
         <v>2.15</v>
       </c>
       <c r="AC70">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AD70">
-        <v>13</v>
+        <v>1.07</v>
       </c>
       <c r="AE70">
-        <v>3.92</v>
+        <v>1.24</v>
       </c>
       <c r="AF70">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="AG70">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH70">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AI70">
         <v>1.62</v>
@@ -15494,100 +15494,100 @@
         <v>2.2</v>
       </c>
       <c r="AK70">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AM70">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN70">
-        <v>1.8</v>
+        <v>0.83</v>
       </c>
       <c r="AO70">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="AP70">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.55</v>
+        <v>0.73</v>
       </c>
       <c r="AR70">
         <v>1.17</v>
       </c>
       <c r="AS70">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AT70">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="AU70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV70">
         <v>6</v>
       </c>
       <c r="AW70">
+        <v>6</v>
+      </c>
+      <c r="AX70">
+        <v>5</v>
+      </c>
+      <c r="AY70">
         <v>11</v>
       </c>
-      <c r="AX70">
-        <v>6</v>
-      </c>
-      <c r="AY70">
-        <v>24</v>
-      </c>
       <c r="AZ70">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA70">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BB70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC70">
+        <v>14</v>
+      </c>
+      <c r="BD70">
+        <v>2.23</v>
+      </c>
+      <c r="BE70">
         <v>7</v>
       </c>
-      <c r="BD70">
-        <v>2.37</v>
-      </c>
-      <c r="BE70">
-        <v>6.5</v>
-      </c>
       <c r="BF70">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="BG70">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BH70">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="BI70">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BJ70">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="BK70">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL70">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BM70">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BN70">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BO70">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BP70">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="71" spans="1:68">
@@ -18727,7 +18727,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18891,7 +18891,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7452342</v>
+        <v>7452344</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18906,43 +18906,43 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O87" t="s">
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>87</v>
+        <v>236</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T87">
         <v>1.33</v>
@@ -18957,73 +18957,73 @@
         <v>1.44</v>
       </c>
       <c r="X87">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AA87">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB87">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC87">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD87">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AE87">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AG87">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH87">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI87">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK87">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL87">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM87">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AN87">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="AO87">
-        <v>1.86</v>
+        <v>0.71</v>
       </c>
       <c r="AP87">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.55</v>
+        <v>0.82</v>
       </c>
       <c r="AR87">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AS87">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AT87">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AU87">
         <v>5</v>
@@ -19032,64 +19032,64 @@
         <v>4</v>
       </c>
       <c r="AW87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX87">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY87">
         <v>13</v>
       </c>
       <c r="AZ87">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB87">
+        <v>7</v>
+      </c>
+      <c r="BC87">
         <v>8</v>
-      </c>
-      <c r="BC87">
-        <v>11</v>
       </c>
       <c r="BD87">
         <v>2.02</v>
       </c>
       <c r="BE87">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="BF87">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="BG87">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BH87">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="BI87">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="BJ87">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="BK87">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="BL87">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="BM87">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="BN87">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="BO87">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="BP87">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="88" spans="1:68">
@@ -19097,7 +19097,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>7452344</v>
+        <v>7452342</v>
       </c>
       <c r="C88" t="s">
         <v>68</v>
@@ -19112,43 +19112,43 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O88" t="s">
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
       <c r="Q88">
+        <v>3.25</v>
+      </c>
+      <c r="R88">
+        <v>2.25</v>
+      </c>
+      <c r="S88">
         <v>3</v>
-      </c>
-      <c r="R88">
-        <v>2.2</v>
-      </c>
-      <c r="S88">
-        <v>3.4</v>
       </c>
       <c r="T88">
         <v>1.33</v>
@@ -19163,73 +19163,73 @@
         <v>1.44</v>
       </c>
       <c r="X88">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AA88">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB88">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC88">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD88">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AG88">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH88">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI88">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ88">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK88">
+        <v>1.57</v>
+      </c>
+      <c r="AL88">
+        <v>1.22</v>
+      </c>
+      <c r="AM88">
         <v>1.45</v>
       </c>
-      <c r="AL88">
-        <v>1.25</v>
-      </c>
-      <c r="AM88">
-        <v>1.53</v>
-      </c>
       <c r="AN88">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="AO88">
-        <v>0.71</v>
+        <v>1.86</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AQ88">
-        <v>0.82</v>
+        <v>1.55</v>
       </c>
       <c r="AR88">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AS88">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AT88">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19238,64 +19238,64 @@
         <v>4</v>
       </c>
       <c r="AW88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX88">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY88">
         <v>13</v>
       </c>
       <c r="AZ88">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC88">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD88">
         <v>2.02</v>
       </c>
       <c r="BE88">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="BF88">
+        <v>1.86</v>
+      </c>
+      <c r="BG88">
+        <v>1.26</v>
+      </c>
+      <c r="BH88">
+        <v>3.4</v>
+      </c>
+      <c r="BI88">
+        <v>1.41</v>
+      </c>
+      <c r="BJ88">
+        <v>2.68</v>
+      </c>
+      <c r="BK88">
+        <v>2.1</v>
+      </c>
+      <c r="BL88">
+        <v>2.04</v>
+      </c>
+      <c r="BM88">
         <v>2.12</v>
       </c>
-      <c r="BG88">
-        <v>1.1</v>
-      </c>
-      <c r="BH88">
-        <v>4.75</v>
-      </c>
-      <c r="BI88">
-        <v>1.3</v>
-      </c>
-      <c r="BJ88">
-        <v>3.2</v>
-      </c>
-      <c r="BK88">
-        <v>1.83</v>
-      </c>
-      <c r="BL88">
-        <v>2.35</v>
-      </c>
-      <c r="BM88">
-        <v>1.9</v>
-      </c>
       <c r="BN88">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="BO88">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="BP88">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="89" spans="1:68">
@@ -23629,7 +23629,7 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>7452364</v>
+        <v>7452368</v>
       </c>
       <c r="C110" t="s">
         <v>68</v>
@@ -23644,190 +23644,190 @@
         <v>19</v>
       </c>
       <c r="G110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H110" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O110" t="s">
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="Q110">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R110">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="T110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="U110">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="V110">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="W110">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y110">
+        <v>1.13</v>
+      </c>
+      <c r="Z110">
+        <v>1.51</v>
+      </c>
+      <c r="AA110">
+        <v>4.3</v>
+      </c>
+      <c r="AB110">
+        <v>5.7</v>
+      </c>
+      <c r="AC110">
+        <v>1.04</v>
+      </c>
+      <c r="AD110">
+        <v>10</v>
+      </c>
+      <c r="AE110">
+        <v>1.2</v>
+      </c>
+      <c r="AF110">
+        <v>4.33</v>
+      </c>
+      <c r="AG110">
+        <v>1.61</v>
+      </c>
+      <c r="AH110">
+        <v>2.17</v>
+      </c>
+      <c r="AI110">
+        <v>1.75</v>
+      </c>
+      <c r="AJ110">
+        <v>2</v>
+      </c>
+      <c r="AK110">
+        <v>1.12</v>
+      </c>
+      <c r="AL110">
         <v>1.17</v>
       </c>
-      <c r="Z110">
-        <v>1.43</v>
-      </c>
-      <c r="AA110">
-        <v>4.8</v>
-      </c>
-      <c r="AB110">
-        <v>6.2</v>
-      </c>
-      <c r="AC110">
-        <v>1.01</v>
-      </c>
-      <c r="AD110">
-        <v>17</v>
-      </c>
-      <c r="AE110">
-        <v>1.15</v>
-      </c>
-      <c r="AF110">
-        <v>5.25</v>
-      </c>
-      <c r="AG110">
-        <v>1.47</v>
-      </c>
-      <c r="AH110">
-        <v>2.57</v>
-      </c>
-      <c r="AI110">
-        <v>1.7</v>
-      </c>
-      <c r="AJ110">
-        <v>2.05</v>
-      </c>
-      <c r="AK110">
-        <v>1.09</v>
-      </c>
-      <c r="AL110">
-        <v>1.13</v>
-      </c>
       <c r="AM110">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AN110">
         <v>2.11</v>
       </c>
       <c r="AO110">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AP110">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="AQ110">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="AR110">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AS110">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AT110">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="AU110">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW110">
         <v>11</v>
       </c>
       <c r="AX110">
+        <v>0</v>
+      </c>
+      <c r="AY110">
+        <v>26</v>
+      </c>
+      <c r="AZ110">
+        <v>3</v>
+      </c>
+      <c r="BA110">
         <v>7</v>
       </c>
-      <c r="AY110">
-        <v>24</v>
-      </c>
-      <c r="AZ110">
-        <v>16</v>
-      </c>
-      <c r="BA110">
-        <v>1</v>
-      </c>
       <c r="BB110">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC110">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD110">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BE110">
         <v>7.5</v>
       </c>
       <c r="BF110">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BG110">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BH110">
         <v>3.2</v>
       </c>
       <c r="BI110">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BJ110">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BK110">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BL110">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BM110">
         <v>2.23</v>
       </c>
       <c r="BN110">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BO110">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BP110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="111" spans="1:68">
@@ -23835,7 +23835,7 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>7452368</v>
+        <v>7452364</v>
       </c>
       <c r="C111" t="s">
         <v>68</v>
@@ -23850,190 +23850,190 @@
         <v>19</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H111" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O111" t="s">
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="Q111">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="R111">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S111">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="T111">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U111">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="V111">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="W111">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y111">
+        <v>1.17</v>
+      </c>
+      <c r="Z111">
+        <v>1.43</v>
+      </c>
+      <c r="AA111">
+        <v>4.8</v>
+      </c>
+      <c r="AB111">
+        <v>6.2</v>
+      </c>
+      <c r="AC111">
+        <v>1.01</v>
+      </c>
+      <c r="AD111">
+        <v>17</v>
+      </c>
+      <c r="AE111">
+        <v>1.15</v>
+      </c>
+      <c r="AF111">
+        <v>5.25</v>
+      </c>
+      <c r="AG111">
+        <v>1.47</v>
+      </c>
+      <c r="AH111">
+        <v>2.57</v>
+      </c>
+      <c r="AI111">
+        <v>1.7</v>
+      </c>
+      <c r="AJ111">
+        <v>2.05</v>
+      </c>
+      <c r="AK111">
+        <v>1.09</v>
+      </c>
+      <c r="AL111">
         <v>1.13</v>
       </c>
-      <c r="Z111">
-        <v>1.51</v>
-      </c>
-      <c r="AA111">
-        <v>4.3</v>
-      </c>
-      <c r="AB111">
-        <v>5.7</v>
-      </c>
-      <c r="AC111">
-        <v>1.04</v>
-      </c>
-      <c r="AD111">
-        <v>10</v>
-      </c>
-      <c r="AE111">
-        <v>1.2</v>
-      </c>
-      <c r="AF111">
-        <v>4.33</v>
-      </c>
-      <c r="AG111">
-        <v>1.61</v>
-      </c>
-      <c r="AH111">
-        <v>2.17</v>
-      </c>
-      <c r="AI111">
-        <v>1.75</v>
-      </c>
-      <c r="AJ111">
-        <v>2</v>
-      </c>
-      <c r="AK111">
-        <v>1.12</v>
-      </c>
-      <c r="AL111">
-        <v>1.17</v>
-      </c>
       <c r="AM111">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AN111">
         <v>2.11</v>
       </c>
       <c r="AO111">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AQ111">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR111">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AS111">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT111">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="AU111">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW111">
         <v>11</v>
       </c>
       <c r="AX111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY111">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ111">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="BA111">
+        <v>1</v>
+      </c>
+      <c r="BB111">
+        <v>6</v>
+      </c>
+      <c r="BC111">
         <v>7</v>
       </c>
-      <c r="BB111">
-        <v>2</v>
-      </c>
-      <c r="BC111">
-        <v>9</v>
-      </c>
       <c r="BD111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BE111">
         <v>7.5</v>
       </c>
       <c r="BF111">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG111">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BH111">
         <v>3.2</v>
       </c>
       <c r="BI111">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BJ111">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BK111">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BL111">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BM111">
         <v>2.23</v>
       </c>
       <c r="BN111">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BO111">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP111">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="112" spans="1:68">
@@ -25071,7 +25071,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>7452374</v>
+        <v>7452373</v>
       </c>
       <c r="C117" t="s">
         <v>68</v>
@@ -25086,25 +25086,25 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H117" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
         <v>3</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>3</v>
-      </c>
-      <c r="L117">
-        <v>3</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
       </c>
       <c r="N117">
         <v>4</v>
@@ -25116,160 +25116,160 @@
         <v>252</v>
       </c>
       <c r="Q117">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="R117">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="T117">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U117">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V117">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W117">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X117">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y117">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z117">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
       <c r="AA117">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="AB117">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="AC117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD117">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE117">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF117">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG117">
         <v>1.67</v>
       </c>
       <c r="AH117">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI117">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ117">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK117">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AL117">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM117">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="AN117">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AO117">
-        <v>0.44</v>
+        <v>1.44</v>
       </c>
       <c r="AP117">
-        <v>1.82</v>
+        <v>0.82</v>
       </c>
       <c r="AQ117">
-        <v>0.36</v>
+        <v>1.55</v>
       </c>
       <c r="AR117">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AS117">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AT117">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="AU117">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV117">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AW117">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX117">
         <v>10</v>
       </c>
       <c r="AY117">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AZ117">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BA117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB117">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC117">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD117">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="BE117">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF117">
-        <v>2.65</v>
+        <v>1.84</v>
       </c>
       <c r="BG117">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="BH117">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="BI117">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="BJ117">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="BK117">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="BL117">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="BM117">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BN117">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="BO117">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="BP117">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="118" spans="1:68">
@@ -25277,7 +25277,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7452373</v>
+        <v>7452374</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25292,25 +25292,25 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -25322,160 +25322,160 @@
         <v>253</v>
       </c>
       <c r="Q118">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="R118">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S118">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="T118">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U118">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V118">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W118">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X118">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y118">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z118">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="AA118">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AB118">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="AC118">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD118">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE118">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF118">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG118">
         <v>1.67</v>
       </c>
       <c r="AH118">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI118">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ118">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AL118">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM118">
+        <v>1.98</v>
+      </c>
+      <c r="AN118">
+        <v>1.56</v>
+      </c>
+      <c r="AO118">
+        <v>0.44</v>
+      </c>
+      <c r="AP118">
+        <v>1.82</v>
+      </c>
+      <c r="AQ118">
+        <v>0.36</v>
+      </c>
+      <c r="AR118">
         <v>1.35</v>
       </c>
-      <c r="AN118">
-        <v>1</v>
-      </c>
-      <c r="AO118">
-        <v>1.44</v>
-      </c>
-      <c r="AP118">
-        <v>0.82</v>
-      </c>
-      <c r="AQ118">
-        <v>1.55</v>
-      </c>
-      <c r="AR118">
-        <v>1.38</v>
-      </c>
       <c r="AS118">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AT118">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="AU118">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV118">
+        <v>3</v>
+      </c>
+      <c r="AW118">
         <v>10</v>
-      </c>
-      <c r="AW118">
-        <v>8</v>
       </c>
       <c r="AX118">
         <v>10</v>
       </c>
       <c r="AY118">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ118">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BA118">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB118">
+        <v>4</v>
+      </c>
+      <c r="BC118">
+        <v>8</v>
+      </c>
+      <c r="BD118">
+        <v>1.57</v>
+      </c>
+      <c r="BE118">
         <v>7</v>
       </c>
-      <c r="BC118">
-        <v>10</v>
-      </c>
-      <c r="BD118">
-        <v>2.17</v>
-      </c>
-      <c r="BE118">
-        <v>6.4</v>
-      </c>
       <c r="BF118">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="BG118">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="BH118">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="BI118">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="BJ118">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="BK118">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="BL118">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="BM118">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="BN118">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="BO118">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="BP118">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -26307,7 +26307,7 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>7452378</v>
+        <v>7452380</v>
       </c>
       <c r="C123" t="s">
         <v>68</v>
@@ -26322,190 +26322,190 @@
         <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H123" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123" t="s">
+        <v>87</v>
+      </c>
+      <c r="P123" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q123">
+        <v>2.38</v>
+      </c>
+      <c r="R123">
+        <v>2.2</v>
+      </c>
+      <c r="S123">
+        <v>5</v>
+      </c>
+      <c r="T123">
+        <v>1.4</v>
+      </c>
+      <c r="U123">
+        <v>2.75</v>
+      </c>
+      <c r="V123">
         <v>3</v>
       </c>
-      <c r="L123">
-        <v>1</v>
-      </c>
-      <c r="M123">
+      <c r="W123">
+        <v>1.36</v>
+      </c>
+      <c r="X123">
+        <v>8</v>
+      </c>
+      <c r="Y123">
+        <v>1.08</v>
+      </c>
+      <c r="Z123">
+        <v>1.61</v>
+      </c>
+      <c r="AA123">
         <v>4</v>
       </c>
-      <c r="N123">
+      <c r="AB123">
         <v>5</v>
       </c>
-      <c r="O123" t="s">
-        <v>177</v>
-      </c>
-      <c r="P123" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q123">
-        <v>4.75</v>
-      </c>
-      <c r="R123">
-        <v>2.38</v>
-      </c>
-      <c r="S123">
-        <v>2.25</v>
-      </c>
-      <c r="T123">
-        <v>1.3</v>
-      </c>
-      <c r="U123">
-        <v>3.4</v>
-      </c>
-      <c r="V123">
-        <v>2.5</v>
-      </c>
-      <c r="W123">
-        <v>1.5</v>
-      </c>
-      <c r="X123">
+      <c r="AC123">
+        <v>1.02</v>
+      </c>
+      <c r="AD123">
+        <v>10</v>
+      </c>
+      <c r="AE123">
+        <v>1.29</v>
+      </c>
+      <c r="AF123">
+        <v>3.3</v>
+      </c>
+      <c r="AG123">
+        <v>1.89</v>
+      </c>
+      <c r="AH123">
+        <v>1.85</v>
+      </c>
+      <c r="AI123">
+        <v>1.91</v>
+      </c>
+      <c r="AJ123">
+        <v>1.91</v>
+      </c>
+      <c r="AK123">
+        <v>1.2</v>
+      </c>
+      <c r="AL123">
+        <v>1.26</v>
+      </c>
+      <c r="AM123">
+        <v>2.05</v>
+      </c>
+      <c r="AN123">
+        <v>1.6</v>
+      </c>
+      <c r="AO123">
+        <v>0.4</v>
+      </c>
+      <c r="AP123">
+        <v>1.45</v>
+      </c>
+      <c r="AQ123">
+        <v>0.64</v>
+      </c>
+      <c r="AR123">
+        <v>1.29</v>
+      </c>
+      <c r="AS123">
+        <v>1.16</v>
+      </c>
+      <c r="AT123">
+        <v>2.45</v>
+      </c>
+      <c r="AU123">
+        <v>7</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>17</v>
+      </c>
+      <c r="AX123">
+        <v>5</v>
+      </c>
+      <c r="AY123">
+        <v>30</v>
+      </c>
+      <c r="AZ123">
+        <v>10</v>
+      </c>
+      <c r="BA123">
         <v>6</v>
       </c>
-      <c r="Y123">
-        <v>1.13</v>
-      </c>
-      <c r="Z123">
-        <v>3.95</v>
-      </c>
-      <c r="AA123">
-        <v>3.9</v>
-      </c>
-      <c r="AB123">
-        <v>1.78</v>
-      </c>
-      <c r="AC123">
-        <v>1.03</v>
-      </c>
-      <c r="AD123">
-        <v>11</v>
-      </c>
-      <c r="AE123">
-        <v>1.18</v>
-      </c>
-      <c r="AF123">
-        <v>4.75</v>
-      </c>
-      <c r="AG123">
-        <v>1.55</v>
-      </c>
-      <c r="AH123">
-        <v>2.2</v>
-      </c>
-      <c r="AI123">
-        <v>1.67</v>
-      </c>
-      <c r="AJ123">
-        <v>2.1</v>
-      </c>
-      <c r="AK123">
-        <v>2.05</v>
-      </c>
-      <c r="AL123">
-        <v>1.18</v>
-      </c>
-      <c r="AM123">
-        <v>1.22</v>
-      </c>
-      <c r="AN123">
-        <v>1.2</v>
-      </c>
-      <c r="AO123">
-        <v>1.2</v>
-      </c>
-      <c r="AP123">
-        <v>1.09</v>
-      </c>
-      <c r="AQ123">
-        <v>1.36</v>
-      </c>
-      <c r="AR123">
-        <v>1.31</v>
-      </c>
-      <c r="AS123">
-        <v>1.53</v>
-      </c>
-      <c r="AT123">
-        <v>2.84</v>
-      </c>
-      <c r="AU123">
+      <c r="BB123">
         <v>4</v>
       </c>
-      <c r="AV123">
+      <c r="BC123">
         <v>10</v>
       </c>
-      <c r="AW123">
-        <v>9</v>
-      </c>
-      <c r="AX123">
-        <v>18</v>
-      </c>
-      <c r="AY123">
-        <v>17</v>
-      </c>
-      <c r="AZ123">
-        <v>35</v>
-      </c>
-      <c r="BA123">
-        <v>8</v>
-      </c>
-      <c r="BB123">
-        <v>7</v>
-      </c>
-      <c r="BC123">
-        <v>15</v>
-      </c>
       <c r="BD123">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="BE123">
         <v>6.75</v>
       </c>
       <c r="BF123">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="BG123">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BH123">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI123">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="BJ123">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BK123">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="BL123">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="BM123">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="BN123">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="BO123">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP123">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="124" spans="1:68">
@@ -26513,7 +26513,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7452380</v>
+        <v>7452378</v>
       </c>
       <c r="C124" t="s">
         <v>68</v>
@@ -26528,190 +26528,190 @@
         <v>21</v>
       </c>
       <c r="G124" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H124" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O124" t="s">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="Q124">
+        <v>4.75</v>
+      </c>
+      <c r="R124">
         <v>2.38</v>
       </c>
-      <c r="R124">
+      <c r="S124">
+        <v>2.25</v>
+      </c>
+      <c r="T124">
+        <v>1.3</v>
+      </c>
+      <c r="U124">
+        <v>3.4</v>
+      </c>
+      <c r="V124">
+        <v>2.5</v>
+      </c>
+      <c r="W124">
+        <v>1.5</v>
+      </c>
+      <c r="X124">
+        <v>6</v>
+      </c>
+      <c r="Y124">
+        <v>1.13</v>
+      </c>
+      <c r="Z124">
+        <v>3.95</v>
+      </c>
+      <c r="AA124">
+        <v>3.9</v>
+      </c>
+      <c r="AB124">
+        <v>1.78</v>
+      </c>
+      <c r="AC124">
+        <v>1.03</v>
+      </c>
+      <c r="AD124">
+        <v>11</v>
+      </c>
+      <c r="AE124">
+        <v>1.18</v>
+      </c>
+      <c r="AF124">
+        <v>4.75</v>
+      </c>
+      <c r="AG124">
+        <v>1.55</v>
+      </c>
+      <c r="AH124">
         <v>2.2</v>
       </c>
-      <c r="S124">
-        <v>5</v>
-      </c>
-      <c r="T124">
-        <v>1.4</v>
-      </c>
-      <c r="U124">
-        <v>2.75</v>
-      </c>
-      <c r="V124">
-        <v>3</v>
-      </c>
-      <c r="W124">
+      <c r="AI124">
+        <v>1.67</v>
+      </c>
+      <c r="AJ124">
+        <v>2.1</v>
+      </c>
+      <c r="AK124">
+        <v>2.05</v>
+      </c>
+      <c r="AL124">
+        <v>1.18</v>
+      </c>
+      <c r="AM124">
+        <v>1.22</v>
+      </c>
+      <c r="AN124">
+        <v>1.2</v>
+      </c>
+      <c r="AO124">
+        <v>1.2</v>
+      </c>
+      <c r="AP124">
+        <v>1.09</v>
+      </c>
+      <c r="AQ124">
         <v>1.36</v>
       </c>
-      <c r="X124">
+      <c r="AR124">
+        <v>1.31</v>
+      </c>
+      <c r="AS124">
+        <v>1.53</v>
+      </c>
+      <c r="AT124">
+        <v>2.84</v>
+      </c>
+      <c r="AU124">
+        <v>4</v>
+      </c>
+      <c r="AV124">
+        <v>10</v>
+      </c>
+      <c r="AW124">
+        <v>9</v>
+      </c>
+      <c r="AX124">
+        <v>18</v>
+      </c>
+      <c r="AY124">
+        <v>17</v>
+      </c>
+      <c r="AZ124">
+        <v>35</v>
+      </c>
+      <c r="BA124">
         <v>8</v>
       </c>
-      <c r="Y124">
-        <v>1.08</v>
-      </c>
-      <c r="Z124">
-        <v>1.61</v>
-      </c>
-      <c r="AA124">
-        <v>4</v>
-      </c>
-      <c r="AB124">
-        <v>5</v>
-      </c>
-      <c r="AC124">
-        <v>1.02</v>
-      </c>
-      <c r="AD124">
-        <v>10</v>
-      </c>
-      <c r="AE124">
-        <v>1.29</v>
-      </c>
-      <c r="AF124">
-        <v>3.3</v>
-      </c>
-      <c r="AG124">
-        <v>1.89</v>
-      </c>
-      <c r="AH124">
-        <v>1.85</v>
-      </c>
-      <c r="AI124">
-        <v>1.91</v>
-      </c>
-      <c r="AJ124">
-        <v>1.91</v>
-      </c>
-      <c r="AK124">
-        <v>1.2</v>
-      </c>
-      <c r="AL124">
-        <v>1.26</v>
-      </c>
-      <c r="AM124">
-        <v>2.05</v>
-      </c>
-      <c r="AN124">
-        <v>1.6</v>
-      </c>
-      <c r="AO124">
-        <v>0.4</v>
-      </c>
-      <c r="AP124">
-        <v>1.45</v>
-      </c>
-      <c r="AQ124">
-        <v>0.64</v>
-      </c>
-      <c r="AR124">
-        <v>1.29</v>
-      </c>
-      <c r="AS124">
-        <v>1.16</v>
-      </c>
-      <c r="AT124">
-        <v>2.45</v>
-      </c>
-      <c r="AU124">
+      <c r="BB124">
         <v>7</v>
       </c>
-      <c r="AV124">
-        <v>4</v>
-      </c>
-      <c r="AW124">
-        <v>17</v>
-      </c>
-      <c r="AX124">
-        <v>5</v>
-      </c>
-      <c r="AY124">
-        <v>30</v>
-      </c>
-      <c r="AZ124">
-        <v>10</v>
-      </c>
-      <c r="BA124">
-        <v>6</v>
-      </c>
-      <c r="BB124">
-        <v>4</v>
-      </c>
       <c r="BC124">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD124">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="BE124">
         <v>6.75</v>
       </c>
       <c r="BF124">
-        <v>2.8</v>
+        <v>1.48</v>
       </c>
       <c r="BG124">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BH124">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BI124">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="BJ124">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="BK124">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="BL124">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BM124">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="BN124">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="BO124">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="BP124">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="125" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -322,10 +322,10 @@
     <t>['74']</t>
   </si>
   <si>
-    <t>['33', '35', '71', '74']</t>
+    <t>['24']</t>
   </si>
   <si>
-    <t>['24']</t>
+    <t>['33', '35', '71', '74']</t>
   </si>
   <si>
     <t>['6', '22', '32', '59', '65']</t>
@@ -379,10 +379,10 @@
     <t>['28', '39', '45+1']</t>
   </si>
   <si>
-    <t>['16', '45+3']</t>
+    <t>['27', '90+7']</t>
   </si>
   <si>
-    <t>['27', '90+7']</t>
+    <t>['16', '45+3']</t>
   </si>
   <si>
     <t>['13', '57', '73']</t>
@@ -457,10 +457,10 @@
     <t>['17']</t>
   </si>
   <si>
-    <t>['45+7']</t>
+    <t>['6', '44']</t>
   </si>
   <si>
-    <t>['6', '44']</t>
+    <t>['45+7']</t>
   </si>
   <si>
     <t>['34', '90+5']</t>
@@ -475,10 +475,10 @@
     <t>['6']</t>
   </si>
   <si>
-    <t>['8', '89']</t>
+    <t>['72']</t>
   </si>
   <si>
-    <t>['72']</t>
+    <t>['8', '89']</t>
   </si>
   <si>
     <t>['47']</t>
@@ -616,10 +616,10 @@
     <t>['65', '90+6']</t>
   </si>
   <si>
-    <t>['31']</t>
+    <t>['28', '48']</t>
   </si>
   <si>
-    <t>['28', '48']</t>
+    <t>['31']</t>
   </si>
   <si>
     <t>['58']</t>
@@ -709,10 +709,10 @@
     <t>['10', '13', '24', '42']</t>
   </si>
   <si>
-    <t>['10', '52', '61', '71', '83']</t>
+    <t>['50']</t>
   </si>
   <si>
-    <t>['50']</t>
+    <t>['10', '52', '61', '71', '83']</t>
   </si>
   <si>
     <t>['88']</t>
@@ -5295,7 +5295,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>7452274</v>
+        <v>7452275</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -5310,88 +5310,88 @@
         <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>2</v>
       </c>
       <c r="O21" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="S21">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="T21">
+        <v>1.25</v>
+      </c>
+      <c r="U21">
+        <v>3.55</v>
+      </c>
+      <c r="V21">
+        <v>2.15</v>
+      </c>
+      <c r="W21">
+        <v>1.62</v>
+      </c>
+      <c r="X21">
+        <v>4.4</v>
+      </c>
+      <c r="Y21">
+        <v>1.17</v>
+      </c>
+      <c r="Z21">
         <v>1.33</v>
       </c>
-      <c r="U21">
-        <v>3</v>
-      </c>
-      <c r="V21">
-        <v>2.45</v>
-      </c>
-      <c r="W21">
+      <c r="AA21">
+        <v>5</v>
+      </c>
+      <c r="AB21">
+        <v>9</v>
+      </c>
+      <c r="AC21">
+        <v>1.02</v>
+      </c>
+      <c r="AD21">
+        <v>20</v>
+      </c>
+      <c r="AE21">
+        <v>1.17</v>
+      </c>
+      <c r="AF21">
+        <v>5</v>
+      </c>
+      <c r="AG21">
         <v>1.48</v>
       </c>
-      <c r="X21">
-        <v>6.2</v>
-      </c>
-      <c r="Y21">
-        <v>1.1</v>
-      </c>
-      <c r="Z21">
-        <v>1.9</v>
-      </c>
-      <c r="AA21">
-        <v>3.4</v>
-      </c>
-      <c r="AB21">
-        <v>4.1</v>
-      </c>
-      <c r="AC21">
-        <v>1.05</v>
-      </c>
-      <c r="AD21">
-        <v>9.5</v>
-      </c>
-      <c r="AE21">
-        <v>1.25</v>
-      </c>
-      <c r="AF21">
-        <v>3.95</v>
-      </c>
-      <c r="AG21">
-        <v>1.95</v>
-      </c>
       <c r="AH21">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AI21">
         <v>1.75</v>
@@ -5400,100 +5400,100 @@
         <v>2</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AL21">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AM21">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="AQ21">
-        <v>1.55</v>
+        <v>0.64</v>
       </c>
       <c r="AR21">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AS21">
-        <v>1.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT21">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AU21">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AV21">
         <v>4</v>
       </c>
       <c r="AW21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY21">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AZ21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA21">
         <v>12</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC21">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD21">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="BE21">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF21">
-        <v>2.86</v>
+        <v>4.66</v>
       </c>
       <c r="BG21">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="BH21">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="BI21">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="BJ21">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BK21">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BL21">
+        <v>2.34</v>
+      </c>
+      <c r="BM21">
         <v>1.98</v>
       </c>
-      <c r="BM21">
-        <v>2.25</v>
-      </c>
       <c r="BN21">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="BO21">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="BP21">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22" spans="1:68">
@@ -5501,7 +5501,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>7452275</v>
+        <v>7452274</v>
       </c>
       <c r="C22" t="s">
         <v>68</v>
@@ -5516,88 +5516,88 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22">
         <v>2</v>
       </c>
       <c r="O22" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="Q22">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="T22">
+        <v>1.33</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>2.45</v>
+      </c>
+      <c r="W22">
+        <v>1.48</v>
+      </c>
+      <c r="X22">
+        <v>6.2</v>
+      </c>
+      <c r="Y22">
+        <v>1.1</v>
+      </c>
+      <c r="Z22">
+        <v>1.9</v>
+      </c>
+      <c r="AA22">
+        <v>3.4</v>
+      </c>
+      <c r="AB22">
+        <v>4.1</v>
+      </c>
+      <c r="AC22">
+        <v>1.05</v>
+      </c>
+      <c r="AD22">
+        <v>9.5</v>
+      </c>
+      <c r="AE22">
         <v>1.25</v>
       </c>
-      <c r="U22">
-        <v>3.55</v>
-      </c>
-      <c r="V22">
-        <v>2.15</v>
-      </c>
-      <c r="W22">
-        <v>1.62</v>
-      </c>
-      <c r="X22">
-        <v>4.4</v>
-      </c>
-      <c r="Y22">
-        <v>1.17</v>
-      </c>
-      <c r="Z22">
-        <v>1.33</v>
-      </c>
-      <c r="AA22">
-        <v>5</v>
-      </c>
-      <c r="AB22">
-        <v>9</v>
-      </c>
-      <c r="AC22">
-        <v>1.02</v>
-      </c>
-      <c r="AD22">
-        <v>20</v>
-      </c>
-      <c r="AE22">
-        <v>1.17</v>
-      </c>
       <c r="AF22">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AG22">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AH22">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AI22">
         <v>1.75</v>
@@ -5606,100 +5606,100 @@
         <v>2</v>
       </c>
       <c r="AK22">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AL22">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AM22">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="AQ22">
-        <v>0.64</v>
+        <v>1.55</v>
       </c>
       <c r="AR22">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AS22">
-        <v>0.8100000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="AT22">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="AU22">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AV22">
         <v>4</v>
       </c>
       <c r="AW22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY22">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AZ22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA22">
         <v>12</v>
       </c>
       <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>12</v>
+      </c>
+      <c r="BD22">
+        <v>1.64</v>
+      </c>
+      <c r="BE22">
+        <v>7.6</v>
+      </c>
+      <c r="BF22">
+        <v>2.86</v>
+      </c>
+      <c r="BG22">
+        <v>1.24</v>
+      </c>
+      <c r="BH22">
+        <v>3.55</v>
+      </c>
+      <c r="BI22">
+        <v>1.49</v>
+      </c>
+      <c r="BJ22">
+        <v>2.45</v>
+      </c>
+      <c r="BK22">
+        <v>2.25</v>
+      </c>
+      <c r="BL22">
+        <v>1.98</v>
+      </c>
+      <c r="BM22">
+        <v>2.25</v>
+      </c>
+      <c r="BN22">
+        <v>1.59</v>
+      </c>
+      <c r="BO22">
         <v>3</v>
       </c>
-      <c r="BC22">
-        <v>15</v>
-      </c>
-      <c r="BD22">
-        <v>1.28</v>
-      </c>
-      <c r="BE22">
-        <v>10.5</v>
-      </c>
-      <c r="BF22">
-        <v>4.66</v>
-      </c>
-      <c r="BG22">
-        <v>1.13</v>
-      </c>
-      <c r="BH22">
-        <v>4.75</v>
-      </c>
-      <c r="BI22">
-        <v>1.28</v>
-      </c>
-      <c r="BJ22">
-        <v>3.2</v>
-      </c>
-      <c r="BK22">
-        <v>1.91</v>
-      </c>
-      <c r="BL22">
-        <v>2.34</v>
-      </c>
-      <c r="BM22">
-        <v>1.98</v>
-      </c>
-      <c r="BN22">
-        <v>1.82</v>
-      </c>
-      <c r="BO22">
-        <v>2.41</v>
-      </c>
       <c r="BP22">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="23" spans="1:68">
@@ -6531,7 +6531,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7452281</v>
+        <v>7452280</v>
       </c>
       <c r="C27" t="s">
         <v>68</v>
@@ -6546,28 +6546,28 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
         <v>3</v>
-      </c>
-      <c r="L27">
-        <v>4</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>5</v>
       </c>
       <c r="O27" t="s">
         <v>102</v>
@@ -6576,160 +6576,160 @@
         <v>200</v>
       </c>
       <c r="Q27">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="T27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA27">
+        <v>3.8</v>
+      </c>
+      <c r="AB27">
+        <v>4.75</v>
+      </c>
+      <c r="AC27">
+        <v>1.03</v>
+      </c>
+      <c r="AD27">
+        <v>12.5</v>
+      </c>
+      <c r="AE27">
+        <v>1.27</v>
+      </c>
+      <c r="AF27">
         <v>3.7</v>
       </c>
-      <c r="AB27">
-        <v>2</v>
-      </c>
-      <c r="AC27">
-        <v>1.02</v>
-      </c>
-      <c r="AD27">
-        <v>14.5</v>
-      </c>
-      <c r="AE27">
-        <v>1.22</v>
-      </c>
-      <c r="AF27">
-        <v>4.3</v>
-      </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH27">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AI27">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ27">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK27">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AL27">
         <v>1.22</v>
       </c>
       <c r="AM27">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AQ27">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AR27">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AS27">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
+        <v>6</v>
+      </c>
+      <c r="AW27">
+        <v>5</v>
+      </c>
+      <c r="AX27">
+        <v>6</v>
+      </c>
+      <c r="AY27">
+        <v>16</v>
+      </c>
+      <c r="AZ27">
+        <v>14</v>
+      </c>
+      <c r="BA27">
         <v>7</v>
-      </c>
-      <c r="AV27">
-        <v>4</v>
-      </c>
-      <c r="AW27">
-        <v>4</v>
-      </c>
-      <c r="AX27">
-        <v>7</v>
-      </c>
-      <c r="AY27">
-        <v>12</v>
-      </c>
-      <c r="AZ27">
-        <v>13</v>
-      </c>
-      <c r="BA27">
-        <v>3</v>
       </c>
       <c r="BB27">
         <v>3</v>
       </c>
       <c r="BC27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD27">
-        <v>2.81</v>
+        <v>1.5</v>
       </c>
       <c r="BE27">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF27">
-        <v>1.65</v>
+        <v>3.34</v>
       </c>
       <c r="BG27">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH27">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BI27">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="BJ27">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="BK27">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BL27">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BM27">
+        <v>1.8</v>
+      </c>
+      <c r="BN27">
+        <v>1.92</v>
+      </c>
+      <c r="BO27">
         <v>2.25</v>
       </c>
-      <c r="BN27">
+      <c r="BP27">
         <v>1.59</v>
-      </c>
-      <c r="BO27">
-        <v>2.88</v>
-      </c>
-      <c r="BP27">
-        <v>1.35</v>
       </c>
     </row>
     <row r="28" spans="1:68">
@@ -6737,7 +6737,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>7452280</v>
+        <v>7452281</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -6752,28 +6752,28 @@
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O28" t="s">
         <v>103</v>
@@ -6782,160 +6782,160 @@
         <v>201</v>
       </c>
       <c r="Q28">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="T28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB28">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD28">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE28">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH28">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI28">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AJ28">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK28">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AL28">
         <v>1.22</v>
       </c>
       <c r="AM28">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AN28">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AQ28">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="AR28">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT28">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AU28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY28">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB28">
         <v>3</v>
       </c>
       <c r="BC28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD28">
-        <v>1.5</v>
+        <v>2.81</v>
       </c>
       <c r="BE28">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF28">
-        <v>3.34</v>
+        <v>1.65</v>
       </c>
       <c r="BG28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH28">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BI28">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="BJ28">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="BK28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BL28">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BM28">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BN28">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="BO28">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="BP28">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="29" spans="1:68">
@@ -10281,7 +10281,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11475,7 +11475,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7452306</v>
+        <v>7452303</v>
       </c>
       <c r="C51" t="s">
         <v>68</v>
@@ -11490,49 +11490,49 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
         <v>3</v>
-      </c>
-      <c r="L51">
-        <v>2</v>
-      </c>
-      <c r="M51">
-        <v>2</v>
-      </c>
-      <c r="N51">
-        <v>4</v>
       </c>
       <c r="O51" t="s">
         <v>121</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
+        <v>101</v>
       </c>
       <c r="Q51">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="T51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U51">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V51">
         <v>2.5</v>
@@ -11541,139 +11541,139 @@
         <v>1.5</v>
       </c>
       <c r="X51">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA51">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AC51">
         <v>1.01</v>
       </c>
       <c r="AD51">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF51">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG51">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH51">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AI51">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AJ51">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK51">
+        <v>1.29</v>
+      </c>
+      <c r="AL51">
+        <v>1.28</v>
+      </c>
+      <c r="AM51">
+        <v>1.84</v>
+      </c>
+      <c r="AN51">
+        <v>0.67</v>
+      </c>
+      <c r="AO51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>0.82</v>
+      </c>
+      <c r="AQ51">
+        <v>0.36</v>
+      </c>
+      <c r="AR51">
+        <v>1.45</v>
+      </c>
+      <c r="AS51">
+        <v>1.24</v>
+      </c>
+      <c r="AT51">
+        <v>2.69</v>
+      </c>
+      <c r="AU51">
+        <v>7</v>
+      </c>
+      <c r="AV51">
+        <v>4</v>
+      </c>
+      <c r="AW51">
+        <v>5</v>
+      </c>
+      <c r="AX51">
+        <v>4</v>
+      </c>
+      <c r="AY51">
+        <v>16</v>
+      </c>
+      <c r="AZ51">
+        <v>10</v>
+      </c>
+      <c r="BA51">
+        <v>4</v>
+      </c>
+      <c r="BB51">
+        <v>2</v>
+      </c>
+      <c r="BC51">
+        <v>6</v>
+      </c>
+      <c r="BD51">
+        <v>1.55</v>
+      </c>
+      <c r="BE51">
+        <v>8.5</v>
+      </c>
+      <c r="BF51">
+        <v>2.91</v>
+      </c>
+      <c r="BG51">
+        <v>1.21</v>
+      </c>
+      <c r="BH51">
+        <v>4.1</v>
+      </c>
+      <c r="BI51">
+        <v>1.4</v>
+      </c>
+      <c r="BJ51">
+        <v>2.8</v>
+      </c>
+      <c r="BK51">
+        <v>2</v>
+      </c>
+      <c r="BL51">
+        <v>2.13</v>
+      </c>
+      <c r="BM51">
+        <v>2.08</v>
+      </c>
+      <c r="BN51">
         <v>1.7</v>
       </c>
-      <c r="AL51">
-        <v>1.29</v>
-      </c>
-      <c r="AM51">
-        <v>1.36</v>
-      </c>
-      <c r="AN51">
-        <v>1.5</v>
-      </c>
-      <c r="AO51">
-        <v>2</v>
-      </c>
-      <c r="AP51">
-        <v>1.64</v>
-      </c>
-      <c r="AQ51">
-        <v>1.36</v>
-      </c>
-      <c r="AR51">
-        <v>1.41</v>
-      </c>
-      <c r="AS51">
-        <v>1.48</v>
-      </c>
-      <c r="AT51">
-        <v>2.89</v>
-      </c>
-      <c r="AU51">
-        <v>5</v>
-      </c>
-      <c r="AV51">
-        <v>7</v>
-      </c>
-      <c r="AW51">
-        <v>8</v>
-      </c>
-      <c r="AX51">
-        <v>3</v>
-      </c>
-      <c r="AY51">
-        <v>18</v>
-      </c>
-      <c r="AZ51">
-        <v>14</v>
-      </c>
-      <c r="BA51">
-        <v>6</v>
-      </c>
-      <c r="BB51">
-        <v>4</v>
-      </c>
-      <c r="BC51">
-        <v>10</v>
-      </c>
-      <c r="BD51">
-        <v>2.58</v>
-      </c>
-      <c r="BE51">
-        <v>6.85</v>
-      </c>
-      <c r="BF51">
-        <v>1.81</v>
-      </c>
-      <c r="BG51">
-        <v>1.11</v>
-      </c>
-      <c r="BH51">
-        <v>4.55</v>
-      </c>
-      <c r="BI51">
-        <v>1.26</v>
-      </c>
-      <c r="BJ51">
-        <v>3.08</v>
-      </c>
-      <c r="BK51">
-        <v>2.1</v>
-      </c>
-      <c r="BL51">
-        <v>2.32</v>
-      </c>
-      <c r="BM51">
-        <v>1.89</v>
-      </c>
-      <c r="BN51">
-        <v>1.85</v>
-      </c>
       <c r="BO51">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BP51">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="52" spans="1:68">
@@ -11681,7 +11681,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7452303</v>
+        <v>7452306</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -11696,49 +11696,49 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52">
         <v>2</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" t="s">
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U52">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V52">
         <v>2.5</v>
@@ -11747,139 +11747,139 @@
         <v>1.5</v>
       </c>
       <c r="X52">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA52">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB52">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
         <v>1.01</v>
       </c>
       <c r="AD52">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF52">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG52">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH52">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AI52">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AJ52">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK52">
+        <v>1.7</v>
+      </c>
+      <c r="AL52">
         <v>1.29</v>
       </c>
-      <c r="AL52">
-        <v>1.28</v>
-      </c>
       <c r="AM52">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AN52">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="AQ52">
-        <v>0.36</v>
+        <v>1.36</v>
       </c>
       <c r="AR52">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AS52">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AT52">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="AU52">
+        <v>5</v>
+      </c>
+      <c r="AV52">
         <v>7</v>
       </c>
-      <c r="AV52">
+      <c r="AW52">
+        <v>8</v>
+      </c>
+      <c r="AX52">
+        <v>3</v>
+      </c>
+      <c r="AY52">
+        <v>18</v>
+      </c>
+      <c r="AZ52">
+        <v>14</v>
+      </c>
+      <c r="BA52">
+        <v>6</v>
+      </c>
+      <c r="BB52">
         <v>4</v>
       </c>
-      <c r="AW52">
-        <v>5</v>
-      </c>
-      <c r="AX52">
-        <v>4</v>
-      </c>
-      <c r="AY52">
-        <v>16</v>
-      </c>
-      <c r="AZ52">
+      <c r="BC52">
         <v>10</v>
       </c>
-      <c r="BA52">
-        <v>4</v>
-      </c>
-      <c r="BB52">
-        <v>2</v>
-      </c>
-      <c r="BC52">
-        <v>6</v>
-      </c>
       <c r="BD52">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="BE52">
-        <v>8.5</v>
+        <v>6.85</v>
       </c>
       <c r="BF52">
-        <v>2.91</v>
+        <v>1.81</v>
       </c>
       <c r="BG52">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BH52">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="BI52">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="BJ52">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="BK52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BL52">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="BM52">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="BN52">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="BO52">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="BP52">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="53" spans="1:68">
@@ -12753,7 +12753,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q57">
         <v>2.25</v>
@@ -15183,7 +15183,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>7452325</v>
+        <v>7452324</v>
       </c>
       <c r="C69" t="s">
         <v>68</v>
@@ -15198,10 +15198,10 @@
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -15216,70 +15216,70 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="Q69">
         <v>3.6</v>
       </c>
       <c r="R69">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
         <v>2.75</v>
       </c>
       <c r="T69">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U69">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V69">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W69">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X69">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y69">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z69">
         <v>3.1</v>
       </c>
       <c r="AA69">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB69">
         <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AD69">
-        <v>13</v>
+        <v>1.07</v>
       </c>
       <c r="AE69">
-        <v>3.92</v>
+        <v>1.24</v>
       </c>
       <c r="AF69">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="AG69">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH69">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AI69">
         <v>1.62</v>
@@ -15288,100 +15288,100 @@
         <v>2.2</v>
       </c>
       <c r="AK69">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AM69">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1.8</v>
+        <v>0.83</v>
       </c>
       <c r="AO69">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
-        <v>1.55</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
         <v>1.17</v>
       </c>
       <c r="AS69">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AT69">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="AU69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV69">
         <v>6</v>
       </c>
       <c r="AW69">
+        <v>6</v>
+      </c>
+      <c r="AX69">
+        <v>5</v>
+      </c>
+      <c r="AY69">
         <v>11</v>
       </c>
-      <c r="AX69">
-        <v>6</v>
-      </c>
-      <c r="AY69">
-        <v>24</v>
-      </c>
       <c r="AZ69">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA69">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BB69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC69">
+        <v>14</v>
+      </c>
+      <c r="BD69">
+        <v>2.23</v>
+      </c>
+      <c r="BE69">
         <v>7</v>
       </c>
-      <c r="BD69">
-        <v>2.37</v>
-      </c>
-      <c r="BE69">
-        <v>6.5</v>
-      </c>
       <c r="BF69">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="BG69">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BH69">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="BI69">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BJ69">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="BK69">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL69">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BM69">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BN69">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BO69">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BP69">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="70" spans="1:68">
@@ -15389,7 +15389,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>7452324</v>
+        <v>7452325</v>
       </c>
       <c r="C70" t="s">
         <v>68</v>
@@ -15404,10 +15404,10 @@
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -15422,70 +15422,70 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="s">
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
         <v>2.75</v>
       </c>
       <c r="T70">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U70">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V70">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W70">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X70">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y70">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z70">
         <v>3.1</v>
       </c>
       <c r="AA70">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB70">
         <v>2.15</v>
       </c>
       <c r="AC70">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AD70">
-        <v>1.07</v>
+        <v>13</v>
       </c>
       <c r="AE70">
-        <v>1.24</v>
+        <v>3.92</v>
       </c>
       <c r="AF70">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="AG70">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH70">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI70">
         <v>1.62</v>
@@ -15494,100 +15494,100 @@
         <v>2.2</v>
       </c>
       <c r="AK70">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AM70">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AN70">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO70">
-        <v>0.83</v>
+        <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ70">
-        <v>0.73</v>
+        <v>1.55</v>
       </c>
       <c r="AR70">
         <v>1.17</v>
       </c>
       <c r="AS70">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AT70">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="AU70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV70">
         <v>6</v>
       </c>
       <c r="AW70">
+        <v>11</v>
+      </c>
+      <c r="AX70">
         <v>6</v>
       </c>
-      <c r="AX70">
-        <v>5</v>
-      </c>
       <c r="AY70">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AZ70">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC70">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD70">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="BE70">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BF70">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="BG70">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BH70">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BI70">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BJ70">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="BK70">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL70">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BM70">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BN70">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BO70">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BP70">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="71" spans="1:68">
@@ -17655,7 +17655,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>7452337</v>
+        <v>7452335</v>
       </c>
       <c r="C81" t="s">
         <v>68</v>
@@ -17670,28 +17670,28 @@
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H81" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81">
         <v>2</v>
       </c>
       <c r="L81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O81" t="s">
         <v>147</v>
@@ -17700,160 +17700,160 @@
         <v>231</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S81">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="T81">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U81">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="V81">
+        <v>2.2</v>
+      </c>
+      <c r="W81">
+        <v>1.62</v>
+      </c>
+      <c r="X81">
+        <v>5</v>
+      </c>
+      <c r="Y81">
+        <v>1.17</v>
+      </c>
+      <c r="Z81">
+        <v>1.5</v>
+      </c>
+      <c r="AA81">
+        <v>4.33</v>
+      </c>
+      <c r="AB81">
+        <v>6</v>
+      </c>
+      <c r="AC81">
+        <v>1.01</v>
+      </c>
+      <c r="AD81">
+        <v>13</v>
+      </c>
+      <c r="AE81">
+        <v>1.17</v>
+      </c>
+      <c r="AF81">
+        <v>5</v>
+      </c>
+      <c r="AG81">
+        <v>1.5</v>
+      </c>
+      <c r="AH81">
         <v>2.5</v>
       </c>
-      <c r="W81">
-        <v>1.5</v>
-      </c>
-      <c r="X81">
-        <v>6.5</v>
-      </c>
-      <c r="Y81">
-        <v>1.11</v>
-      </c>
-      <c r="Z81">
-        <v>2.38</v>
-      </c>
-      <c r="AA81">
+      <c r="AI81">
+        <v>1.62</v>
+      </c>
+      <c r="AJ81">
+        <v>2.2</v>
+      </c>
+      <c r="AK81">
+        <v>1.15</v>
+      </c>
+      <c r="AL81">
+        <v>1.18</v>
+      </c>
+      <c r="AM81">
+        <v>2.3</v>
+      </c>
+      <c r="AN81">
+        <v>1.86</v>
+      </c>
+      <c r="AO81">
+        <v>0.86</v>
+      </c>
+      <c r="AP81">
+        <v>2.27</v>
+      </c>
+      <c r="AQ81">
+        <v>0.73</v>
+      </c>
+      <c r="AR81">
+        <v>1.65</v>
+      </c>
+      <c r="AS81">
+        <v>1.45</v>
+      </c>
+      <c r="AT81">
+        <v>3.1</v>
+      </c>
+      <c r="AU81">
+        <v>8</v>
+      </c>
+      <c r="AV81">
+        <v>4</v>
+      </c>
+      <c r="AW81">
+        <v>7</v>
+      </c>
+      <c r="AX81">
+        <v>2</v>
+      </c>
+      <c r="AY81">
+        <v>23</v>
+      </c>
+      <c r="AZ81">
+        <v>9</v>
+      </c>
+      <c r="BA81">
+        <v>6</v>
+      </c>
+      <c r="BB81">
+        <v>4</v>
+      </c>
+      <c r="BC81">
+        <v>10</v>
+      </c>
+      <c r="BD81">
+        <v>1.2</v>
+      </c>
+      <c r="BE81">
+        <v>9.6</v>
+      </c>
+      <c r="BF81">
+        <v>5.15</v>
+      </c>
+      <c r="BG81">
+        <v>1.22</v>
+      </c>
+      <c r="BH81">
+        <v>3.9</v>
+      </c>
+      <c r="BI81">
+        <v>1.25</v>
+      </c>
+      <c r="BJ81">
         <v>3.5</v>
       </c>
-      <c r="AB81">
-        <v>2.75</v>
-      </c>
-      <c r="AC81">
-        <v>1.04</v>
-      </c>
-      <c r="AD81">
-        <v>10</v>
-      </c>
-      <c r="AE81">
-        <v>1.22</v>
-      </c>
-      <c r="AF81">
-        <v>4.2</v>
-      </c>
-      <c r="AG81">
-        <v>1.67</v>
-      </c>
-      <c r="AH81">
-        <v>2.15</v>
-      </c>
-      <c r="AI81">
-        <v>1.57</v>
-      </c>
-      <c r="AJ81">
-        <v>2.25</v>
-      </c>
-      <c r="AK81">
-        <v>1.38</v>
-      </c>
-      <c r="AL81">
-        <v>1.22</v>
-      </c>
-      <c r="AM81">
-        <v>1.62</v>
-      </c>
-      <c r="AN81">
-        <v>3</v>
-      </c>
-      <c r="AO81">
-        <v>1.14</v>
-      </c>
-      <c r="AP81">
-        <v>2.73</v>
-      </c>
-      <c r="AQ81">
-        <v>1.18</v>
-      </c>
-      <c r="AR81">
-        <v>1.78</v>
-      </c>
-      <c r="AS81">
-        <v>1.78</v>
-      </c>
-      <c r="AT81">
-        <v>3.56</v>
-      </c>
-      <c r="AU81">
-        <v>7</v>
-      </c>
-      <c r="AV81">
-        <v>12</v>
-      </c>
-      <c r="AW81">
-        <v>5</v>
-      </c>
-      <c r="AX81">
-        <v>4</v>
-      </c>
-      <c r="AY81">
-        <v>15</v>
-      </c>
-      <c r="AZ81">
-        <v>17</v>
-      </c>
-      <c r="BA81">
-        <v>5</v>
-      </c>
-      <c r="BB81">
-        <v>2</v>
-      </c>
-      <c r="BC81">
-        <v>7</v>
-      </c>
-      <c r="BD81">
+      <c r="BK81">
+        <v>2</v>
+      </c>
+      <c r="BL81">
+        <v>2.45</v>
+      </c>
+      <c r="BM81">
         <v>1.82</v>
       </c>
-      <c r="BE81">
-        <v>7.2</v>
-      </c>
-      <c r="BF81">
-        <v>2.25</v>
-      </c>
-      <c r="BG81">
-        <v>1.12</v>
-      </c>
-      <c r="BH81">
-        <v>4.5</v>
-      </c>
-      <c r="BI81">
-        <v>1.28</v>
-      </c>
-      <c r="BJ81">
-        <v>3.25</v>
-      </c>
-      <c r="BK81">
-        <v>2</v>
-      </c>
-      <c r="BL81">
-        <v>2.35</v>
-      </c>
-      <c r="BM81">
-        <v>1.88</v>
-      </c>
       <c r="BN81">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BO81">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BP81">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="82" spans="1:68">
@@ -17861,7 +17861,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>7452335</v>
+        <v>7452337</v>
       </c>
       <c r="C82" t="s">
         <v>68</v>
@@ -17876,28 +17876,28 @@
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82">
         <v>2</v>
       </c>
       <c r="L82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O82" t="s">
         <v>148</v>
@@ -17906,160 +17906,160 @@
         <v>232</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="T82">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="U82">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="V82">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="W82">
+        <v>1.5</v>
+      </c>
+      <c r="X82">
+        <v>6.5</v>
+      </c>
+      <c r="Y82">
+        <v>1.11</v>
+      </c>
+      <c r="Z82">
+        <v>2.38</v>
+      </c>
+      <c r="AA82">
+        <v>3.5</v>
+      </c>
+      <c r="AB82">
+        <v>2.75</v>
+      </c>
+      <c r="AC82">
+        <v>1.04</v>
+      </c>
+      <c r="AD82">
+        <v>10</v>
+      </c>
+      <c r="AE82">
+        <v>1.22</v>
+      </c>
+      <c r="AF82">
+        <v>4.2</v>
+      </c>
+      <c r="AG82">
+        <v>1.67</v>
+      </c>
+      <c r="AH82">
+        <v>2.15</v>
+      </c>
+      <c r="AI82">
+        <v>1.57</v>
+      </c>
+      <c r="AJ82">
+        <v>2.25</v>
+      </c>
+      <c r="AK82">
+        <v>1.38</v>
+      </c>
+      <c r="AL82">
+        <v>1.22</v>
+      </c>
+      <c r="AM82">
         <v>1.62</v>
       </c>
-      <c r="X82">
+      <c r="AN82">
+        <v>3</v>
+      </c>
+      <c r="AO82">
+        <v>1.14</v>
+      </c>
+      <c r="AP82">
+        <v>2.73</v>
+      </c>
+      <c r="AQ82">
+        <v>1.18</v>
+      </c>
+      <c r="AR82">
+        <v>1.78</v>
+      </c>
+      <c r="AS82">
+        <v>1.78</v>
+      </c>
+      <c r="AT82">
+        <v>3.56</v>
+      </c>
+      <c r="AU82">
+        <v>7</v>
+      </c>
+      <c r="AV82">
+        <v>12</v>
+      </c>
+      <c r="AW82">
         <v>5</v>
       </c>
-      <c r="Y82">
-        <v>1.17</v>
-      </c>
-      <c r="Z82">
-        <v>1.5</v>
-      </c>
-      <c r="AA82">
-        <v>4.33</v>
-      </c>
-      <c r="AB82">
-        <v>6</v>
-      </c>
-      <c r="AC82">
-        <v>1.01</v>
-      </c>
-      <c r="AD82">
-        <v>13</v>
-      </c>
-      <c r="AE82">
-        <v>1.17</v>
-      </c>
-      <c r="AF82">
+      <c r="AX82">
+        <v>4</v>
+      </c>
+      <c r="AY82">
+        <v>15</v>
+      </c>
+      <c r="AZ82">
+        <v>17</v>
+      </c>
+      <c r="BA82">
         <v>5</v>
       </c>
-      <c r="AG82">
-        <v>1.5</v>
-      </c>
-      <c r="AH82">
+      <c r="BB82">
+        <v>2</v>
+      </c>
+      <c r="BC82">
+        <v>7</v>
+      </c>
+      <c r="BD82">
+        <v>1.82</v>
+      </c>
+      <c r="BE82">
+        <v>7.2</v>
+      </c>
+      <c r="BF82">
+        <v>2.25</v>
+      </c>
+      <c r="BG82">
+        <v>1.12</v>
+      </c>
+      <c r="BH82">
+        <v>4.5</v>
+      </c>
+      <c r="BI82">
+        <v>1.28</v>
+      </c>
+      <c r="BJ82">
+        <v>3.25</v>
+      </c>
+      <c r="BK82">
+        <v>2</v>
+      </c>
+      <c r="BL82">
+        <v>2.35</v>
+      </c>
+      <c r="BM82">
+        <v>1.88</v>
+      </c>
+      <c r="BN82">
+        <v>1.8</v>
+      </c>
+      <c r="BO82">
         <v>2.5</v>
       </c>
-      <c r="AI82">
-        <v>1.62</v>
-      </c>
-      <c r="AJ82">
-        <v>2.2</v>
-      </c>
-      <c r="AK82">
-        <v>1.15</v>
-      </c>
-      <c r="AL82">
-        <v>1.18</v>
-      </c>
-      <c r="AM82">
-        <v>2.3</v>
-      </c>
-      <c r="AN82">
-        <v>1.86</v>
-      </c>
-      <c r="AO82">
-        <v>0.86</v>
-      </c>
-      <c r="AP82">
-        <v>2.27</v>
-      </c>
-      <c r="AQ82">
-        <v>0.73</v>
-      </c>
-      <c r="AR82">
-        <v>1.65</v>
-      </c>
-      <c r="AS82">
-        <v>1.45</v>
-      </c>
-      <c r="AT82">
-        <v>3.1</v>
-      </c>
-      <c r="AU82">
-        <v>8</v>
-      </c>
-      <c r="AV82">
-        <v>4</v>
-      </c>
-      <c r="AW82">
-        <v>7</v>
-      </c>
-      <c r="AX82">
-        <v>2</v>
-      </c>
-      <c r="AY82">
-        <v>23</v>
-      </c>
-      <c r="AZ82">
-        <v>9</v>
-      </c>
-      <c r="BA82">
-        <v>6</v>
-      </c>
-      <c r="BB82">
-        <v>4</v>
-      </c>
-      <c r="BC82">
-        <v>10</v>
-      </c>
-      <c r="BD82">
-        <v>1.2</v>
-      </c>
-      <c r="BE82">
-        <v>9.6</v>
-      </c>
-      <c r="BF82">
-        <v>5.15</v>
-      </c>
-      <c r="BG82">
-        <v>1.22</v>
-      </c>
-      <c r="BH82">
-        <v>3.9</v>
-      </c>
-      <c r="BI82">
-        <v>1.25</v>
-      </c>
-      <c r="BJ82">
-        <v>3.5</v>
-      </c>
-      <c r="BK82">
-        <v>2</v>
-      </c>
-      <c r="BL82">
-        <v>2.45</v>
-      </c>
-      <c r="BM82">
-        <v>1.82</v>
-      </c>
-      <c r="BN82">
-        <v>1.85</v>
-      </c>
-      <c r="BO82">
-        <v>2.42</v>
-      </c>
       <c r="BP82">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="83" spans="1:68">
@@ -18727,7 +18727,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18891,7 +18891,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7452344</v>
+        <v>7452342</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18906,43 +18906,43 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
       <c r="Q87">
+        <v>3.25</v>
+      </c>
+      <c r="R87">
+        <v>2.25</v>
+      </c>
+      <c r="S87">
         <v>3</v>
-      </c>
-      <c r="R87">
-        <v>2.2</v>
-      </c>
-      <c r="S87">
-        <v>3.4</v>
       </c>
       <c r="T87">
         <v>1.33</v>
@@ -18957,73 +18957,73 @@
         <v>1.44</v>
       </c>
       <c r="X87">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z87">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AA87">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB87">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC87">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD87">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF87">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AG87">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH87">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI87">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK87">
+        <v>1.57</v>
+      </c>
+      <c r="AL87">
+        <v>1.22</v>
+      </c>
+      <c r="AM87">
         <v>1.45</v>
       </c>
-      <c r="AL87">
-        <v>1.25</v>
-      </c>
-      <c r="AM87">
-        <v>1.53</v>
-      </c>
       <c r="AN87">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="AO87">
-        <v>0.71</v>
+        <v>1.86</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AQ87">
-        <v>0.82</v>
+        <v>1.55</v>
       </c>
       <c r="AR87">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AS87">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AT87">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AU87">
         <v>5</v>
@@ -19032,64 +19032,64 @@
         <v>4</v>
       </c>
       <c r="AW87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX87">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY87">
         <v>13</v>
       </c>
       <c r="AZ87">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC87">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD87">
         <v>2.02</v>
       </c>
       <c r="BE87">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="BF87">
+        <v>1.86</v>
+      </c>
+      <c r="BG87">
+        <v>1.26</v>
+      </c>
+      <c r="BH87">
+        <v>3.4</v>
+      </c>
+      <c r="BI87">
+        <v>1.41</v>
+      </c>
+      <c r="BJ87">
+        <v>2.68</v>
+      </c>
+      <c r="BK87">
+        <v>2.1</v>
+      </c>
+      <c r="BL87">
+        <v>2.04</v>
+      </c>
+      <c r="BM87">
         <v>2.12</v>
       </c>
-      <c r="BG87">
-        <v>1.1</v>
-      </c>
-      <c r="BH87">
-        <v>4.75</v>
-      </c>
-      <c r="BI87">
-        <v>1.3</v>
-      </c>
-      <c r="BJ87">
-        <v>3.2</v>
-      </c>
-      <c r="BK87">
-        <v>1.83</v>
-      </c>
-      <c r="BL87">
-        <v>2.35</v>
-      </c>
-      <c r="BM87">
-        <v>1.9</v>
-      </c>
       <c r="BN87">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="BO87">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="BP87">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="88" spans="1:68">
@@ -19097,7 +19097,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>7452342</v>
+        <v>7452344</v>
       </c>
       <c r="C88" t="s">
         <v>68</v>
@@ -19112,43 +19112,43 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O88" t="s">
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>87</v>
+        <v>236</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S88">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T88">
         <v>1.33</v>
@@ -19163,73 +19163,73 @@
         <v>1.44</v>
       </c>
       <c r="X88">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AA88">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB88">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC88">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD88">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AE88">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AG88">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH88">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI88">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ88">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK88">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL88">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM88">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AN88">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="AO88">
-        <v>1.86</v>
+        <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
-        <v>1.55</v>
+        <v>0.82</v>
       </c>
       <c r="AR88">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AS88">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AT88">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19238,64 +19238,64 @@
         <v>4</v>
       </c>
       <c r="AW88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX88">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY88">
         <v>13</v>
       </c>
       <c r="AZ88">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB88">
+        <v>7</v>
+      </c>
+      <c r="BC88">
         <v>8</v>
-      </c>
-      <c r="BC88">
-        <v>11</v>
       </c>
       <c r="BD88">
         <v>2.02</v>
       </c>
       <c r="BE88">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="BF88">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="BG88">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BH88">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="BI88">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="BJ88">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="BK88">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="BL88">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="BM88">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="BN88">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="BO88">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="BP88">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="89" spans="1:68">
@@ -20127,7 +20127,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>7452347</v>
+        <v>7452348</v>
       </c>
       <c r="C93" t="s">
         <v>68</v>
@@ -20142,10 +20142,10 @@
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -20157,34 +20157,34 @@
         <v>0</v>
       </c>
       <c r="L93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93">
         <v>0</v>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="P93" t="s">
         <v>87</v>
       </c>
       <c r="Q93">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R93">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S93">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="T93">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U93">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V93">
         <v>2.38</v>
@@ -20193,100 +20193,100 @@
         <v>1.53</v>
       </c>
       <c r="X93">
+        <v>5.5</v>
+      </c>
+      <c r="Y93">
+        <v>1.14</v>
+      </c>
+      <c r="Z93">
+        <v>3.1</v>
+      </c>
+      <c r="AA93">
+        <v>3.6</v>
+      </c>
+      <c r="AB93">
+        <v>2.15</v>
+      </c>
+      <c r="AC93">
+        <v>3.91</v>
+      </c>
+      <c r="AD93">
+        <v>1.27</v>
+      </c>
+      <c r="AE93">
+        <v>0</v>
+      </c>
+      <c r="AF93">
+        <v>0</v>
+      </c>
+      <c r="AG93">
+        <v>1.53</v>
+      </c>
+      <c r="AH93">
+        <v>2.4</v>
+      </c>
+      <c r="AI93">
+        <v>1.5</v>
+      </c>
+      <c r="AJ93">
+        <v>2.5</v>
+      </c>
+      <c r="AK93">
+        <v>0</v>
+      </c>
+      <c r="AL93">
+        <v>0</v>
+      </c>
+      <c r="AM93">
+        <v>0</v>
+      </c>
+      <c r="AN93">
+        <v>1.43</v>
+      </c>
+      <c r="AO93">
+        <v>0.75</v>
+      </c>
+      <c r="AP93">
+        <v>1.09</v>
+      </c>
+      <c r="AQ93">
+        <v>0.73</v>
+      </c>
+      <c r="AR93">
+        <v>1.41</v>
+      </c>
+      <c r="AS93">
+        <v>1.39</v>
+      </c>
+      <c r="AT93">
+        <v>2.8</v>
+      </c>
+      <c r="AU93">
+        <v>3</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>5</v>
+      </c>
+      <c r="AX93">
         <v>6</v>
       </c>
-      <c r="Y93">
-        <v>1.13</v>
-      </c>
-      <c r="Z93">
-        <v>1.57</v>
-      </c>
-      <c r="AA93">
-        <v>4.2</v>
-      </c>
-      <c r="AB93">
-        <v>5.25</v>
-      </c>
-      <c r="AC93">
-        <v>0</v>
-      </c>
-      <c r="AD93">
-        <v>0</v>
-      </c>
-      <c r="AE93">
-        <v>0</v>
-      </c>
-      <c r="AF93">
-        <v>0</v>
-      </c>
-      <c r="AG93">
-        <v>1.6</v>
-      </c>
-      <c r="AH93">
-        <v>2.3</v>
-      </c>
-      <c r="AI93">
-        <v>1.67</v>
-      </c>
-      <c r="AJ93">
-        <v>2.1</v>
-      </c>
-      <c r="AK93">
-        <v>0</v>
-      </c>
-      <c r="AL93">
-        <v>0</v>
-      </c>
-      <c r="AM93">
-        <v>0</v>
-      </c>
-      <c r="AN93">
-        <v>1.57</v>
-      </c>
-      <c r="AO93">
-        <v>0.14</v>
-      </c>
-      <c r="AP93">
-        <v>1.64</v>
-      </c>
-      <c r="AQ93">
-        <v>0.36</v>
-      </c>
-      <c r="AR93">
-        <v>1.44</v>
-      </c>
-      <c r="AS93">
-        <v>1.26</v>
-      </c>
-      <c r="AT93">
-        <v>2.7</v>
-      </c>
-      <c r="AU93">
-        <v>7</v>
-      </c>
-      <c r="AV93">
-        <v>2</v>
-      </c>
-      <c r="AW93">
-        <v>8</v>
-      </c>
-      <c r="AX93">
-        <v>4</v>
-      </c>
       <c r="AY93">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ93">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BA93">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB93">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BC93">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD93">
         <v>0</v>
@@ -20310,7 +20310,7 @@
         <v>0</v>
       </c>
       <c r="BK93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BL93">
         <v>0</v>
@@ -20333,7 +20333,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>7452348</v>
+        <v>7452347</v>
       </c>
       <c r="C94" t="s">
         <v>68</v>
@@ -20348,10 +20348,10 @@
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -20363,34 +20363,34 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94">
         <v>0</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O94" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="P94" t="s">
         <v>87</v>
       </c>
       <c r="Q94">
+        <v>2.1</v>
+      </c>
+      <c r="R94">
+        <v>2.5</v>
+      </c>
+      <c r="S94">
+        <v>5</v>
+      </c>
+      <c r="T94">
+        <v>1.3</v>
+      </c>
+      <c r="U94">
         <v>3.4</v>
-      </c>
-      <c r="R94">
-        <v>2.38</v>
-      </c>
-      <c r="S94">
-        <v>2.75</v>
-      </c>
-      <c r="T94">
-        <v>1.29</v>
-      </c>
-      <c r="U94">
-        <v>3.5</v>
       </c>
       <c r="V94">
         <v>2.38</v>
@@ -20399,25 +20399,25 @@
         <v>1.53</v>
       </c>
       <c r="X94">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Y94">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="AA94">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB94">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="AC94">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AD94">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE94">
         <v>0</v>
@@ -20426,16 +20426,16 @@
         <v>0</v>
       </c>
       <c r="AG94">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH94">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI94">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ94">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK94">
         <v>0</v>
@@ -20447,52 +20447,52 @@
         <v>0</v>
       </c>
       <c r="AN94">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AO94">
-        <v>0.75</v>
+        <v>0.14</v>
       </c>
       <c r="AP94">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="AQ94">
-        <v>0.73</v>
+        <v>0.36</v>
       </c>
       <c r="AR94">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AS94">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT94">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU94">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV94">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW94">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX94">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY94">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AZ94">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BA94">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB94">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BC94">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD94">
         <v>0</v>
@@ -20516,7 +20516,7 @@
         <v>0</v>
       </c>
       <c r="BK94">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BL94">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -26349,7 +26349,7 @@
         <v>87</v>
       </c>
       <c r="P123" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q123">
         <v>2.38</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="265">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -807,6 +807,9 @@
   <si>
     <t>['12', '47', '60']</t>
   </si>
+  <si>
+    <t>['21', '41', '64', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1167,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3152,7 +3155,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ10">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3355,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.55</v>
@@ -4388,7 +4391,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ16">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR16">
         <v>1.37</v>
@@ -7066,7 +7069,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ29">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR29">
         <v>1.88</v>
@@ -7269,7 +7272,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
         <v>1.18</v>
@@ -7681,7 +7684,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>1.18</v>
@@ -9332,7 +9335,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ40">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -10153,7 +10156,7 @@
         <v>0.67</v>
       </c>
       <c r="AP44">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>0.64</v>
@@ -10774,7 +10777,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ47">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -12834,7 +12837,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ57">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.87</v>
@@ -13037,7 +13040,7 @@
         <v>0.6</v>
       </c>
       <c r="AP58">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
         <v>0.73</v>
@@ -15306,7 +15309,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR69">
         <v>1.17</v>
@@ -15509,7 +15512,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>1.55</v>
@@ -17778,7 +17781,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ81">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR81">
         <v>1.65</v>
@@ -18393,7 +18396,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ84">
         <v>0.36</v>
@@ -20247,10 +20250,10 @@
         <v>0.75</v>
       </c>
       <c r="AP93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR93">
         <v>1.41</v>
@@ -22516,7 +22519,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR104">
         <v>1.62</v>
@@ -24779,7 +24782,7 @@
         <v>0.88</v>
       </c>
       <c r="AP115">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>0.91</v>
@@ -25809,7 +25812,7 @@
         <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ120">
         <v>1.45</v>
@@ -26633,7 +26636,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ124">
         <v>1.36</v>
@@ -26842,7 +26845,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ125">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR125">
         <v>1.82</v>
@@ -28566,6 +28569,212 @@
       </c>
       <c r="BP133">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7861084</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45744.625</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>78</v>
+      </c>
+      <c r="H134" t="s">
+        <v>74</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>2</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>4</v>
+      </c>
+      <c r="N134">
+        <v>4</v>
+      </c>
+      <c r="O134" t="s">
+        <v>87</v>
+      </c>
+      <c r="P134" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q134">
+        <v>3.4</v>
+      </c>
+      <c r="R134">
+        <v>2.25</v>
+      </c>
+      <c r="S134">
+        <v>3</v>
+      </c>
+      <c r="T134">
+        <v>1.36</v>
+      </c>
+      <c r="U134">
+        <v>3</v>
+      </c>
+      <c r="V134">
+        <v>2.63</v>
+      </c>
+      <c r="W134">
+        <v>1.44</v>
+      </c>
+      <c r="X134">
+        <v>7</v>
+      </c>
+      <c r="Y134">
+        <v>1.1</v>
+      </c>
+      <c r="Z134">
+        <v>2.82</v>
+      </c>
+      <c r="AA134">
+        <v>3.36</v>
+      </c>
+      <c r="AB134">
+        <v>2.4</v>
+      </c>
+      <c r="AC134">
+        <v>1.05</v>
+      </c>
+      <c r="AD134">
+        <v>9.5</v>
+      </c>
+      <c r="AE134">
+        <v>1.25</v>
+      </c>
+      <c r="AF134">
+        <v>3.75</v>
+      </c>
+      <c r="AG134">
+        <v>1.77</v>
+      </c>
+      <c r="AH134">
+        <v>1.95</v>
+      </c>
+      <c r="AI134">
+        <v>1.62</v>
+      </c>
+      <c r="AJ134">
+        <v>2.2</v>
+      </c>
+      <c r="AK134">
+        <v>1.53</v>
+      </c>
+      <c r="AL134">
+        <v>1.31</v>
+      </c>
+      <c r="AM134">
+        <v>1.41</v>
+      </c>
+      <c r="AN134">
+        <v>0.95</v>
+      </c>
+      <c r="AO134">
+        <v>1.27</v>
+      </c>
+      <c r="AP134">
+        <v>0.91</v>
+      </c>
+      <c r="AQ134">
+        <v>1.35</v>
+      </c>
+      <c r="AR134">
+        <v>1.28</v>
+      </c>
+      <c r="AS134">
+        <v>1.38</v>
+      </c>
+      <c r="AT134">
+        <v>2.66</v>
+      </c>
+      <c r="AU134">
+        <v>5</v>
+      </c>
+      <c r="AV134">
+        <v>11</v>
+      </c>
+      <c r="AW134">
+        <v>11</v>
+      </c>
+      <c r="AX134">
+        <v>5</v>
+      </c>
+      <c r="AY134">
+        <v>17</v>
+      </c>
+      <c r="AZ134">
+        <v>21</v>
+      </c>
+      <c r="BA134">
+        <v>6</v>
+      </c>
+      <c r="BB134">
+        <v>6</v>
+      </c>
+      <c r="BC134">
+        <v>12</v>
+      </c>
+      <c r="BD134">
+        <v>1.97</v>
+      </c>
+      <c r="BE134">
+        <v>6.7</v>
+      </c>
+      <c r="BF134">
+        <v>2.29</v>
+      </c>
+      <c r="BG134">
+        <v>1.15</v>
+      </c>
+      <c r="BH134">
+        <v>4.25</v>
+      </c>
+      <c r="BI134">
+        <v>1.31</v>
+      </c>
+      <c r="BJ134">
+        <v>2.92</v>
+      </c>
+      <c r="BK134">
+        <v>1.58</v>
+      </c>
+      <c r="BL134">
+        <v>2.17</v>
+      </c>
+      <c r="BM134">
+        <v>1.95</v>
+      </c>
+      <c r="BN134">
+        <v>1.77</v>
+      </c>
+      <c r="BO134">
+        <v>2.57</v>
+      </c>
+      <c r="BP134">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,15 @@
     <t>['48', '60', '66']</t>
   </si>
   <si>
+    <t>['5', '44']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['4', '56']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -697,9 +706,6 @@
     <t>['71', '85']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
     <t>['63', '85']</t>
   </si>
   <si>
@@ -809,6 +815,12 @@
   </si>
   <si>
     <t>['21', '41', '64', '90+5']</t>
+  </si>
+  <si>
+    <t>['15', '24']</t>
+  </si>
+  <si>
+    <t>['44', '57']</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2">
         <v>1.36</v>
@@ -2044,7 +2056,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2250,7 +2262,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2331,7 +2343,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2456,7 +2468,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2534,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
         <v>1.45</v>
@@ -2662,7 +2674,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2740,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>0.64</v>
@@ -2868,7 +2880,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3280,7 +3292,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3361,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="AQ11">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3486,7 +3498,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3773,7 +3785,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3976,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ14">
         <v>0.73</v>
@@ -4182,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15">
         <v>0.82</v>
@@ -4516,7 +4528,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4722,7 +4734,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4800,10 +4812,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ18">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
         <v>1.15</v>
@@ -4928,7 +4940,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5009,7 +5021,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ19">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR19">
         <v>1.07</v>
@@ -5212,10 +5224,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR20">
         <v>1.75</v>
@@ -5546,7 +5558,7 @@
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -5627,7 +5639,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ22">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -5752,7 +5764,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5958,7 +5970,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6036,7 +6048,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.45</v>
@@ -6164,7 +6176,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6370,7 +6382,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6448,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ26">
         <v>1.36</v>
@@ -6576,7 +6588,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6782,7 +6794,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6863,7 +6875,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ28">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR28">
         <v>1.19</v>
@@ -6988,7 +7000,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7194,7 +7206,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7275,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.16</v>
@@ -7478,10 +7490,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR31">
         <v>1.74</v>
@@ -7606,7 +7618,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7812,7 +7824,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7890,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33">
         <v>0.73</v>
@@ -8018,7 +8030,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8099,7 +8111,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ34">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8224,7 +8236,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8430,7 +8442,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8920,10 +8932,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ38">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR38">
         <v>1.09</v>
@@ -9048,7 +9060,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9126,10 +9138,10 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ39">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>1.84</v>
@@ -9254,7 +9266,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9332,7 +9344,7 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
         <v>0.92</v>
@@ -9460,7 +9472,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q41">
         <v>2.75</v>
@@ -9541,7 +9553,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ41">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.87</v>
@@ -9666,7 +9678,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10078,7 +10090,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10284,7 +10296,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10362,7 +10374,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ45">
         <v>1.45</v>
@@ -10490,7 +10502,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10568,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10696,7 +10708,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11314,7 +11326,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11395,7 +11407,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR50">
         <v>1.51</v>
@@ -11598,10 +11610,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR51">
         <v>1.45</v>
@@ -11726,7 +11738,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12010,7 +12022,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ53">
         <v>1.18</v>
@@ -12138,7 +12150,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12219,7 +12231,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12550,7 +12562,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12628,7 +12640,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ56">
         <v>1.55</v>
@@ -12834,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57">
         <v>0.92</v>
@@ -13168,7 +13180,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13246,10 +13258,10 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ59">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
         <v>1.04</v>
@@ -13374,7 +13386,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13580,7 +13592,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13661,7 +13673,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR61">
         <v>1.74</v>
@@ -13786,7 +13798,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13992,7 +14004,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14070,10 +14082,10 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR63">
         <v>1.52</v>
@@ -14198,7 +14210,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14404,7 +14416,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14816,7 +14828,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -15103,7 +15115,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ68">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR68">
         <v>1.76</v>
@@ -15306,7 +15318,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ69">
         <v>0.92</v>
@@ -15434,7 +15446,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15640,7 +15652,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="Q71">
         <v>1.95</v>
@@ -15721,7 +15733,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -15846,7 +15858,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15924,7 +15936,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -16130,10 +16142,10 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ73">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
         <v>1.58</v>
@@ -16876,7 +16888,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17160,7 +17172,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ78">
         <v>1.18</v>
@@ -17369,7 +17381,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ79">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
         <v>1.38</v>
@@ -17494,7 +17506,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17572,7 +17584,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1.55</v>
@@ -17700,7 +17712,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17906,7 +17918,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -17984,10 +17996,10 @@
         <v>1.14</v>
       </c>
       <c r="AP82">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ82">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18112,7 +18124,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18190,7 +18202,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ83">
         <v>0.64</v>
@@ -18318,7 +18330,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18399,7 +18411,7 @@
         <v>1</v>
       </c>
       <c r="AQ84">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR84">
         <v>1.31</v>
@@ -18524,7 +18536,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18605,7 +18617,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ85">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -19142,7 +19154,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19220,7 +19232,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ88">
         <v>0.82</v>
@@ -19554,7 +19566,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19632,7 +19644,7 @@
         <v>1.57</v>
       </c>
       <c r="AP90">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ90">
         <v>1.45</v>
@@ -19760,7 +19772,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19841,7 +19853,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ91">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR91">
         <v>1.65</v>
@@ -20459,7 +20471,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ94">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR94">
         <v>1.44</v>
@@ -20584,7 +20596,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20662,10 +20674,10 @@
         <v>1.38</v>
       </c>
       <c r="AP95">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -20790,7 +20802,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21074,10 +21086,10 @@
         <v>1.43</v>
       </c>
       <c r="AP97">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ97">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR97">
         <v>1.78</v>
@@ -21408,7 +21420,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21486,7 +21498,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ99">
         <v>0.73</v>
@@ -21614,7 +21626,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21820,7 +21832,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22026,7 +22038,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22313,7 +22325,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR103">
         <v>2.05</v>
@@ -22438,7 +22450,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22644,7 +22656,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22725,7 +22737,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ105">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR105">
         <v>1.26</v>
@@ -22850,7 +22862,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -22928,7 +22940,7 @@
         <v>1.13</v>
       </c>
       <c r="AP106">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>1.18</v>
@@ -23134,7 +23146,7 @@
         <v>0.38</v>
       </c>
       <c r="AP107">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ107">
         <v>0.64</v>
@@ -23262,7 +23274,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23546,7 +23558,7 @@
         <v>1.78</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ109">
         <v>1.55</v>
@@ -23752,7 +23764,7 @@
         <v>0.67</v>
       </c>
       <c r="AP110">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ110">
         <v>0.82</v>
@@ -23880,7 +23892,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q111">
         <v>1.83</v>
@@ -24086,7 +24098,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24167,7 +24179,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ112">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR112">
         <v>1.42</v>
@@ -24498,7 +24510,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24579,7 +24591,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ114">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR114">
         <v>1.41</v>
@@ -24704,7 +24716,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24785,7 +24797,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR115">
         <v>1.35</v>
@@ -24910,7 +24922,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25116,7 +25128,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25194,10 +25206,10 @@
         <v>1.44</v>
       </c>
       <c r="AP117">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ117">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR117">
         <v>1.38</v>
@@ -25322,7 +25334,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25403,7 +25415,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ118">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR118">
         <v>1.35</v>
@@ -25528,7 +25540,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -25606,10 +25618,10 @@
         <v>1.11</v>
       </c>
       <c r="AP119">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ119">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR119">
         <v>1.65</v>
@@ -26227,7 +26239,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ122">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR122">
         <v>1.71</v>
@@ -26352,7 +26364,7 @@
         <v>87</v>
       </c>
       <c r="P123" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26558,7 +26570,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q124">
         <v>4.75</v>
@@ -26764,7 +26776,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -26842,7 +26854,7 @@
         <v>0.7</v>
       </c>
       <c r="AP125">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ125">
         <v>0.92</v>
@@ -26970,7 +26982,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27176,7 +27188,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q127">
         <v>3.5</v>
@@ -27257,7 +27269,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR127">
         <v>1.45</v>
@@ -27382,7 +27394,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>2.25</v>
@@ -27463,7 +27475,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ128">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR128">
         <v>1.76</v>
@@ -27588,7 +27600,7 @@
         <v>181</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>2.25</v>
@@ -27666,7 +27678,7 @@
         <v>1.7</v>
       </c>
       <c r="AP129">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ129">
         <v>1.55</v>
@@ -27872,10 +27884,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ130">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR130">
         <v>1.23</v>
@@ -28000,7 +28012,7 @@
         <v>183</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>5</v>
@@ -28206,7 +28218,7 @@
         <v>184</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>4.75</v>
@@ -28412,7 +28424,7 @@
         <v>87</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28490,7 +28502,7 @@
         <v>0.6</v>
       </c>
       <c r="AP133">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ133">
         <v>0.82</v>
@@ -28618,7 +28630,7 @@
         <v>87</v>
       </c>
       <c r="P134" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28775,6 +28787,830 @@
       </c>
       <c r="BP134">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7861085</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s">
+        <v>72</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135">
+        <v>2</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>3</v>
+      </c>
+      <c r="O135" t="s">
+        <v>185</v>
+      </c>
+      <c r="P135" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q135">
+        <v>4</v>
+      </c>
+      <c r="R135">
+        <v>2.3</v>
+      </c>
+      <c r="S135">
+        <v>2.6</v>
+      </c>
+      <c r="T135">
+        <v>1.33</v>
+      </c>
+      <c r="U135">
+        <v>3.25</v>
+      </c>
+      <c r="V135">
+        <v>2.5</v>
+      </c>
+      <c r="W135">
+        <v>1.5</v>
+      </c>
+      <c r="X135">
+        <v>6.5</v>
+      </c>
+      <c r="Y135">
+        <v>1.11</v>
+      </c>
+      <c r="Z135">
+        <v>3.35</v>
+      </c>
+      <c r="AA135">
+        <v>3.76</v>
+      </c>
+      <c r="AB135">
+        <v>1.98</v>
+      </c>
+      <c r="AC135">
+        <v>1</v>
+      </c>
+      <c r="AD135">
+        <v>12.8</v>
+      </c>
+      <c r="AE135">
+        <v>1.2</v>
+      </c>
+      <c r="AF135">
+        <v>4.48</v>
+      </c>
+      <c r="AG135">
+        <v>1.61</v>
+      </c>
+      <c r="AH135">
+        <v>2.1</v>
+      </c>
+      <c r="AI135">
+        <v>1.62</v>
+      </c>
+      <c r="AJ135">
+        <v>2.2</v>
+      </c>
+      <c r="AK135">
+        <v>1.82</v>
+      </c>
+      <c r="AL135">
+        <v>1.27</v>
+      </c>
+      <c r="AM135">
+        <v>1.27</v>
+      </c>
+      <c r="AN135">
+        <v>0.77</v>
+      </c>
+      <c r="AO135">
+        <v>1.5</v>
+      </c>
+      <c r="AP135">
+        <v>0.87</v>
+      </c>
+      <c r="AQ135">
+        <v>1.43</v>
+      </c>
+      <c r="AR135">
+        <v>1.29</v>
+      </c>
+      <c r="AS135">
+        <v>1.39</v>
+      </c>
+      <c r="AT135">
+        <v>2.68</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>6</v>
+      </c>
+      <c r="AW135">
+        <v>2</v>
+      </c>
+      <c r="AX135">
+        <v>19</v>
+      </c>
+      <c r="AY135">
+        <v>7</v>
+      </c>
+      <c r="AZ135">
+        <v>34</v>
+      </c>
+      <c r="BA135">
+        <v>3</v>
+      </c>
+      <c r="BB135">
+        <v>6</v>
+      </c>
+      <c r="BC135">
+        <v>9</v>
+      </c>
+      <c r="BD135">
+        <v>2.69</v>
+      </c>
+      <c r="BE135">
+        <v>6.65</v>
+      </c>
+      <c r="BF135">
+        <v>1.75</v>
+      </c>
+      <c r="BG135">
+        <v>1.21</v>
+      </c>
+      <c r="BH135">
+        <v>3.58</v>
+      </c>
+      <c r="BI135">
+        <v>1.42</v>
+      </c>
+      <c r="BJ135">
+        <v>2.57</v>
+      </c>
+      <c r="BK135">
+        <v>1.77</v>
+      </c>
+      <c r="BL135">
+        <v>1.95</v>
+      </c>
+      <c r="BM135">
+        <v>2.21</v>
+      </c>
+      <c r="BN135">
+        <v>1.56</v>
+      </c>
+      <c r="BO135">
+        <v>2.92</v>
+      </c>
+      <c r="BP135">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7861086</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>75</v>
+      </c>
+      <c r="H136" t="s">
+        <v>73</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>2</v>
+      </c>
+      <c r="K136">
+        <v>3</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>2</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136" t="s">
+        <v>186</v>
+      </c>
+      <c r="P136" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q136">
+        <v>3</v>
+      </c>
+      <c r="R136">
+        <v>2.1</v>
+      </c>
+      <c r="S136">
+        <v>3.75</v>
+      </c>
+      <c r="T136">
+        <v>1.44</v>
+      </c>
+      <c r="U136">
+        <v>2.63</v>
+      </c>
+      <c r="V136">
+        <v>3.25</v>
+      </c>
+      <c r="W136">
+        <v>1.33</v>
+      </c>
+      <c r="X136">
+        <v>9</v>
+      </c>
+      <c r="Y136">
+        <v>1.07</v>
+      </c>
+      <c r="Z136">
+        <v>2.22</v>
+      </c>
+      <c r="AA136">
+        <v>3.27</v>
+      </c>
+      <c r="AB136">
+        <v>3.19</v>
+      </c>
+      <c r="AC136">
+        <v>1</v>
+      </c>
+      <c r="AD136">
+        <v>9.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.31</v>
+      </c>
+      <c r="AF136">
+        <v>3.42</v>
+      </c>
+      <c r="AG136">
+        <v>1.95</v>
+      </c>
+      <c r="AH136">
+        <v>1.79</v>
+      </c>
+      <c r="AI136">
+        <v>1.8</v>
+      </c>
+      <c r="AJ136">
+        <v>1.95</v>
+      </c>
+      <c r="AK136">
+        <v>1.35</v>
+      </c>
+      <c r="AL136">
+        <v>1.31</v>
+      </c>
+      <c r="AM136">
+        <v>1.61</v>
+      </c>
+      <c r="AN136">
+        <v>0.82</v>
+      </c>
+      <c r="AO136">
+        <v>0.59</v>
+      </c>
+      <c r="AP136">
+        <v>0.78</v>
+      </c>
+      <c r="AQ136">
+        <v>0.7</v>
+      </c>
+      <c r="AR136">
+        <v>1.17</v>
+      </c>
+      <c r="AS136">
+        <v>1.28</v>
+      </c>
+      <c r="AT136">
+        <v>2.45</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>4</v>
+      </c>
+      <c r="AW136">
+        <v>8</v>
+      </c>
+      <c r="AX136">
+        <v>8</v>
+      </c>
+      <c r="AY136">
+        <v>17</v>
+      </c>
+      <c r="AZ136">
+        <v>14</v>
+      </c>
+      <c r="BA136">
+        <v>7</v>
+      </c>
+      <c r="BB136">
+        <v>2</v>
+      </c>
+      <c r="BC136">
+        <v>9</v>
+      </c>
+      <c r="BD136">
+        <v>1.6</v>
+      </c>
+      <c r="BE136">
+        <v>7.1</v>
+      </c>
+      <c r="BF136">
+        <v>3.06</v>
+      </c>
+      <c r="BG136">
+        <v>1.14</v>
+      </c>
+      <c r="BH136">
+        <v>4.4</v>
+      </c>
+      <c r="BI136">
+        <v>1.3</v>
+      </c>
+      <c r="BJ136">
+        <v>2.97</v>
+      </c>
+      <c r="BK136">
+        <v>1.56</v>
+      </c>
+      <c r="BL136">
+        <v>2.21</v>
+      </c>
+      <c r="BM136">
+        <v>1.95</v>
+      </c>
+      <c r="BN136">
+        <v>1.77</v>
+      </c>
+      <c r="BO136">
+        <v>2.51</v>
+      </c>
+      <c r="BP136">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7861081</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45746.45833333334</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>70</v>
+      </c>
+      <c r="H137" t="s">
+        <v>71</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>187</v>
+      </c>
+      <c r="P137" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q137">
+        <v>2.75</v>
+      </c>
+      <c r="R137">
+        <v>2.1</v>
+      </c>
+      <c r="S137">
+        <v>4</v>
+      </c>
+      <c r="T137">
+        <v>1.4</v>
+      </c>
+      <c r="U137">
+        <v>2.75</v>
+      </c>
+      <c r="V137">
+        <v>3</v>
+      </c>
+      <c r="W137">
+        <v>1.36</v>
+      </c>
+      <c r="X137">
+        <v>9</v>
+      </c>
+      <c r="Y137">
+        <v>1.07</v>
+      </c>
+      <c r="Z137">
+        <v>1.91</v>
+      </c>
+      <c r="AA137">
+        <v>3.53</v>
+      </c>
+      <c r="AB137">
+        <v>3.79</v>
+      </c>
+      <c r="AC137">
+        <v>1.02</v>
+      </c>
+      <c r="AD137">
+        <v>9</v>
+      </c>
+      <c r="AE137">
+        <v>1.32</v>
+      </c>
+      <c r="AF137">
+        <v>3.34</v>
+      </c>
+      <c r="AG137">
+        <v>1.82</v>
+      </c>
+      <c r="AH137">
+        <v>1.92</v>
+      </c>
+      <c r="AI137">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137">
+        <v>1.95</v>
+      </c>
+      <c r="AK137">
+        <v>1.3</v>
+      </c>
+      <c r="AL137">
+        <v>1.3</v>
+      </c>
+      <c r="AM137">
+        <v>1.71</v>
+      </c>
+      <c r="AN137">
+        <v>1.64</v>
+      </c>
+      <c r="AO137">
+        <v>1.59</v>
+      </c>
+      <c r="AP137">
+        <v>1.7</v>
+      </c>
+      <c r="AQ137">
+        <v>1.52</v>
+      </c>
+      <c r="AR137">
+        <v>1.6</v>
+      </c>
+      <c r="AS137">
+        <v>1.69</v>
+      </c>
+      <c r="AT137">
+        <v>3.29</v>
+      </c>
+      <c r="AU137">
+        <v>7</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>8</v>
+      </c>
+      <c r="AX137">
+        <v>7</v>
+      </c>
+      <c r="AY137">
+        <v>18</v>
+      </c>
+      <c r="AZ137">
+        <v>11</v>
+      </c>
+      <c r="BA137">
+        <v>4</v>
+      </c>
+      <c r="BB137">
+        <v>4</v>
+      </c>
+      <c r="BC137">
+        <v>8</v>
+      </c>
+      <c r="BD137">
+        <v>1.6</v>
+      </c>
+      <c r="BE137">
+        <v>8.9</v>
+      </c>
+      <c r="BF137">
+        <v>2.81</v>
+      </c>
+      <c r="BG137">
+        <v>1.2</v>
+      </c>
+      <c r="BH137">
+        <v>3.72</v>
+      </c>
+      <c r="BI137">
+        <v>1.41</v>
+      </c>
+      <c r="BJ137">
+        <v>2.6</v>
+      </c>
+      <c r="BK137">
+        <v>1.7</v>
+      </c>
+      <c r="BL137">
+        <v>2.05</v>
+      </c>
+      <c r="BM137">
+        <v>2.17</v>
+      </c>
+      <c r="BN137">
+        <v>1.58</v>
+      </c>
+      <c r="BO137">
+        <v>2.83</v>
+      </c>
+      <c r="BP137">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7861082</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45746.54166666666</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>81</v>
+      </c>
+      <c r="H138" t="s">
+        <v>80</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
+      <c r="N138">
+        <v>2</v>
+      </c>
+      <c r="O138" t="s">
+        <v>87</v>
+      </c>
+      <c r="P138" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q138">
+        <v>2.75</v>
+      </c>
+      <c r="R138">
+        <v>2.3</v>
+      </c>
+      <c r="S138">
+        <v>3.6</v>
+      </c>
+      <c r="T138">
+        <v>1.33</v>
+      </c>
+      <c r="U138">
+        <v>3.25</v>
+      </c>
+      <c r="V138">
+        <v>2.63</v>
+      </c>
+      <c r="W138">
+        <v>1.44</v>
+      </c>
+      <c r="X138">
+        <v>6.5</v>
+      </c>
+      <c r="Y138">
+        <v>1.11</v>
+      </c>
+      <c r="Z138">
+        <v>2.11</v>
+      </c>
+      <c r="AA138">
+        <v>3.67</v>
+      </c>
+      <c r="AB138">
+        <v>3.09</v>
+      </c>
+      <c r="AC138">
+        <v>1.03</v>
+      </c>
+      <c r="AD138">
+        <v>11</v>
+      </c>
+      <c r="AE138">
+        <v>1.22</v>
+      </c>
+      <c r="AF138">
+        <v>4.32</v>
+      </c>
+      <c r="AG138">
+        <v>1.67</v>
+      </c>
+      <c r="AH138">
+        <v>2</v>
+      </c>
+      <c r="AI138">
+        <v>1.57</v>
+      </c>
+      <c r="AJ138">
+        <v>2.25</v>
+      </c>
+      <c r="AK138">
+        <v>1.35</v>
+      </c>
+      <c r="AL138">
+        <v>1.27</v>
+      </c>
+      <c r="AM138">
+        <v>1.68</v>
+      </c>
+      <c r="AN138">
+        <v>2.05</v>
+      </c>
+      <c r="AO138">
+        <v>1.5</v>
+      </c>
+      <c r="AP138">
+        <v>1.96</v>
+      </c>
+      <c r="AQ138">
+        <v>1.57</v>
+      </c>
+      <c r="AR138">
+        <v>1.7</v>
+      </c>
+      <c r="AS138">
+        <v>1.8</v>
+      </c>
+      <c r="AT138">
+        <v>3.5</v>
+      </c>
+      <c r="AU138">
+        <v>9</v>
+      </c>
+      <c r="AV138">
+        <v>6</v>
+      </c>
+      <c r="AW138">
+        <v>15</v>
+      </c>
+      <c r="AX138">
+        <v>5</v>
+      </c>
+      <c r="AY138">
+        <v>25</v>
+      </c>
+      <c r="AZ138">
+        <v>11</v>
+      </c>
+      <c r="BA138">
+        <v>16</v>
+      </c>
+      <c r="BB138">
+        <v>5</v>
+      </c>
+      <c r="BC138">
+        <v>21</v>
+      </c>
+      <c r="BD138">
+        <v>1.6</v>
+      </c>
+      <c r="BE138">
+        <v>6.95</v>
+      </c>
+      <c r="BF138">
+        <v>3.08</v>
+      </c>
+      <c r="BG138">
+        <v>1.16</v>
+      </c>
+      <c r="BH138">
+        <v>4.05</v>
+      </c>
+      <c r="BI138">
+        <v>1.34</v>
+      </c>
+      <c r="BJ138">
+        <v>2.78</v>
+      </c>
+      <c r="BK138">
+        <v>1.7</v>
+      </c>
+      <c r="BL138">
+        <v>2.05</v>
+      </c>
+      <c r="BM138">
+        <v>2.05</v>
+      </c>
+      <c r="BN138">
+        <v>1.7</v>
+      </c>
+      <c r="BO138">
+        <v>2.67</v>
+      </c>
+      <c r="BP138">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,6 +580,9 @@
     <t>['4', '56']</t>
   </si>
   <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -587,9 +590,6 @@
   </si>
   <si>
     <t>['7', '30']</t>
-  </si>
-  <si>
-    <t>['20']</t>
   </si>
   <si>
     <t>['11', '45']</t>
@@ -1182,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2056,7 +2056,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2137,7 +2137,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ5">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2468,7 +2468,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2674,7 +2674,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ12">
         <v>1.18</v>
@@ -4606,10 +4606,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR17">
         <v>1.41</v>
@@ -7078,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29">
         <v>0.92</v>
@@ -8523,7 +8523,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ36">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR36">
         <v>1.69</v>
@@ -9550,7 +9550,7 @@
         <v>2.33</v>
       </c>
       <c r="AP41">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -11201,7 +11201,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR49">
         <v>1.79</v>
@@ -12434,7 +12434,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
         <v>0.82</v>
@@ -12643,7 +12643,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ56">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -15112,7 +15112,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ68">
         <v>0.58</v>
@@ -15527,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR70">
         <v>1.17</v>
@@ -17587,7 +17587,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR80">
         <v>1.37</v>
@@ -18614,7 +18614,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ85">
         <v>1.42</v>
@@ -19029,7 +19029,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ87">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -20880,7 +20880,7 @@
         <v>0.43</v>
       </c>
       <c r="AP96">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ96">
         <v>0.64</v>
@@ -21707,7 +21707,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -22322,7 +22322,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103">
         <v>0.83</v>
@@ -23561,7 +23561,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ109">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR109">
         <v>1.19</v>
@@ -24382,7 +24382,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ113">
         <v>1.36</v>
@@ -27060,7 +27060,7 @@
         <v>0.7</v>
       </c>
       <c r="AP126">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ126">
         <v>0.73</v>
@@ -27681,7 +27681,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ129">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR129">
         <v>1.73</v>
@@ -29611,6 +29611,212 @@
       </c>
       <c r="BP138">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7861083</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="s">
+        <v>79</v>
+      </c>
+      <c r="H139" t="s">
+        <v>77</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>188</v>
+      </c>
+      <c r="P139" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q139">
+        <v>2.3</v>
+      </c>
+      <c r="R139">
+        <v>2.2</v>
+      </c>
+      <c r="S139">
+        <v>5</v>
+      </c>
+      <c r="T139">
+        <v>1.4</v>
+      </c>
+      <c r="U139">
+        <v>2.75</v>
+      </c>
+      <c r="V139">
+        <v>2.75</v>
+      </c>
+      <c r="W139">
+        <v>1.4</v>
+      </c>
+      <c r="X139">
+        <v>8</v>
+      </c>
+      <c r="Y139">
+        <v>1.08</v>
+      </c>
+      <c r="Z139">
+        <v>1.73</v>
+      </c>
+      <c r="AA139">
+        <v>3.71</v>
+      </c>
+      <c r="AB139">
+        <v>4.5</v>
+      </c>
+      <c r="AC139">
+        <v>1</v>
+      </c>
+      <c r="AD139">
+        <v>10.8</v>
+      </c>
+      <c r="AE139">
+        <v>1.27</v>
+      </c>
+      <c r="AF139">
+        <v>3.76</v>
+      </c>
+      <c r="AG139">
+        <v>1.85</v>
+      </c>
+      <c r="AH139">
+        <v>1.89</v>
+      </c>
+      <c r="AI139">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139">
+        <v>1.95</v>
+      </c>
+      <c r="AK139">
+        <v>1.19</v>
+      </c>
+      <c r="AL139">
+        <v>1.26</v>
+      </c>
+      <c r="AM139">
+        <v>2.05</v>
+      </c>
+      <c r="AN139">
+        <v>1.86</v>
+      </c>
+      <c r="AO139">
+        <v>1.59</v>
+      </c>
+      <c r="AP139">
+        <v>1.91</v>
+      </c>
+      <c r="AQ139">
+        <v>1.52</v>
+      </c>
+      <c r="AR139">
+        <v>1.77</v>
+      </c>
+      <c r="AS139">
+        <v>1.39</v>
+      </c>
+      <c r="AT139">
+        <v>3.16</v>
+      </c>
+      <c r="AU139">
+        <v>5</v>
+      </c>
+      <c r="AV139">
+        <v>0</v>
+      </c>
+      <c r="AW139">
+        <v>9</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>18</v>
+      </c>
+      <c r="AZ139">
+        <v>4</v>
+      </c>
+      <c r="BA139">
+        <v>3</v>
+      </c>
+      <c r="BB139">
+        <v>2</v>
+      </c>
+      <c r="BC139">
+        <v>5</v>
+      </c>
+      <c r="BD139">
+        <v>1.77</v>
+      </c>
+      <c r="BE139">
+        <v>6.75</v>
+      </c>
+      <c r="BF139">
+        <v>2.63</v>
+      </c>
+      <c r="BG139">
+        <v>1.18</v>
+      </c>
+      <c r="BH139">
+        <v>3.9</v>
+      </c>
+      <c r="BI139">
+        <v>1.37</v>
+      </c>
+      <c r="BJ139">
+        <v>2.75</v>
+      </c>
+      <c r="BK139">
+        <v>1.7</v>
+      </c>
+      <c r="BL139">
+        <v>2.05</v>
+      </c>
+      <c r="BM139">
+        <v>2.09</v>
+      </c>
+      <c r="BN139">
+        <v>1.63</v>
+      </c>
+      <c r="BO139">
+        <v>2.7</v>
+      </c>
+      <c r="BP139">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="271">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -583,6 +583,9 @@
     <t>['20']</t>
   </si>
   <si>
+    <t>['15', '68']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -821,6 +824,9 @@
   </si>
   <si>
     <t>['44', '57']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1519,7 +1525,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2056,7 +2062,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2262,7 +2268,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2468,7 +2474,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2880,7 +2886,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2961,7 +2967,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ9">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>1.96</v>
@@ -3164,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10">
         <v>0.92</v>
@@ -3292,7 +3298,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3498,7 +3504,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -4528,7 +4534,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4734,7 +4740,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4940,7 +4946,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5558,7 +5564,7 @@
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -5636,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>1.42</v>
@@ -5764,7 +5770,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5970,7 +5976,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6176,7 +6182,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6382,7 +6388,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6463,7 +6469,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR26">
         <v>1.11</v>
@@ -6588,7 +6594,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6666,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ27">
         <v>0.73</v>
@@ -6794,7 +6800,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7000,7 +7006,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7206,7 +7212,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7618,7 +7624,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7824,7 +7830,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -8030,7 +8036,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8236,7 +8242,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8442,7 +8448,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9060,7 +9066,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9266,7 +9272,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9472,7 +9478,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q41">
         <v>2.75</v>
@@ -9678,7 +9684,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9759,7 +9765,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ42">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR42">
         <v>1.27</v>
@@ -9962,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>0.82</v>
@@ -10090,7 +10096,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10296,7 +10302,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10502,7 +10508,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10708,7 +10714,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11326,7 +11332,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11738,7 +11744,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11816,10 +11822,10 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR52">
         <v>1.41</v>
@@ -12150,7 +12156,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12562,7 +12568,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13180,7 +13186,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13386,7 +13392,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13592,7 +13598,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13798,7 +13804,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -14004,7 +14010,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14210,7 +14216,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14288,7 +14294,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
         <v>0.64</v>
@@ -14416,7 +14422,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14703,7 +14709,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ66">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR66">
         <v>1.84</v>
@@ -14828,7 +14834,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -15446,7 +15452,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15858,7 +15864,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -15939,7 +15945,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16888,7 +16894,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17378,7 +17384,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ79">
         <v>0.83</v>
@@ -17506,7 +17512,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17712,7 +17718,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17918,7 +17924,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -18124,7 +18130,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18330,7 +18336,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18536,7 +18542,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19154,7 +19160,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19441,7 +19447,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19566,7 +19572,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19772,7 +19778,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -20468,7 +20474,7 @@
         <v>0.14</v>
       </c>
       <c r="AP94">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ94">
         <v>0.58</v>
@@ -20596,7 +20602,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20802,7 +20808,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21420,7 +21426,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21626,7 +21632,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21832,7 +21838,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21913,7 +21919,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -22038,7 +22044,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22450,7 +22456,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22656,7 +22662,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22862,7 +22868,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23274,7 +23280,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23352,7 +23358,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ108">
         <v>1.45</v>
@@ -23892,7 +23898,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q111">
         <v>1.83</v>
@@ -24098,7 +24104,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24385,7 +24391,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ113">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR113">
         <v>1.93</v>
@@ -24510,7 +24516,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24716,7 +24722,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24922,7 +24928,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25000,7 +25006,7 @@
         <v>1.33</v>
       </c>
       <c r="AP116">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ116">
         <v>1.18</v>
@@ -25128,7 +25134,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25334,7 +25340,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25540,7 +25546,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -26364,7 +26370,7 @@
         <v>87</v>
       </c>
       <c r="P123" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26570,7 +26576,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q124">
         <v>4.75</v>
@@ -26651,7 +26657,7 @@
         <v>1</v>
       </c>
       <c r="AQ124">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR124">
         <v>1.31</v>
@@ -26776,7 +26782,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -26982,7 +26988,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27188,7 +27194,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q127">
         <v>3.5</v>
@@ -27266,7 +27272,7 @@
         <v>1.3</v>
       </c>
       <c r="AP127">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ127">
         <v>1.33</v>
@@ -27394,7 +27400,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q128">
         <v>2.25</v>
@@ -27600,7 +27606,7 @@
         <v>181</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>2.25</v>
@@ -28012,7 +28018,7 @@
         <v>183</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q131">
         <v>5</v>
@@ -28218,7 +28224,7 @@
         <v>184</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q132">
         <v>4.75</v>
@@ -28424,7 +28430,7 @@
         <v>87</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28630,7 +28636,7 @@
         <v>87</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29042,7 +29048,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29454,7 +29460,7 @@
         <v>87</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q138">
         <v>2.75</v>
@@ -29532,7 +29538,7 @@
         <v>1.5</v>
       </c>
       <c r="AP138">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AQ138">
         <v>1.57</v>
@@ -29741,7 +29747,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ139">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AR139">
         <v>1.77</v>
@@ -29817,6 +29823,212 @@
       </c>
       <c r="BP139">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7861619</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45751.58333333334</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140" t="s">
+        <v>77</v>
+      </c>
+      <c r="H140" t="s">
+        <v>81</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>189</v>
+      </c>
+      <c r="P140" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q140">
+        <v>3.25</v>
+      </c>
+      <c r="R140">
+        <v>2.25</v>
+      </c>
+      <c r="S140">
+        <v>3.1</v>
+      </c>
+      <c r="T140">
+        <v>1.36</v>
+      </c>
+      <c r="U140">
+        <v>3</v>
+      </c>
+      <c r="V140">
+        <v>2.63</v>
+      </c>
+      <c r="W140">
+        <v>1.44</v>
+      </c>
+      <c r="X140">
+        <v>7</v>
+      </c>
+      <c r="Y140">
+        <v>1.1</v>
+      </c>
+      <c r="Z140">
+        <v>2.55</v>
+      </c>
+      <c r="AA140">
+        <v>3.5</v>
+      </c>
+      <c r="AB140">
+        <v>2.55</v>
+      </c>
+      <c r="AC140">
+        <v>1.05</v>
+      </c>
+      <c r="AD140">
+        <v>9.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.25</v>
+      </c>
+      <c r="AF140">
+        <v>3.75</v>
+      </c>
+      <c r="AG140">
+        <v>1.82</v>
+      </c>
+      <c r="AH140">
+        <v>1.92</v>
+      </c>
+      <c r="AI140">
+        <v>1.62</v>
+      </c>
+      <c r="AJ140">
+        <v>2.2</v>
+      </c>
+      <c r="AK140">
+        <v>1.51</v>
+      </c>
+      <c r="AL140">
+        <v>1.29</v>
+      </c>
+      <c r="AM140">
+        <v>1.46</v>
+      </c>
+      <c r="AN140">
+        <v>1.52</v>
+      </c>
+      <c r="AO140">
+        <v>1.96</v>
+      </c>
+      <c r="AP140">
+        <v>1.58</v>
+      </c>
+      <c r="AQ140">
+        <v>1.88</v>
+      </c>
+      <c r="AR140">
+        <v>1.35</v>
+      </c>
+      <c r="AS140">
+        <v>1.74</v>
+      </c>
+      <c r="AT140">
+        <v>3.09</v>
+      </c>
+      <c r="AU140">
+        <v>7</v>
+      </c>
+      <c r="AV140">
+        <v>4</v>
+      </c>
+      <c r="AW140">
+        <v>6</v>
+      </c>
+      <c r="AX140">
+        <v>6</v>
+      </c>
+      <c r="AY140">
+        <v>16</v>
+      </c>
+      <c r="AZ140">
+        <v>11</v>
+      </c>
+      <c r="BA140">
+        <v>8</v>
+      </c>
+      <c r="BB140">
+        <v>2</v>
+      </c>
+      <c r="BC140">
+        <v>10</v>
+      </c>
+      <c r="BD140">
+        <v>1.98</v>
+      </c>
+      <c r="BE140">
+        <v>6.75</v>
+      </c>
+      <c r="BF140">
+        <v>1.97</v>
+      </c>
+      <c r="BG140">
+        <v>1.21</v>
+      </c>
+      <c r="BH140">
+        <v>3.8</v>
+      </c>
+      <c r="BI140">
+        <v>1.37</v>
+      </c>
+      <c r="BJ140">
+        <v>2.8</v>
+      </c>
+      <c r="BK140">
+        <v>1.63</v>
+      </c>
+      <c r="BL140">
+        <v>2.12</v>
+      </c>
+      <c r="BM140">
+        <v>1.96</v>
+      </c>
+      <c r="BN140">
+        <v>1.73</v>
+      </c>
+      <c r="BO140">
+        <v>2.45</v>
+      </c>
+      <c r="BP140">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="276">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -586,6 +586,15 @@
     <t>['15', '68']</t>
   </si>
   <si>
+    <t>['8', '15']</t>
+  </si>
+  <si>
+    <t>['18', '63']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -827,6 +836,12 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1728,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1934,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2062,7 +2077,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2140,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ5">
         <v>1.42</v>
@@ -2268,7 +2283,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2346,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6">
         <v>1.33</v>
@@ -2474,7 +2489,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2555,7 +2570,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2761,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2886,7 +2901,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2964,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9">
         <v>1.25</v>
@@ -3298,7 +3313,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3504,7 +3519,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3997,7 +4012,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ14">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR14">
         <v>1.77</v>
@@ -4203,7 +4218,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ15">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4406,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ16">
         <v>0.92</v>
@@ -4534,7 +4549,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4740,7 +4755,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4946,7 +4961,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5024,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ19">
         <v>0.83</v>
@@ -5436,10 +5451,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR21">
         <v>1.44</v>
@@ -5564,7 +5579,7 @@
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -5770,7 +5785,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5976,7 +5991,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6057,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
         <v>1.85</v>
@@ -6182,7 +6197,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6260,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR25">
         <v>0.91</v>
@@ -6388,7 +6403,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6594,7 +6609,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6675,7 +6690,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ27">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>1.35</v>
@@ -6800,7 +6815,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6878,7 +6893,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ28">
         <v>0.83</v>
@@ -7006,7 +7021,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7212,7 +7227,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7624,7 +7639,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7830,7 +7845,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -7911,7 +7926,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR33">
         <v>1.8</v>
@@ -8036,7 +8051,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8114,7 +8129,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ34">
         <v>1.42</v>
@@ -8242,7 +8257,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8320,10 +8335,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ35">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR35">
         <v>1.81</v>
@@ -8448,7 +8463,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8732,10 +8747,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ37">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR37">
         <v>1.54</v>
@@ -9066,7 +9081,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9272,7 +9287,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9478,7 +9493,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q41">
         <v>2.75</v>
@@ -9684,7 +9699,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9762,7 +9777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP42">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ42">
         <v>1.25</v>
@@ -9971,7 +9986,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -10096,7 +10111,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10177,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR44">
         <v>0.9</v>
@@ -10302,7 +10317,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10383,7 +10398,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ45">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR45">
         <v>1.88</v>
@@ -10508,7 +10523,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10714,7 +10729,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -10792,7 +10807,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ47">
         <v>0.92</v>
@@ -11001,7 +11016,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ48">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR48">
         <v>1.96</v>
@@ -11204,7 +11219,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49">
         <v>1.42</v>
@@ -11332,7 +11347,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11410,7 +11425,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ50">
         <v>0.83</v>
@@ -11744,7 +11759,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12156,7 +12171,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12234,7 +12249,7 @@
         <v>1.75</v>
       </c>
       <c r="AP54">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12443,7 +12458,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ55">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR55">
         <v>1.59</v>
@@ -12568,7 +12583,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13061,7 +13076,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR58">
         <v>1.05</v>
@@ -13186,7 +13201,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13392,7 +13407,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13470,10 +13485,10 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR60">
         <v>1.56</v>
@@ -13598,7 +13613,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13676,7 +13691,7 @@
         <v>1.6</v>
       </c>
       <c r="AP61">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -13804,7 +13819,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -13882,10 +13897,10 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ62">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR62">
         <v>1.34</v>
@@ -14010,7 +14025,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14216,7 +14231,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14297,7 +14312,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR64">
         <v>1.45</v>
@@ -14422,7 +14437,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14500,7 +14515,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ65">
         <v>1.18</v>
@@ -14834,7 +14849,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -14912,10 +14927,10 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ67">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR67">
         <v>1.23</v>
@@ -15452,7 +15467,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15736,7 +15751,7 @@
         <v>1.6</v>
       </c>
       <c r="AP71">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ71">
         <v>1.42</v>
@@ -15864,7 +15879,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16354,10 +16369,10 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ74">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16563,7 +16578,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR75">
         <v>1.81</v>
@@ -16766,10 +16781,10 @@
         <v>0.6</v>
       </c>
       <c r="AP76">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ76">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR76">
         <v>1.38</v>
@@ -16894,7 +16909,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -16972,10 +16987,10 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ77">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR77">
         <v>1.44</v>
@@ -17512,7 +17527,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17718,7 +17733,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17796,7 +17811,7 @@
         <v>0.86</v>
       </c>
       <c r="AP81">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ81">
         <v>0.92</v>
@@ -17924,7 +17939,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -18130,7 +18145,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18211,7 +18226,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ83">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR83">
         <v>1.59</v>
@@ -18336,7 +18351,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18542,7 +18557,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -18826,10 +18841,10 @@
         <v>0.43</v>
       </c>
       <c r="AP86">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ86">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
         <v>1.41</v>
@@ -19032,7 +19047,7 @@
         <v>1.86</v>
       </c>
       <c r="AP87">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ87">
         <v>1.42</v>
@@ -19160,7 +19175,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19241,7 +19256,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ88">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR88">
         <v>1.19</v>
@@ -19444,7 +19459,7 @@
         <v>1.29</v>
       </c>
       <c r="AP89">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ89">
         <v>1.25</v>
@@ -19572,7 +19587,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19653,7 +19668,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ90">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR90">
         <v>1.66</v>
@@ -19778,7 +19793,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -20062,7 +20077,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ92">
         <v>1.18</v>
@@ -20602,7 +20617,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20808,7 +20823,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -20889,7 +20904,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ96">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR96">
         <v>1.89</v>
@@ -21301,7 +21316,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ98">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR98">
         <v>1.56</v>
@@ -21426,7 +21441,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21507,7 +21522,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ99">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21632,7 +21647,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21710,7 +21725,7 @@
         <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>1.42</v>
@@ -21838,7 +21853,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21916,7 +21931,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ101">
         <v>1.25</v>
@@ -22044,7 +22059,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22122,7 +22137,7 @@
         <v>1.14</v>
       </c>
       <c r="AP102">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ102">
         <v>1.18</v>
@@ -22456,7 +22471,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22662,7 +22677,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22740,7 +22755,7 @@
         <v>0.13</v>
       </c>
       <c r="AP105">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ105">
         <v>0.58</v>
@@ -22868,7 +22883,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -23155,7 +23170,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ107">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR107">
         <v>1.68</v>
@@ -23280,7 +23295,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23361,7 +23376,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR108">
         <v>1.51</v>
@@ -23773,7 +23788,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR110">
         <v>1.71</v>
@@ -23898,7 +23913,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>1.83</v>
@@ -23976,10 +23991,10 @@
         <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ111">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR111">
         <v>1.63</v>
@@ -24104,7 +24119,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24182,7 +24197,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ112">
         <v>1.33</v>
@@ -24516,7 +24531,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24594,7 +24609,7 @@
         <v>1.25</v>
       </c>
       <c r="AP114">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114">
         <v>1.42</v>
@@ -24722,7 +24737,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24928,7 +24943,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25134,7 +25149,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25340,7 +25355,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25418,7 +25433,7 @@
         <v>0.44</v>
       </c>
       <c r="AP118">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ118">
         <v>0.58</v>
@@ -25546,7 +25561,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -25833,7 +25848,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR120">
         <v>1.35</v>
@@ -26039,7 +26054,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ121">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR121">
         <v>1.67</v>
@@ -26242,7 +26257,7 @@
         <v>0.4</v>
       </c>
       <c r="AP122">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ122">
         <v>0.58</v>
@@ -26370,7 +26385,7 @@
         <v>87</v>
       </c>
       <c r="P123" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26448,10 +26463,10 @@
         <v>0.4</v>
       </c>
       <c r="AP123">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ123">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26576,7 +26591,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q124">
         <v>4.75</v>
@@ -26782,7 +26797,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -26988,7 +27003,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27069,7 +27084,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ126">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR126">
         <v>1.92</v>
@@ -27194,7 +27209,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>3.5</v>
@@ -27400,7 +27415,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q128">
         <v>2.25</v>
@@ -27606,7 +27621,7 @@
         <v>181</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>2.25</v>
@@ -28018,7 +28033,7 @@
         <v>183</v>
       </c>
       <c r="P131" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q131">
         <v>5</v>
@@ -28096,7 +28111,7 @@
         <v>1.3</v>
       </c>
       <c r="AP131">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ131">
         <v>1.18</v>
@@ -28224,7 +28239,7 @@
         <v>184</v>
       </c>
       <c r="P132" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q132">
         <v>4.75</v>
@@ -28302,10 +28317,10 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ132">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR132">
         <v>1.38</v>
@@ -28430,7 +28445,7 @@
         <v>87</v>
       </c>
       <c r="P133" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28511,7 +28526,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR133">
         <v>1.44</v>
@@ -28636,7 +28651,7 @@
         <v>87</v>
       </c>
       <c r="P134" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -28714,10 +28729,10 @@
         <v>1.27</v>
       </c>
       <c r="AP134">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ134">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -28920,10 +28935,10 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AQ135">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR135">
         <v>1.29</v>
@@ -29048,7 +29063,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29126,10 +29141,10 @@
         <v>0.59</v>
       </c>
       <c r="AP136">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AQ136">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AR136">
         <v>1.17</v>
@@ -29335,7 +29350,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ137">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.6</v>
@@ -29460,7 +29475,7 @@
         <v>87</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q138">
         <v>2.75</v>
@@ -29744,7 +29759,7 @@
         <v>1.59</v>
       </c>
       <c r="AP139">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AQ139">
         <v>1.58</v>
@@ -29872,7 +29887,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q140">
         <v>3.25</v>
@@ -30029,6 +30044,830 @@
       </c>
       <c r="BP140">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7861647</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>72</v>
+      </c>
+      <c r="H141" t="s">
+        <v>75</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>3</v>
+      </c>
+      <c r="O141" t="s">
+        <v>190</v>
+      </c>
+      <c r="P141" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q141">
+        <v>2.4</v>
+      </c>
+      <c r="R141">
+        <v>2.25</v>
+      </c>
+      <c r="S141">
+        <v>4.75</v>
+      </c>
+      <c r="T141">
+        <v>1.36</v>
+      </c>
+      <c r="U141">
+        <v>3</v>
+      </c>
+      <c r="V141">
+        <v>2.75</v>
+      </c>
+      <c r="W141">
+        <v>1.4</v>
+      </c>
+      <c r="X141">
+        <v>7</v>
+      </c>
+      <c r="Y141">
+        <v>1.1</v>
+      </c>
+      <c r="Z141">
+        <v>1.77</v>
+      </c>
+      <c r="AA141">
+        <v>3.69</v>
+      </c>
+      <c r="AB141">
+        <v>4.3</v>
+      </c>
+      <c r="AC141">
+        <v>1.05</v>
+      </c>
+      <c r="AD141">
+        <v>9.5</v>
+      </c>
+      <c r="AE141">
+        <v>1.25</v>
+      </c>
+      <c r="AF141">
+        <v>3.7</v>
+      </c>
+      <c r="AG141">
+        <v>1.8</v>
+      </c>
+      <c r="AH141">
+        <v>1.94</v>
+      </c>
+      <c r="AI141">
+        <v>1.75</v>
+      </c>
+      <c r="AJ141">
+        <v>2</v>
+      </c>
+      <c r="AK141">
+        <v>1.2</v>
+      </c>
+      <c r="AL141">
+        <v>1.22</v>
+      </c>
+      <c r="AM141">
+        <v>2</v>
+      </c>
+      <c r="AN141">
+        <v>1.43</v>
+      </c>
+      <c r="AO141">
+        <v>0.78</v>
+      </c>
+      <c r="AP141">
+        <v>1.5</v>
+      </c>
+      <c r="AQ141">
+        <v>0.75</v>
+      </c>
+      <c r="AR141">
+        <v>1.44</v>
+      </c>
+      <c r="AS141">
+        <v>1.2</v>
+      </c>
+      <c r="AT141">
+        <v>2.64</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>3</v>
+      </c>
+      <c r="AW141">
+        <v>3</v>
+      </c>
+      <c r="AX141">
+        <v>6</v>
+      </c>
+      <c r="AY141">
+        <v>9</v>
+      </c>
+      <c r="AZ141">
+        <v>10</v>
+      </c>
+      <c r="BA141">
+        <v>1</v>
+      </c>
+      <c r="BB141">
+        <v>3</v>
+      </c>
+      <c r="BC141">
+        <v>4</v>
+      </c>
+      <c r="BD141">
+        <v>1.61</v>
+      </c>
+      <c r="BE141">
+        <v>6.4</v>
+      </c>
+      <c r="BF141">
+        <v>2.55</v>
+      </c>
+      <c r="BG141">
+        <v>1.28</v>
+      </c>
+      <c r="BH141">
+        <v>3.3</v>
+      </c>
+      <c r="BI141">
+        <v>1.48</v>
+      </c>
+      <c r="BJ141">
+        <v>2.45</v>
+      </c>
+      <c r="BK141">
+        <v>1.76</v>
+      </c>
+      <c r="BL141">
+        <v>1.94</v>
+      </c>
+      <c r="BM141">
+        <v>2.17</v>
+      </c>
+      <c r="BN141">
+        <v>1.6</v>
+      </c>
+      <c r="BO141">
+        <v>2.8</v>
+      </c>
+      <c r="BP141">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7861646</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142" t="s">
+        <v>74</v>
+      </c>
+      <c r="H142" t="s">
+        <v>76</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>2</v>
+      </c>
+      <c r="L142">
+        <v>2</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>3</v>
+      </c>
+      <c r="O142" t="s">
+        <v>191</v>
+      </c>
+      <c r="P142" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q142">
+        <v>2.2</v>
+      </c>
+      <c r="R142">
+        <v>2.4</v>
+      </c>
+      <c r="S142">
+        <v>5</v>
+      </c>
+      <c r="T142">
+        <v>1.29</v>
+      </c>
+      <c r="U142">
+        <v>3.5</v>
+      </c>
+      <c r="V142">
+        <v>2.38</v>
+      </c>
+      <c r="W142">
+        <v>1.53</v>
+      </c>
+      <c r="X142">
+        <v>5.5</v>
+      </c>
+      <c r="Y142">
+        <v>1.14</v>
+      </c>
+      <c r="Z142">
+        <v>1.76</v>
+      </c>
+      <c r="AA142">
+        <v>3.65</v>
+      </c>
+      <c r="AB142">
+        <v>4.4</v>
+      </c>
+      <c r="AC142">
+        <v>1.04</v>
+      </c>
+      <c r="AD142">
+        <v>10</v>
+      </c>
+      <c r="AE142">
+        <v>1.2</v>
+      </c>
+      <c r="AF142">
+        <v>4.33</v>
+      </c>
+      <c r="AG142">
+        <v>1.55</v>
+      </c>
+      <c r="AH142">
+        <v>2.2</v>
+      </c>
+      <c r="AI142">
+        <v>1.62</v>
+      </c>
+      <c r="AJ142">
+        <v>2.2</v>
+      </c>
+      <c r="AK142">
+        <v>1.17</v>
+      </c>
+      <c r="AL142">
+        <v>1.18</v>
+      </c>
+      <c r="AM142">
+        <v>2.2</v>
+      </c>
+      <c r="AN142">
+        <v>1.35</v>
+      </c>
+      <c r="AO142">
+        <v>0.87</v>
+      </c>
+      <c r="AP142">
+        <v>1.42</v>
+      </c>
+      <c r="AQ142">
+        <v>0.83</v>
+      </c>
+      <c r="AR142">
+        <v>1.42</v>
+      </c>
+      <c r="AS142">
+        <v>1.27</v>
+      </c>
+      <c r="AT142">
+        <v>2.69</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>7</v>
+      </c>
+      <c r="AW142">
+        <v>6</v>
+      </c>
+      <c r="AX142">
+        <v>10</v>
+      </c>
+      <c r="AY142">
+        <v>12</v>
+      </c>
+      <c r="AZ142">
+        <v>17</v>
+      </c>
+      <c r="BA142">
+        <v>4</v>
+      </c>
+      <c r="BB142">
+        <v>5</v>
+      </c>
+      <c r="BC142">
+        <v>9</v>
+      </c>
+      <c r="BD142">
+        <v>1.65</v>
+      </c>
+      <c r="BE142">
+        <v>6.75</v>
+      </c>
+      <c r="BF142">
+        <v>2.48</v>
+      </c>
+      <c r="BG142">
+        <v>1.25</v>
+      </c>
+      <c r="BH142">
+        <v>3.4</v>
+      </c>
+      <c r="BI142">
+        <v>1.44</v>
+      </c>
+      <c r="BJ142">
+        <v>2.55</v>
+      </c>
+      <c r="BK142">
+        <v>1.73</v>
+      </c>
+      <c r="BL142">
+        <v>1.96</v>
+      </c>
+      <c r="BM142">
+        <v>2.14</v>
+      </c>
+      <c r="BN142">
+        <v>1.61</v>
+      </c>
+      <c r="BO142">
+        <v>2.7</v>
+      </c>
+      <c r="BP142">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7861648</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45753.45833333334</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>73</v>
+      </c>
+      <c r="H143" t="s">
+        <v>78</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>192</v>
+      </c>
+      <c r="P143" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q143">
+        <v>2.88</v>
+      </c>
+      <c r="R143">
+        <v>2.3</v>
+      </c>
+      <c r="S143">
+        <v>3.4</v>
+      </c>
+      <c r="T143">
+        <v>1.33</v>
+      </c>
+      <c r="U143">
+        <v>3.25</v>
+      </c>
+      <c r="V143">
+        <v>2.5</v>
+      </c>
+      <c r="W143">
+        <v>1.5</v>
+      </c>
+      <c r="X143">
+        <v>6.5</v>
+      </c>
+      <c r="Y143">
+        <v>1.11</v>
+      </c>
+      <c r="Z143">
+        <v>2.33</v>
+      </c>
+      <c r="AA143">
+        <v>3.7</v>
+      </c>
+      <c r="AB143">
+        <v>2.7</v>
+      </c>
+      <c r="AC143">
+        <v>1.04</v>
+      </c>
+      <c r="AD143">
+        <v>10</v>
+      </c>
+      <c r="AE143">
+        <v>1.2</v>
+      </c>
+      <c r="AF143">
+        <v>4.33</v>
+      </c>
+      <c r="AG143">
+        <v>1.6</v>
+      </c>
+      <c r="AH143">
+        <v>2.15</v>
+      </c>
+      <c r="AI143">
+        <v>1.57</v>
+      </c>
+      <c r="AJ143">
+        <v>2.25</v>
+      </c>
+      <c r="AK143">
+        <v>1.4</v>
+      </c>
+      <c r="AL143">
+        <v>1.22</v>
+      </c>
+      <c r="AM143">
+        <v>1.6</v>
+      </c>
+      <c r="AN143">
+        <v>0.7</v>
+      </c>
+      <c r="AO143">
+        <v>0.91</v>
+      </c>
+      <c r="AP143">
+        <v>0.71</v>
+      </c>
+      <c r="AQ143">
+        <v>0.92</v>
+      </c>
+      <c r="AR143">
+        <v>1.28</v>
+      </c>
+      <c r="AS143">
+        <v>1.29</v>
+      </c>
+      <c r="AT143">
+        <v>2.57</v>
+      </c>
+      <c r="AU143">
+        <v>3</v>
+      </c>
+      <c r="AV143">
+        <v>4</v>
+      </c>
+      <c r="AW143">
+        <v>10</v>
+      </c>
+      <c r="AX143">
+        <v>7</v>
+      </c>
+      <c r="AY143">
+        <v>15</v>
+      </c>
+      <c r="AZ143">
+        <v>12</v>
+      </c>
+      <c r="BA143">
+        <v>5</v>
+      </c>
+      <c r="BB143">
+        <v>5</v>
+      </c>
+      <c r="BC143">
+        <v>10</v>
+      </c>
+      <c r="BD143">
+        <v>1.88</v>
+      </c>
+      <c r="BE143">
+        <v>6.4</v>
+      </c>
+      <c r="BF143">
+        <v>2.12</v>
+      </c>
+      <c r="BG143">
+        <v>1.25</v>
+      </c>
+      <c r="BH143">
+        <v>3.45</v>
+      </c>
+      <c r="BI143">
+        <v>1.44</v>
+      </c>
+      <c r="BJ143">
+        <v>2.55</v>
+      </c>
+      <c r="BK143">
+        <v>1.72</v>
+      </c>
+      <c r="BL143">
+        <v>1.98</v>
+      </c>
+      <c r="BM143">
+        <v>2.14</v>
+      </c>
+      <c r="BN143">
+        <v>1.61</v>
+      </c>
+      <c r="BO143">
+        <v>2.65</v>
+      </c>
+      <c r="BP143">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7861620</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45753.54166666666</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>71</v>
+      </c>
+      <c r="H144" t="s">
+        <v>79</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
+        <v>87</v>
+      </c>
+      <c r="P144" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q144">
+        <v>3.4</v>
+      </c>
+      <c r="R144">
+        <v>2.25</v>
+      </c>
+      <c r="S144">
+        <v>3</v>
+      </c>
+      <c r="T144">
+        <v>1.36</v>
+      </c>
+      <c r="U144">
+        <v>3</v>
+      </c>
+      <c r="V144">
+        <v>2.63</v>
+      </c>
+      <c r="W144">
+        <v>1.44</v>
+      </c>
+      <c r="X144">
+        <v>7</v>
+      </c>
+      <c r="Y144">
+        <v>1.1</v>
+      </c>
+      <c r="Z144">
+        <v>2.61</v>
+      </c>
+      <c r="AA144">
+        <v>3.5</v>
+      </c>
+      <c r="AB144">
+        <v>2.5</v>
+      </c>
+      <c r="AC144">
+        <v>1.04</v>
+      </c>
+      <c r="AD144">
+        <v>10</v>
+      </c>
+      <c r="AE144">
+        <v>1.25</v>
+      </c>
+      <c r="AF144">
+        <v>3.95</v>
+      </c>
+      <c r="AG144">
+        <v>1.77</v>
+      </c>
+      <c r="AH144">
+        <v>1.98</v>
+      </c>
+      <c r="AI144">
+        <v>1.62</v>
+      </c>
+      <c r="AJ144">
+        <v>2.2</v>
+      </c>
+      <c r="AK144">
+        <v>1.57</v>
+      </c>
+      <c r="AL144">
+        <v>1.22</v>
+      </c>
+      <c r="AM144">
+        <v>1.42</v>
+      </c>
+      <c r="AN144">
+        <v>1.52</v>
+      </c>
+      <c r="AO144">
+        <v>1.91</v>
+      </c>
+      <c r="AP144">
+        <v>1.46</v>
+      </c>
+      <c r="AQ144">
+        <v>1.96</v>
+      </c>
+      <c r="AR144">
+        <v>1.67</v>
+      </c>
+      <c r="AS144">
+        <v>1.77</v>
+      </c>
+      <c r="AT144">
+        <v>3.44</v>
+      </c>
+      <c r="AU144">
+        <v>3</v>
+      </c>
+      <c r="AV144">
+        <v>6</v>
+      </c>
+      <c r="AW144">
+        <v>3</v>
+      </c>
+      <c r="AX144">
+        <v>10</v>
+      </c>
+      <c r="AY144">
+        <v>8</v>
+      </c>
+      <c r="AZ144">
+        <v>18</v>
+      </c>
+      <c r="BA144">
+        <v>3</v>
+      </c>
+      <c r="BB144">
+        <v>2</v>
+      </c>
+      <c r="BC144">
+        <v>5</v>
+      </c>
+      <c r="BD144">
+        <v>2.02</v>
+      </c>
+      <c r="BE144">
+        <v>6.4</v>
+      </c>
+      <c r="BF144">
+        <v>1.97</v>
+      </c>
+      <c r="BG144">
+        <v>1.3</v>
+      </c>
+      <c r="BH144">
+        <v>3.15</v>
+      </c>
+      <c r="BI144">
+        <v>1.53</v>
+      </c>
+      <c r="BJ144">
+        <v>2.32</v>
+      </c>
+      <c r="BK144">
+        <v>1.86</v>
+      </c>
+      <c r="BL144">
+        <v>1.82</v>
+      </c>
+      <c r="BM144">
+        <v>2.33</v>
+      </c>
+      <c r="BN144">
+        <v>1.5</v>
+      </c>
+      <c r="BO144">
+        <v>3.05</v>
+      </c>
+      <c r="BP144">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Denmark Superliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="278">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,9 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['13', '50']</t>
+  </si>
+  <si>
     <t>['53', '59', '90+2']</t>
   </si>
   <si>
@@ -842,6 +845,9 @@
   </si>
   <si>
     <t>['38']</t>
+  </si>
+  <si>
+    <t>['73']</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2077,7 +2083,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2283,7 +2289,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2489,7 +2495,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -2901,7 +2907,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -3313,7 +3319,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3519,7 +3525,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3600,7 +3606,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ12">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3803,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ13">
         <v>0.58</v>
@@ -4549,7 +4555,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q17">
         <v>1.95</v>
@@ -4755,7 +4761,7 @@
         <v>87</v>
       </c>
       <c r="P18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -4961,7 +4967,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5579,7 +5585,7 @@
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -5785,7 +5791,7 @@
         <v>87</v>
       </c>
       <c r="P23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5863,10 +5869,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR23">
         <v>1.53</v>
@@ -5991,7 +5997,7 @@
         <v>87</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -6197,7 +6203,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>2.5</v>
@@ -6403,7 +6409,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6609,7 +6615,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6815,7 +6821,7 @@
         <v>103</v>
       </c>
       <c r="P28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7021,7 +7027,7 @@
         <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -7227,7 +7233,7 @@
         <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q30">
         <v>4</v>
@@ -7639,7 +7645,7 @@
         <v>87</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -7720,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>1.14</v>
@@ -7845,7 +7851,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q33">
         <v>2.25</v>
@@ -8051,7 +8057,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8257,7 +8263,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8463,7 +8469,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8541,7 +8547,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ36">
         <v>1.42</v>
@@ -9081,7 +9087,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
@@ -9287,7 +9293,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9493,7 +9499,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q41">
         <v>2.75</v>
@@ -9699,7 +9705,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10111,7 +10117,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10317,7 +10323,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10523,7 +10529,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10729,7 +10735,7 @@
         <v>87</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>3.4</v>
@@ -11013,7 +11019,7 @@
         <v>0.75</v>
       </c>
       <c r="AP48">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48">
         <v>0.67</v>
@@ -11347,7 +11353,7 @@
         <v>120</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11759,7 +11765,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -12046,7 +12052,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ53">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR53">
         <v>1.13</v>
@@ -12171,7 +12177,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>4.5</v>
@@ -12583,7 +12589,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13201,7 +13207,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -13407,7 +13413,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q60">
         <v>6.5</v>
@@ -13613,7 +13619,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13819,7 +13825,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -14025,7 +14031,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14231,7 +14237,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -14437,7 +14443,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65">
         <v>3.2</v>
@@ -14518,7 +14524,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14721,7 +14727,7 @@
         <v>1.8</v>
       </c>
       <c r="AP66">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>1.25</v>
@@ -14849,7 +14855,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>4.5</v>
@@ -15467,7 +15473,7 @@
         <v>87</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>3.6</v>
@@ -15879,7 +15885,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72">
         <v>5</v>
@@ -16575,7 +16581,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75">
         <v>1.58</v>
@@ -16909,7 +16915,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q77">
         <v>2.2</v>
@@ -17196,7 +17202,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ78">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR78">
         <v>1.92</v>
@@ -17527,7 +17533,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17733,7 +17739,7 @@
         <v>147</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17939,7 +17945,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -18145,7 +18151,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q83">
         <v>2</v>
@@ -18351,7 +18357,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q84">
         <v>2.63</v>
@@ -18557,7 +18563,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q85">
         <v>1.91</v>
@@ -19175,7 +19181,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>3</v>
@@ -19587,7 +19593,7 @@
         <v>155</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19793,7 +19799,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
@@ -19871,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ91">
         <v>0.83</v>
@@ -20080,7 +20086,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ92">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
         <v>1.68</v>
@@ -20617,7 +20623,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q95">
         <v>5.5</v>
@@ -20823,7 +20829,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q96">
         <v>1.73</v>
@@ -21313,7 +21319,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ98">
         <v>0.83</v>
@@ -21441,7 +21447,7 @@
         <v>87</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21647,7 +21653,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21853,7 +21859,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22059,7 +22065,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q102">
         <v>4.33</v>
@@ -22140,7 +22146,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.25</v>
@@ -22471,7 +22477,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q104">
         <v>2.05</v>
@@ -22549,7 +22555,7 @@
         <v>0.78</v>
       </c>
       <c r="AP104">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ104">
         <v>0.92</v>
@@ -22677,7 +22683,7 @@
         <v>87</v>
       </c>
       <c r="P105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>2.3</v>
@@ -22883,7 +22889,7 @@
         <v>160</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>5</v>
@@ -22964,7 +22970,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR106">
         <v>1.4</v>
@@ -23295,7 +23301,7 @@
         <v>129</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q108">
         <v>3.6</v>
@@ -23913,7 +23919,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>1.83</v>
@@ -24119,7 +24125,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24531,7 +24537,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24737,7 +24743,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24943,7 +24949,7 @@
         <v>165</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>3.75</v>
@@ -25024,7 +25030,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ116">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR116">
         <v>1.48</v>
@@ -25149,7 +25155,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25355,7 +25361,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25561,7 +25567,7 @@
         <v>174</v>
       </c>
       <c r="P119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>2.5</v>
@@ -26051,7 +26057,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121">
         <v>0.58</v>
@@ -26385,7 +26391,7 @@
         <v>87</v>
       </c>
       <c r="P123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26591,7 +26597,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>4.75</v>
@@ -26797,7 +26803,7 @@
         <v>178</v>
       </c>
       <c r="P125" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q125">
         <v>2.25</v>
@@ -27003,7 +27009,7 @@
         <v>82</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>1.73</v>
@@ -27209,7 +27215,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q127">
         <v>3.5</v>
@@ -27415,7 +27421,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q128">
         <v>2.25</v>
@@ -27493,7 +27499,7 @@
         <v>1.6</v>
       </c>
       <c r="AP128">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ128">
         <v>1.42</v>
@@ -27621,7 +27627,7 @@
         <v>181</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>2.25</v>
@@ -28033,7 +28039,7 @@
         <v>183</v>
       </c>
       <c r="P131" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>5</v>
@@ -28114,7 +28120,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ131">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR131">
         <v>1.4</v>
@@ -28239,7 +28245,7 @@
         <v>184</v>
       </c>
       <c r="P132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>4.75</v>
@@ -28445,7 +28451,7 @@
         <v>87</v>
       </c>
       <c r="P133" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28651,7 +28657,7 @@
         <v>87</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29063,7 +29069,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29347,7 +29353,7 @@
         <v>1.59</v>
       </c>
       <c r="AP137">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AQ137">
         <v>1.46</v>
@@ -29475,7 +29481,7 @@
         <v>87</v>
       </c>
       <c r="P138" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q138">
         <v>2.75</v>
@@ -29556,7 +29562,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ138">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AR138">
         <v>1.7</v>
@@ -29887,7 +29893,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q140">
         <v>3.25</v>
@@ -30093,7 +30099,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30299,7 +30305,7 @@
         <v>191</v>
       </c>
       <c r="P142" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q142">
         <v>2.2</v>
@@ -30505,7 +30511,7 @@
         <v>192</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>2.88</v>
@@ -30868,6 +30874,212 @@
       </c>
       <c r="BP144">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7861621</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145" t="s">
+        <v>80</v>
+      </c>
+      <c r="H145" t="s">
+        <v>70</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>2</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>3</v>
+      </c>
+      <c r="O145" t="s">
+        <v>193</v>
+      </c>
+      <c r="P145" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q145">
+        <v>3.1</v>
+      </c>
+      <c r="R145">
+        <v>2.1</v>
+      </c>
+      <c r="S145">
+        <v>3.5</v>
+      </c>
+      <c r="T145">
+        <v>1.4</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>3</v>
+      </c>
+      <c r="W145">
+        <v>1.36</v>
+      </c>
+      <c r="X145">
+        <v>8</v>
+      </c>
+      <c r="Y145">
+        <v>1.08</v>
+      </c>
+      <c r="Z145">
+        <v>2.34</v>
+      </c>
+      <c r="AA145">
+        <v>3.42</v>
+      </c>
+      <c r="AB145">
+        <v>3.03</v>
+      </c>
+      <c r="AC145">
+        <v>1</v>
+      </c>
+      <c r="AD145">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AE145">
+        <v>1.28</v>
+      </c>
+      <c r="AF145">
+        <v>3.63</v>
+      </c>
+      <c r="AG145">
+        <v>1.95</v>
+      </c>
+      <c r="AH145">
+        <v>1.88</v>
+      </c>
+      <c r="AI145">
+        <v>1.75</v>
+      </c>
+      <c r="AJ145">
+        <v>2</v>
+      </c>
+      <c r="AK145">
+        <v>1.36</v>
+      </c>
+      <c r="AL145">
+        <v>1.25</v>
+      </c>
+      <c r="AM145">
+        <v>1.57</v>
+      </c>
+      <c r="AN145">
+        <v>1.57</v>
+      </c>
+      <c r="AO145">
+        <v>1.7</v>
+      </c>
+      <c r="AP145">
+        <v>1.63</v>
+      </c>
+      <c r="AQ145">
+        <v>1.63</v>
+      </c>
+      <c r="AR145">
+        <v>1.79</v>
+      </c>
+      <c r="AS145">
+        <v>1.6</v>
+      </c>
+      <c r="AT145">
+        <v>3.39</v>
+      </c>
+      <c r="AU145">
+        <v>5</v>
+      </c>
+      <c r="AV145">
+        <v>4</v>
+      </c>
+      <c r="AW145">
+        <v>7</v>
+      </c>
+      <c r="AX145">
+        <v>5</v>
+      </c>
+      <c r="AY145">
+        <v>13</v>
+      </c>
+      <c r="AZ145">
+        <v>10</v>
+      </c>
+      <c r="BA145">
+        <v>4</v>
+      </c>
+      <c r="BB145">
+        <v>5</v>
+      </c>
+      <c r="BC145">
+        <v>9</v>
+      </c>
+      <c r="BD145">
+        <v>1.79</v>
+      </c>
+      <c r="BE145">
+        <v>6.4</v>
+      </c>
+      <c r="BF145">
+        <v>2.23</v>
+      </c>
+      <c r="BG145">
+        <v>1.29</v>
+      </c>
+      <c r="BH145">
+        <v>3.2</v>
+      </c>
+      <c r="BI145">
+        <v>1.5</v>
+      </c>
+      <c r="BJ145">
+        <v>2.4</v>
+      </c>
+      <c r="BK145">
+        <v>1.81</v>
+      </c>
+      <c r="BL145">
+        <v>1.88</v>
+      </c>
+      <c r="BM145">
+        <v>2.25</v>
+      </c>
+      <c r="BN145">
+        <v>1.55</v>
+      </c>
+      <c r="BO145">
+        <v>2.9</v>
+      </c>
+      <c r="BP145">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
